--- a/www/flightdata/xlsx/eoss-308.xlsx
+++ b/www/flightdata/xlsx/eoss-308.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="486">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>504</t>
+  </si>
+  <si>
+    <t>1hrs 36mins 30secs</t>
   </si>
   <si>
     <t>18.68</t>
@@ -1820,10 +1835,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1863,46 +1878,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>98291</v>
+      </c>
+      <c r="H2">
+        <v>209</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>5790</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1917,102 +1956,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>44289.28019246528</v>
@@ -2030,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2060,7 +2099,7 @@
         <v>1.1</v>
       </c>
       <c r="V2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="X2">
         <v>1.1</v>
@@ -2071,10 +2110,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>44289.28077677084</v>
@@ -2092,13 +2131,13 @@
         <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K3">
         <v>152</v>
@@ -2134,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W3">
         <v>-0.003333</v>
@@ -2157,10 +2196,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>44289.2812353125</v>
@@ -2178,13 +2217,13 @@
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -2208,7 +2247,7 @@
         <v>9.733333330000001</v>
       </c>
       <c r="V4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W4">
         <v>0.145556</v>
@@ -2237,10 +2276,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>44289.28146958334</v>
@@ -2258,13 +2297,13 @@
         <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="K5">
         <v>27</v>
@@ -2300,7 +2339,7 @@
         <v>18.98333333</v>
       </c>
       <c r="V5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W5">
         <v>0.154167</v>
@@ -2329,10 +2368,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>44289.28192900463</v>
@@ -2350,13 +2389,13 @@
         <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K6">
         <v>66</v>
@@ -2380,7 +2419,7 @@
         <v>23.41666667</v>
       </c>
       <c r="V6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W6">
         <v>0.073889</v>
@@ -2409,10 +2448,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>44289.28216378472</v>
@@ -2430,13 +2469,13 @@
         <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K7">
         <v>53</v>
@@ -2472,7 +2511,7 @@
         <v>23.5</v>
       </c>
       <c r="V7" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W7">
         <v>0.001389</v>
@@ -2501,10 +2540,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>44289.28227481482</v>
@@ -2522,13 +2561,13 @@
         <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -2552,7 +2591,7 @@
         <v>23.26666667</v>
       </c>
       <c r="V8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W8">
         <v>-0.007778</v>
@@ -2581,10 +2620,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>44289.28262090278</v>
@@ -2602,13 +2641,13 @@
         <v>210</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K9">
         <v>51</v>
@@ -2632,7 +2671,7 @@
         <v>23.63333333</v>
       </c>
       <c r="V9" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W9">
         <v>0.012222</v>
@@ -2661,10 +2700,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>44289.28285877315</v>
@@ -2682,13 +2721,13 @@
         <v>228</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K10">
         <v>89</v>
@@ -2724,7 +2763,7 @@
         <v>24.1</v>
       </c>
       <c r="V10" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W10">
         <v>0.007778</v>
@@ -2753,10 +2792,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>44289.28331505787</v>
@@ -2774,13 +2813,13 @@
         <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K11">
         <v>121</v>
@@ -2804,7 +2843,7 @@
         <v>23.8</v>
       </c>
       <c r="V11" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W11">
         <v>-0.005</v>
@@ -2833,10 +2872,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>44289.28355309028</v>
@@ -2854,13 +2893,13 @@
         <v>288</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K12">
         <v>108</v>
@@ -2896,7 +2935,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V12" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W12">
         <v>0.006111</v>
@@ -2925,10 +2964,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>44289.28366530093</v>
@@ -2946,13 +2985,13 @@
         <v>300</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K13">
         <v>131</v>
@@ -2976,7 +3015,7 @@
         <v>24.8</v>
       </c>
       <c r="V13" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W13">
         <v>0.021111</v>
@@ -3005,10 +3044,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>44289.28424723379</v>
@@ -3026,13 +3065,13 @@
         <v>348</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K14">
         <v>139</v>
@@ -3068,7 +3107,7 @@
         <v>25.16666667</v>
       </c>
       <c r="V14" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W14">
         <v>0.006111</v>
@@ -3097,10 +3136,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>44289.28494046296</v>
@@ -3118,13 +3157,13 @@
         <v>408</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K15">
         <v>123</v>
@@ -3160,7 +3199,7 @@
         <v>25.71666667</v>
       </c>
       <c r="V15" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W15">
         <v>0.009167</v>
@@ -3189,10 +3228,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>44289.28505245371</v>
@@ -3210,13 +3249,13 @@
         <v>420</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K16">
         <v>106</v>
@@ -3240,7 +3279,7 @@
         <v>25.625</v>
       </c>
       <c r="V16" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W16">
         <v>-0.000764</v>
@@ -3269,10 +3308,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>44289.28539890047</v>
@@ -3290,13 +3329,13 @@
         <v>450</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K17">
         <v>127</v>
@@ -3320,7 +3359,7 @@
         <v>26.36666667</v>
       </c>
       <c r="V17" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W17">
         <v>0.024722</v>
@@ -3349,10 +3388,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>44289.28563660879</v>
@@ -3370,13 +3409,13 @@
         <v>468</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K18">
         <v>121</v>
@@ -3412,7 +3451,7 @@
         <v>26.48333333</v>
       </c>
       <c r="V18" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W18">
         <v>0.001944</v>
@@ -3441,10 +3480,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>44289.28609410879</v>
@@ -3462,13 +3501,13 @@
         <v>510</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K19">
         <v>119</v>
@@ -3492,7 +3531,7 @@
         <v>27.4</v>
       </c>
       <c r="V19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W19">
         <v>0.015278</v>
@@ -3521,10 +3560,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>44289.28633056713</v>
@@ -3542,13 +3581,13 @@
         <v>528</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K20">
         <v>87</v>
@@ -3584,7 +3623,7 @@
         <v>27.73333333</v>
       </c>
       <c r="V20" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W20">
         <v>0.005556</v>
@@ -3613,10 +3652,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>44289.28644520833</v>
@@ -3634,13 +3673,13 @@
         <v>540</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K21">
         <v>25</v>
@@ -3664,7 +3703,7 @@
         <v>28</v>
       </c>
       <c r="V21" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W21">
         <v>0.008888999999999999</v>
@@ -3693,10 +3732,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>44289.2867875463</v>
@@ -3714,13 +3753,13 @@
         <v>570</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K22">
         <v>70</v>
@@ -3744,7 +3783,7 @@
         <v>27</v>
       </c>
       <c r="V22" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W22">
         <v>-0.033333</v>
@@ -3773,10 +3812,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>44289.28702484954</v>
@@ -3794,13 +3833,13 @@
         <v>588</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K23">
         <v>141</v>
@@ -3836,7 +3875,7 @@
         <v>27.56666667</v>
       </c>
       <c r="V23" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W23">
         <v>0.009443999999999999</v>
@@ -3865,10 +3904,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>44289.28772012731</v>
@@ -3886,13 +3925,13 @@
         <v>648</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K24">
         <v>88</v>
@@ -3928,7 +3967,7 @@
         <v>27.93333333</v>
       </c>
       <c r="V24" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W24">
         <v>0.006111</v>
@@ -3957,10 +3996,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>44289.28783434028</v>
@@ -3978,13 +4017,13 @@
         <v>660</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K25">
         <v>165</v>
@@ -4008,7 +4047,7 @@
         <v>27.96666667</v>
       </c>
       <c r="V25" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W25">
         <v>0.00037</v>
@@ -4037,10 +4076,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>44289.28817766203</v>
@@ -4058,13 +4097,13 @@
         <v>690</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K26">
         <v>145</v>
@@ -4088,7 +4127,7 @@
         <v>27.43333333</v>
       </c>
       <c r="V26" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W26">
         <v>-0.017778</v>
@@ -4117,10 +4156,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>44289.28910834491</v>
@@ -4138,13 +4177,13 @@
         <v>768</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K27">
         <v>136</v>
@@ -4180,7 +4219,7 @@
         <v>27.76666667</v>
       </c>
       <c r="V27" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W27">
         <v>0.002778</v>
@@ -4209,10 +4248,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>44289.28922019676</v>
@@ -4230,13 +4269,13 @@
         <v>780</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K28">
         <v>136</v>
@@ -4260,7 +4299,7 @@
         <v>27.9</v>
       </c>
       <c r="V28" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W28">
         <v>0.001481</v>
@@ -4289,10 +4328,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>44289.28956606481</v>
@@ -4310,13 +4349,13 @@
         <v>810</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K29">
         <v>129</v>
@@ -4340,7 +4379,7 @@
         <v>28.3</v>
       </c>
       <c r="V29" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W29">
         <v>0.013333</v>
@@ -4369,10 +4408,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>44289.28980344907</v>
@@ -4390,13 +4429,13 @@
         <v>828</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K30">
         <v>129</v>
@@ -4432,7 +4471,7 @@
         <v>28.38333333</v>
       </c>
       <c r="V30" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W30">
         <v>0.001389</v>
@@ -4461,10 +4500,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>44289.29049829861</v>
@@ -4482,13 +4521,13 @@
         <v>888</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K31">
         <v>106</v>
@@ -4524,7 +4563,7 @@
         <v>28.9</v>
       </c>
       <c r="V31" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W31">
         <v>0.008611000000000001</v>
@@ -4553,10 +4592,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>44289.29060908565</v>
@@ -4574,13 +4613,13 @@
         <v>900</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K32">
         <v>77</v>
@@ -4604,7 +4643,7 @@
         <v>28.65555556</v>
       </c>
       <c r="V32" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W32">
         <v>-0.002716</v>
@@ -4633,10 +4672,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>44289.29095655093</v>
@@ -4654,13 +4693,13 @@
         <v>930</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K33">
         <v>118</v>
@@ -4684,7 +4723,7 @@
         <v>27.8</v>
       </c>
       <c r="V33" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W33">
         <v>-0.028519</v>
@@ -4713,10 +4752,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>44289.29119109954</v>
@@ -4734,13 +4773,13 @@
         <v>948</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K34">
         <v>114</v>
@@ -4776,7 +4815,7 @@
         <v>28.01666667</v>
       </c>
       <c r="V34" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W34">
         <v>0.003611</v>
@@ -4805,10 +4844,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>44289.2918871875</v>
@@ -4826,13 +4865,13 @@
         <v>1008</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K35">
         <v>108</v>
@@ -4868,7 +4907,7 @@
         <v>28.26666667</v>
       </c>
       <c r="V35" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W35">
         <v>0.004167</v>
@@ -4897,10 +4936,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>44289.29200021991</v>
@@ -4918,13 +4957,13 @@
         <v>1020</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K36">
         <v>168</v>
@@ -4948,7 +4987,7 @@
         <v>28.36666667</v>
       </c>
       <c r="V36" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W36">
         <v>0.001111</v>
@@ -4977,10 +5016,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>44289.29234341435</v>
@@ -4998,13 +5037,13 @@
         <v>1050</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K37">
         <v>110</v>
@@ -5028,7 +5067,7 @@
         <v>28.53333333</v>
       </c>
       <c r="V37" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W37">
         <v>0.005556</v>
@@ -5057,10 +5096,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>44289.29258180556</v>
@@ -5078,13 +5117,13 @@
         <v>1068</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K38">
         <v>152</v>
@@ -5120,7 +5159,7 @@
         <v>28.98333333</v>
       </c>
       <c r="V38" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W38">
         <v>0.0075</v>
@@ -5149,10 +5188,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>44289.29327503472</v>
@@ -5170,13 +5209,13 @@
         <v>1128</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K39">
         <v>117</v>
@@ -5212,7 +5251,7 @@
         <v>29.56666667</v>
       </c>
       <c r="V39" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W39">
         <v>0.009722</v>
@@ -5241,10 +5280,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>44289.29338480324</v>
@@ -5262,13 +5301,13 @@
         <v>1140</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K40">
         <v>70</v>
@@ -5292,7 +5331,7 @@
         <v>29.78888889</v>
       </c>
       <c r="V40" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W40">
         <v>0.002469</v>
@@ -5321,10 +5360,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>44289.29373170139</v>
@@ -5342,13 +5381,13 @@
         <v>1170</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K41">
         <v>144</v>
@@ -5372,7 +5411,7 @@
         <v>28.53333333</v>
       </c>
       <c r="V41" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W41">
         <v>-0.041852</v>
@@ -5401,10 +5440,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>44289.29397111111</v>
@@ -5422,13 +5461,13 @@
         <v>1188</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K42">
         <v>120</v>
@@ -5464,7 +5503,7 @@
         <v>28.48333333</v>
       </c>
       <c r="V42" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W42">
         <v>-0.000833</v>
@@ -5493,10 +5532,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>44289.29410799769</v>
@@ -5514,13 +5553,13 @@
         <v>1200</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K43">
         <v>92</v>
@@ -5544,7 +5583,7 @@
         <v>28.9</v>
       </c>
       <c r="V43" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W43">
         <v>0.013889</v>
@@ -5573,10 +5612,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>44289.29443003472</v>
@@ -5594,13 +5633,13 @@
         <v>1230</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K44">
         <v>76</v>
@@ -5624,7 +5663,7 @@
         <v>30.4</v>
       </c>
       <c r="V44" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W44">
         <v>0.05</v>
@@ -5653,10 +5692,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2">
         <v>44289.29466424768</v>
@@ -5674,13 +5713,13 @@
         <v>1248</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K45">
         <v>136</v>
@@ -5716,7 +5755,7 @@
         <v>31.2</v>
       </c>
       <c r="V45" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W45">
         <v>0.013333</v>
@@ -5745,10 +5784,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>44289.29477479167</v>
@@ -5766,13 +5805,13 @@
         <v>1260</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K46">
         <v>136</v>
@@ -5796,7 +5835,7 @@
         <v>28.1</v>
       </c>
       <c r="V46" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W46">
         <v>-0.103333</v>
@@ -5825,10 +5864,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>44289.29512045139</v>
@@ -5846,13 +5885,13 @@
         <v>1290</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K47">
         <v>163</v>
@@ -5876,7 +5915,7 @@
         <v>29.43333333</v>
       </c>
       <c r="V47" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W47">
         <v>0.044444</v>
@@ -5905,10 +5944,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>44289.29535901621</v>
@@ -5926,13 +5965,13 @@
         <v>1308</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K48">
         <v>123</v>
@@ -5968,7 +6007,7 @@
         <v>28.4</v>
       </c>
       <c r="V48" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W48">
         <v>-0.017222</v>
@@ -5997,10 +6036,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>44289.29605268518</v>
@@ -6018,13 +6057,13 @@
         <v>1368</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K49">
         <v>112</v>
@@ -6060,7 +6099,7 @@
         <v>29.23333333</v>
       </c>
       <c r="V49" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W49">
         <v>0.013889</v>
@@ -6089,10 +6128,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>44289.29616422454</v>
@@ -6110,13 +6149,13 @@
         <v>1380</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K50">
         <v>102</v>
@@ -6140,7 +6179,7 @@
         <v>29.6</v>
       </c>
       <c r="V50" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W50">
         <v>0.004074</v>
@@ -6169,10 +6208,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>44289.29674895833</v>
@@ -6190,13 +6229,13 @@
         <v>1428</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K51">
         <v>118</v>
@@ -6232,7 +6271,7 @@
         <v>28.75</v>
       </c>
       <c r="V51" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W51">
         <v>-0.014167</v>
@@ -6261,10 +6300,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>44289.29688769676</v>
@@ -6282,13 +6321,13 @@
         <v>1440</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K52">
         <v>133</v>
@@ -6312,7 +6351,7 @@
         <v>29.1</v>
       </c>
       <c r="V52" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W52">
         <v>0.005833</v>
@@ -6341,10 +6380,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>44289.29744302083</v>
@@ -6362,13 +6401,13 @@
         <v>1488</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K53">
         <v>112</v>
@@ -6404,7 +6443,7 @@
         <v>31.65</v>
       </c>
       <c r="V53" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W53">
         <v>0.0425</v>
@@ -6433,10 +6472,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>44289.29790137731</v>
@@ -6454,13 +6493,13 @@
         <v>1530</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K54">
         <v>104</v>
@@ -6484,7 +6523,7 @@
         <v>33.93333333</v>
       </c>
       <c r="V54" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W54">
         <v>0.02537</v>
@@ -6513,10 +6552,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>44289.2981371412</v>
@@ -6534,13 +6573,13 @@
         <v>1548</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K55">
         <v>110</v>
@@ -6576,7 +6615,7 @@
         <v>35.66666667</v>
       </c>
       <c r="V55" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W55">
         <v>0.028889</v>
@@ -6605,10 +6644,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>44289.29859505787</v>
@@ -6626,13 +6665,13 @@
         <v>1590</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K56">
         <v>93</v>
@@ -6656,7 +6695,7 @@
         <v>32.65</v>
       </c>
       <c r="V56" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W56">
         <v>-0.050278</v>
@@ -6685,10 +6724,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>44289.29883195602</v>
@@ -6706,13 +6745,13 @@
         <v>1608</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K57">
         <v>94</v>
@@ -6748,7 +6787,7 @@
         <v>33.08333333</v>
       </c>
       <c r="V57" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W57">
         <v>0.007222</v>
@@ -6777,10 +6816,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>44289.29894071759</v>
@@ -6798,13 +6837,13 @@
         <v>1620</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K58">
         <v>71</v>
@@ -6828,7 +6867,7 @@
         <v>34.23333333</v>
       </c>
       <c r="V58" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W58">
         <v>0.038333</v>
@@ -6857,10 +6896,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>44289.29928905093</v>
@@ -6878,13 +6917,13 @@
         <v>1650</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K59">
         <v>93</v>
@@ -6908,7 +6947,7 @@
         <v>32.26666667</v>
       </c>
       <c r="V59" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W59">
         <v>-0.065556</v>
@@ -6937,10 +6976,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>44289.29952543981</v>
@@ -6958,13 +6997,13 @@
         <v>1668</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K60">
         <v>95</v>
@@ -7000,7 +7039,7 @@
         <v>33.25</v>
       </c>
       <c r="V60" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W60">
         <v>0.016389</v>
@@ -7029,10 +7068,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>44289.29998225695</v>
@@ -7050,13 +7089,13 @@
         <v>1710</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K61">
         <v>94</v>
@@ -7080,7 +7119,7 @@
         <v>33.31666667</v>
       </c>
       <c r="V61" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W61">
         <v>0.001111</v>
@@ -7109,10 +7148,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>44289.30022049769</v>
@@ -7130,13 +7169,13 @@
         <v>1728</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K62">
         <v>103</v>
@@ -7172,7 +7211,7 @@
         <v>32.2</v>
       </c>
       <c r="V62" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W62">
         <v>-0.018611</v>
@@ -7201,10 +7240,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>44289.30032944444</v>
@@ -7222,13 +7261,13 @@
         <v>1740</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K63">
         <v>107</v>
@@ -7252,7 +7291,7 @@
         <v>32.56666667</v>
       </c>
       <c r="V63" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W63">
         <v>0.012222</v>
@@ -7281,10 +7320,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>44289.3006796412</v>
@@ -7302,13 +7341,13 @@
         <v>1770</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K64">
         <v>119</v>
@@ -7332,7 +7371,7 @@
         <v>32.06666667</v>
       </c>
       <c r="V64" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W64">
         <v>-0.016667</v>
@@ -7361,10 +7400,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>44289.30091864584</v>
@@ -7382,13 +7421,13 @@
         <v>1788</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K65">
         <v>88</v>
@@ -7424,7 +7463,7 @@
         <v>33.85</v>
       </c>
       <c r="V65" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="W65">
         <v>0.029722</v>
@@ -7453,10 +7492,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>44289.30160892361</v>
@@ -7474,13 +7513,13 @@
         <v>1848</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K66">
         <v>138</v>
@@ -7516,7 +7555,7 @@
         <v>31.85</v>
       </c>
       <c r="V66" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W66">
         <v>-0.033333</v>
@@ -7545,10 +7584,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>44289.30172013889</v>
@@ -7566,13 +7605,13 @@
         <v>1860</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K67">
         <v>125</v>
@@ -7596,7 +7635,7 @@
         <v>31.97777778</v>
       </c>
       <c r="V67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W67">
         <v>0.00142</v>
@@ -7625,10 +7664,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>44289.30230331019</v>
@@ -7646,13 +7685,13 @@
         <v>1908</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K68">
         <v>97</v>
@@ -7688,7 +7727,7 @@
         <v>23.66666667</v>
       </c>
       <c r="V68" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W68">
         <v>-0.138519</v>
@@ -7717,10 +7756,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>44289.3024141088</v>
@@ -7738,13 +7777,13 @@
         <v>1920</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K69">
         <v>101</v>
@@ -7768,7 +7807,7 @@
         <v>22.51666667</v>
       </c>
       <c r="V69" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W69">
         <v>-0.019167</v>
@@ -7797,10 +7836,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>44289.30299829861</v>
@@ -7818,13 +7857,13 @@
         <v>1968</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -7860,7 +7899,7 @@
         <v>18.35</v>
       </c>
       <c r="V70" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W70">
         <v>-0.06944400000000001</v>
@@ -7889,10 +7928,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>44289.30310839121</v>
@@ -7910,13 +7949,13 @@
         <v>1980</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K71">
         <v>109</v>
@@ -7940,7 +7979,7 @@
         <v>18.05</v>
       </c>
       <c r="V71" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W71">
         <v>-0.005</v>
@@ -7969,10 +8008,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>44289.30369325232</v>
@@ -7990,13 +8029,13 @@
         <v>2028</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K72">
         <v>103</v>
@@ -8032,7 +8071,7 @@
         <v>19.6</v>
       </c>
       <c r="V72" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W72">
         <v>0.025833</v>
@@ -8061,10 +8100,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2">
         <v>44289.30383386574</v>
@@ -8082,13 +8121,13 @@
         <v>2040</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K73">
         <v>148</v>
@@ -8112,7 +8151,7 @@
         <v>23.68333333</v>
       </c>
       <c r="V73" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W73">
         <v>0.06805600000000001</v>
@@ -8141,10 +8180,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>44289.30438799768</v>
@@ -8162,13 +8201,13 @@
         <v>2088</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K74">
         <v>108</v>
@@ -8204,7 +8243,7 @@
         <v>28.9</v>
       </c>
       <c r="V74" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W74">
         <v>0.08694399999999999</v>
@@ -8233,10 +8272,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>44289.30449833333</v>
@@ -8254,13 +8293,13 @@
         <v>2100</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K75">
         <v>65</v>
@@ -8284,7 +8323,7 @@
         <v>27.18333333</v>
       </c>
       <c r="V75" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W75">
         <v>-0.028611</v>
@@ -8313,10 +8352,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C76" s="2">
         <v>44289.30508075232</v>
@@ -8334,13 +8373,13 @@
         <v>2148</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K76">
         <v>63</v>
@@ -8376,7 +8415,7 @@
         <v>27.41666667</v>
       </c>
       <c r="V76" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W76">
         <v>0.003889</v>
@@ -8405,10 +8444,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>44289.30577674769</v>
@@ -8426,13 +8465,13 @@
         <v>2208</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K77">
         <v>95</v>
@@ -8468,7 +8507,7 @@
         <v>22.65</v>
       </c>
       <c r="V77" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W77">
         <v>-0.079444</v>
@@ -8497,10 +8536,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2">
         <v>44289.30588592593</v>
@@ -8518,13 +8557,13 @@
         <v>2220</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K78">
         <v>130</v>
@@ -8548,7 +8587,7 @@
         <v>24.225</v>
       </c>
       <c r="V78" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W78">
         <v>0.013125</v>
@@ -8577,10 +8616,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>44289.30647016204</v>
@@ -8598,13 +8637,13 @@
         <v>2268</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K79">
         <v>122</v>
@@ -8640,7 +8679,7 @@
         <v>24.11666667</v>
       </c>
       <c r="V79" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W79">
         <v>-0.001806</v>
@@ -8669,10 +8708,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>44289.30716491898</v>
@@ -8690,13 +8729,13 @@
         <v>2328</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K80">
         <v>63</v>
@@ -8732,7 +8771,7 @@
         <v>23.23333333</v>
       </c>
       <c r="V80" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W80">
         <v>-0.014722</v>
@@ -8761,10 +8800,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C81" s="2">
         <v>44289.30727484954</v>
@@ -8782,13 +8821,13 @@
         <v>2340</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K81">
         <v>97</v>
@@ -8812,7 +8851,7 @@
         <v>24.5</v>
       </c>
       <c r="V81" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W81">
         <v>0.010556</v>
@@ -8841,10 +8880,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2">
         <v>44289.30786054398</v>
@@ -8862,13 +8901,13 @@
         <v>2388</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K82">
         <v>96</v>
@@ -8904,7 +8943,7 @@
         <v>23.96666667</v>
       </c>
       <c r="V82" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W82">
         <v>-0.008888999999999999</v>
@@ -8933,10 +8972,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2">
         <v>44289.30797071759</v>
@@ -8954,13 +8993,13 @@
         <v>2400</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K83">
         <v>168</v>
@@ -8984,7 +9023,7 @@
         <v>26.3</v>
       </c>
       <c r="V83" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W83">
         <v>0.038889</v>
@@ -9013,10 +9052,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C84" s="2">
         <v>44289.30855472222</v>
@@ -9034,13 +9073,13 @@
         <v>2448</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K84">
         <v>115</v>
@@ -9076,7 +9115,7 @@
         <v>27.68333333</v>
       </c>
       <c r="V84" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W84">
         <v>0.023056</v>
@@ -9105,10 +9144,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C85" s="2">
         <v>44289.30866436342</v>
@@ -9126,13 +9165,13 @@
         <v>2460</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K85">
         <v>190</v>
@@ -9156,7 +9195,7 @@
         <v>23.95</v>
       </c>
       <c r="V85" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W85">
         <v>-0.062222</v>
@@ -9185,10 +9224,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2">
         <v>44289.30900952547</v>
@@ -9206,13 +9245,13 @@
         <v>2490</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K86">
         <v>205</v>
@@ -9236,7 +9275,7 @@
         <v>19.16666667</v>
       </c>
       <c r="V86" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W86">
         <v>-0.159444</v>
@@ -9265,10 +9304,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C87" s="2">
         <v>44289.30924861111</v>
@@ -9286,13 +9325,13 @@
         <v>2508</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K87">
         <v>117</v>
@@ -9328,7 +9367,7 @@
         <v>19.56666667</v>
       </c>
       <c r="V87" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W87">
         <v>0.006667</v>
@@ -9357,10 +9396,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2">
         <v>44289.30970675926</v>
@@ -9378,13 +9417,13 @@
         <v>2550</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K88">
         <v>187</v>
@@ -9408,7 +9447,7 @@
         <v>21.31666667</v>
       </c>
       <c r="V88" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W88">
         <v>0.029167</v>
@@ -9437,10 +9476,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2">
         <v>44289.30994333333</v>
@@ -9458,13 +9497,13 @@
         <v>2568</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K89">
         <v>118</v>
@@ -9500,7 +9539,7 @@
         <v>21.13333333</v>
       </c>
       <c r="V89" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W89">
         <v>-0.003056</v>
@@ -9529,10 +9568,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>44289.31005087963</v>
@@ -9550,13 +9589,13 @@
         <v>2580</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K90">
         <v>153</v>
@@ -9580,7 +9619,7 @@
         <v>20.46666667</v>
       </c>
       <c r="V90" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W90">
         <v>-0.022222</v>
@@ -9609,10 +9648,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C91" s="2">
         <v>44289.31039877314</v>
@@ -9630,13 +9669,13 @@
         <v>2610</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K91">
         <v>171</v>
@@ -9660,7 +9699,7 @@
         <v>22.2</v>
       </c>
       <c r="V91" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W91">
         <v>0.057778</v>
@@ -9689,10 +9728,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C92" s="2">
         <v>44289.31063765047</v>
@@ -9710,13 +9749,13 @@
         <v>2628</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K92">
         <v>150</v>
@@ -9752,7 +9791,7 @@
         <v>21.7</v>
       </c>
       <c r="V92" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W92">
         <v>-0.008333</v>
@@ -9781,10 +9820,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C93" s="2">
         <v>44289.31133126158</v>
@@ -9802,13 +9841,13 @@
         <v>2688</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K93">
         <v>134</v>
@@ -9844,7 +9883,7 @@
         <v>21.31666667</v>
       </c>
       <c r="V93" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W93">
         <v>-0.006389</v>
@@ -9873,10 +9912,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>44289.31144152777</v>
@@ -9894,13 +9933,13 @@
         <v>2700</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K94">
         <v>182</v>
@@ -9924,7 +9963,7 @@
         <v>20.96666667</v>
       </c>
       <c r="V94" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W94">
         <v>-0.003889</v>
@@ -9953,10 +9992,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C95" s="2">
         <v>44289.3117890162</v>
@@ -9974,13 +10013,13 @@
         <v>2730</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K95">
         <v>170</v>
@@ -10004,7 +10043,7 @@
         <v>19.8</v>
       </c>
       <c r="V95" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W95">
         <v>-0.038889</v>
@@ -10033,10 +10072,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C96" s="2">
         <v>44289.31202645833</v>
@@ -10054,13 +10093,13 @@
         <v>2748</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K96">
         <v>112</v>
@@ -10096,7 +10135,7 @@
         <v>18.98333333</v>
       </c>
       <c r="V96" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W96">
         <v>-0.013611</v>
@@ -10125,10 +10164,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C97" s="2">
         <v>44289.31248106482</v>
@@ -10146,13 +10185,13 @@
         <v>2790</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K97">
         <v>143</v>
@@ -10176,7 +10215,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V97" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W97">
         <v>-0.015833</v>
@@ -10205,10 +10244,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2">
         <v>44289.31272116898</v>
@@ -10226,13 +10265,13 @@
         <v>2808</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K98">
         <v>98</v>
@@ -10268,7 +10307,7 @@
         <v>19.3</v>
       </c>
       <c r="V98" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W98">
         <v>0.021111</v>
@@ -10297,10 +10336,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C99" s="2">
         <v>44289.31283771991</v>
@@ -10318,13 +10357,13 @@
         <v>2820</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K99">
         <v>121</v>
@@ -10348,7 +10387,7 @@
         <v>21.33333333</v>
       </c>
       <c r="V99" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W99">
         <v>0.067778</v>
@@ -10377,10 +10416,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C100" s="2">
         <v>44289.3131762037</v>
@@ -10398,13 +10437,13 @@
         <v>2850</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K100">
         <v>136</v>
@@ -10428,7 +10467,7 @@
         <v>29.86666667</v>
       </c>
       <c r="V100" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W100">
         <v>0.284444</v>
@@ -10457,10 +10496,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C101" s="2">
         <v>44289.31341512731</v>
@@ -10478,13 +10517,13 @@
         <v>2868</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K101">
         <v>120</v>
@@ -10520,7 +10559,7 @@
         <v>27.78333333</v>
       </c>
       <c r="V101" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W101">
         <v>-0.034722</v>
@@ -10549,10 +10588,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C102" s="2">
         <v>44289.31352519676</v>
@@ -10570,13 +10609,13 @@
         <v>2880</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K102">
         <v>134</v>
@@ -10600,7 +10639,7 @@
         <v>27.03333333</v>
       </c>
       <c r="V102" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W102">
         <v>-0.025</v>
@@ -10629,10 +10668,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C103" s="2">
         <v>44289.31387267361</v>
@@ -10650,13 +10689,13 @@
         <v>2910</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K103">
         <v>114</v>
@@ -10680,7 +10719,7 @@
         <v>26.33333333</v>
       </c>
       <c r="V103" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W103">
         <v>-0.023333</v>
@@ -10709,10 +10748,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2">
         <v>44289.31411021991</v>
@@ -10730,13 +10769,13 @@
         <v>2928</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K104">
         <v>108</v>
@@ -10772,7 +10811,7 @@
         <v>25.11666667</v>
       </c>
       <c r="V104" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W104">
         <v>-0.020278</v>
@@ -10801,10 +10840,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2">
         <v>44289.31422042824</v>
@@ -10822,13 +10861,13 @@
         <v>2940</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K105">
         <v>111</v>
@@ -10852,7 +10891,7 @@
         <v>23.3</v>
       </c>
       <c r="V105" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W105">
         <v>-0.060556</v>
@@ -10881,10 +10920,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C106" s="2">
         <v>44289.31456719907</v>
@@ -10902,13 +10941,13 @@
         <v>2970</v>
       </c>
       <c r="H106" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J106" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K106">
         <v>96</v>
@@ -10932,7 +10971,7 @@
         <v>20.8</v>
       </c>
       <c r="V106" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W106">
         <v>-0.083333</v>
@@ -10961,10 +11000,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C107" s="2">
         <v>44289.31480430556</v>
@@ -10982,13 +11021,13 @@
         <v>2988</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J107" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K107">
         <v>110</v>
@@ -11024,7 +11063,7 @@
         <v>20.71666667</v>
       </c>
       <c r="V107" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W107">
         <v>-0.001389</v>
@@ -11053,10 +11092,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C108" s="2">
         <v>44289.31549835648</v>
@@ -11074,13 +11113,13 @@
         <v>3048</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J108" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K108">
         <v>116</v>
@@ -11116,7 +11155,7 @@
         <v>16.75</v>
       </c>
       <c r="V108" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W108">
         <v>-0.066111</v>
@@ -11145,10 +11184,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C109" s="2">
         <v>44289.31561175926</v>
@@ -11166,13 +11205,13 @@
         <v>3060</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J109" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K109">
         <v>92</v>
@@ -11196,7 +11235,7 @@
         <v>17.56666667</v>
       </c>
       <c r="V109" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W109">
         <v>0.009074</v>
@@ -11225,10 +11264,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2">
         <v>44289.31595774306</v>
@@ -11246,13 +11285,13 @@
         <v>3090</v>
       </c>
       <c r="H110" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J110" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K110">
         <v>83</v>
@@ -11276,7 +11315,7 @@
         <v>18.6</v>
       </c>
       <c r="V110" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W110">
         <v>0.034444</v>
@@ -11305,10 +11344,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C111" s="2">
         <v>44289.31619278935</v>
@@ -11326,13 +11365,13 @@
         <v>3108</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J111" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K111">
         <v>90</v>
@@ -11368,7 +11407,7 @@
         <v>19.41666667</v>
       </c>
       <c r="V111" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W111">
         <v>0.013611</v>
@@ -11397,10 +11436,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C112" s="2">
         <v>44289.31630166667</v>
@@ -11418,13 +11457,13 @@
         <v>3120</v>
       </c>
       <c r="H112" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J112" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K112">
         <v>70</v>
@@ -11448,7 +11487,7 @@
         <v>21.23333333</v>
       </c>
       <c r="V112" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W112">
         <v>0.060556</v>
@@ -11477,10 +11516,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C113" s="2">
         <v>44289.3168882176</v>
@@ -11498,13 +11537,13 @@
         <v>3168</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J113" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K113">
         <v>98</v>
@@ -11540,7 +11579,7 @@
         <v>23.76666667</v>
       </c>
       <c r="V113" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W113">
         <v>0.042222</v>
@@ -11569,10 +11608,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C114" s="2">
         <v>44289.31699675926</v>
@@ -11590,13 +11629,13 @@
         <v>3180</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J114" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K114">
         <v>88</v>
@@ -11620,7 +11659,7 @@
         <v>24.65</v>
       </c>
       <c r="V114" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W114">
         <v>0.014722</v>
@@ -11649,10 +11688,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C115" s="2">
         <v>44289.31734570602</v>
@@ -11670,13 +11709,13 @@
         <v>3210</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J115" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K115">
         <v>103</v>
@@ -11700,7 +11739,7 @@
         <v>26.16666667</v>
       </c>
       <c r="V115" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W115">
         <v>0.050556</v>
@@ -11729,10 +11768,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C116" s="2">
         <v>44289.3175825463</v>
@@ -11750,13 +11789,13 @@
         <v>3228</v>
       </c>
       <c r="H116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K116">
         <v>97</v>
@@ -11792,7 +11831,7 @@
         <v>26.41666667</v>
       </c>
       <c r="V116" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W116">
         <v>0.004167</v>
@@ -11821,10 +11860,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C117" s="2">
         <v>44289.31803774305</v>
@@ -11842,13 +11881,13 @@
         <v>3270</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J117" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K117">
         <v>86</v>
@@ -11872,7 +11911,7 @@
         <v>24.71666667</v>
       </c>
       <c r="V117" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W117">
         <v>-0.028333</v>
@@ -11901,10 +11940,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C118" s="2">
         <v>44289.31827712963</v>
@@ -11922,13 +11961,13 @@
         <v>3288</v>
       </c>
       <c r="H118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J118" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K118">
         <v>94</v>
@@ -11964,7 +12003,7 @@
         <v>23.85</v>
       </c>
       <c r="V118" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W118">
         <v>-0.014444</v>
@@ -11993,10 +12032,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C119" s="2">
         <v>44289.31838730324</v>
@@ -12014,13 +12053,13 @@
         <v>3300</v>
       </c>
       <c r="H119" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I119" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J119" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K119">
         <v>99</v>
@@ -12044,7 +12083,7 @@
         <v>23.5</v>
       </c>
       <c r="V119" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W119">
         <v>-0.011667</v>
@@ -12073,10 +12112,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2">
         <v>44289.31873393519</v>
@@ -12094,13 +12133,13 @@
         <v>3330</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J120" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K120">
         <v>114</v>
@@ -12124,7 +12163,7 @@
         <v>22.43333333</v>
       </c>
       <c r="V120" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W120">
         <v>-0.035556</v>
@@ -12153,10 +12192,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C121" s="2">
         <v>44289.31897037037</v>
@@ -12174,13 +12213,13 @@
         <v>3348</v>
       </c>
       <c r="H121" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J121" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K121">
         <v>103</v>
@@ -12216,7 +12255,7 @@
         <v>22.75</v>
       </c>
       <c r="V121" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W121">
         <v>0.005278</v>
@@ -12245,10 +12284,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C122" s="2">
         <v>44289.31942747685</v>
@@ -12266,13 +12305,13 @@
         <v>3390</v>
       </c>
       <c r="H122" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J122" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K122">
         <v>110</v>
@@ -12296,7 +12335,7 @@
         <v>21.65</v>
       </c>
       <c r="V122" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W122">
         <v>-0.018333</v>
@@ -12325,10 +12364,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C123" s="2">
         <v>44289.31966621528</v>
@@ -12346,13 +12385,13 @@
         <v>3408</v>
       </c>
       <c r="H123" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J123" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K123">
         <v>99</v>
@@ -12388,7 +12427,7 @@
         <v>21.28333333</v>
       </c>
       <c r="V123" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W123">
         <v>-0.006111</v>
@@ -12417,10 +12456,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C124" s="2">
         <v>44289.31977466435</v>
@@ -12438,13 +12477,13 @@
         <v>3420</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K124">
         <v>99</v>
@@ -12468,7 +12507,7 @@
         <v>20.56666667</v>
       </c>
       <c r="V124" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W124">
         <v>-0.023889</v>
@@ -12497,10 +12536,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2">
         <v>44289.32012114584</v>
@@ -12518,13 +12557,13 @@
         <v>3450</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I125" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J125" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K125">
         <v>113</v>
@@ -12548,7 +12587,7 @@
         <v>19.03333333</v>
       </c>
       <c r="V125" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W125">
         <v>-0.051111</v>
@@ -12577,10 +12616,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C126" s="2">
         <v>44289.32035984954</v>
@@ -12598,13 +12637,13 @@
         <v>3468</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J126" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K126">
         <v>101</v>
@@ -12640,7 +12679,7 @@
         <v>19.18333333</v>
       </c>
       <c r="V126" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W126">
         <v>0.0025</v>
@@ -12669,10 +12708,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C127" s="2">
         <v>44289.32081715278</v>
@@ -12690,13 +12729,13 @@
         <v>3510</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I127" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K127">
         <v>97</v>
@@ -12720,7 +12759,7 @@
         <v>20.28333333</v>
       </c>
       <c r="V127" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W127">
         <v>0.018333</v>
@@ -12749,10 +12788,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C128" s="2">
         <v>44289.32105385417</v>
@@ -12770,13 +12809,13 @@
         <v>3528</v>
       </c>
       <c r="H128" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J128" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K128">
         <v>101</v>
@@ -12812,7 +12851,7 @@
         <v>21.45</v>
       </c>
       <c r="V128" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W128">
         <v>0.019444</v>
@@ -12841,10 +12880,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C129" s="2">
         <v>44289.32116510416</v>
@@ -12862,13 +12901,13 @@
         <v>3540</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J129" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K129">
         <v>83</v>
@@ -12892,7 +12931,7 @@
         <v>22.76666667</v>
       </c>
       <c r="V129" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W129">
         <v>0.043889</v>
@@ -12921,10 +12960,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C130" s="2">
         <v>44289.32151105324</v>
@@ -12942,13 +12981,13 @@
         <v>3570</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J130" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K130">
         <v>114</v>
@@ -12972,7 +13011,7 @@
         <v>24.5</v>
       </c>
       <c r="V130" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W130">
         <v>0.057778</v>
@@ -13001,10 +13040,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C131" s="2">
         <v>44289.32174909722</v>
@@ -13022,13 +13061,13 @@
         <v>3588</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K131">
         <v>101</v>
@@ -13064,7 +13103,7 @@
         <v>23.85</v>
       </c>
       <c r="V131" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W131">
         <v>-0.010833</v>
@@ -13093,10 +13132,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C132" s="2">
         <v>44289.32185712963</v>
@@ -13114,13 +13153,13 @@
         <v>3600</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I132" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J132" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K132">
         <v>108</v>
@@ -13144,7 +13183,7 @@
         <v>23.4</v>
       </c>
       <c r="V132" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W132">
         <v>-0.015</v>
@@ -13173,10 +13212,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C133" s="2">
         <v>44289.32244366898</v>
@@ -13194,13 +13233,13 @@
         <v>3648</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J133" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K133">
         <v>94</v>
@@ -13236,7 +13275,7 @@
         <v>21.81666667</v>
       </c>
       <c r="V133" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W133">
         <v>-0.026389</v>
@@ -13265,10 +13304,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C134" s="2">
         <v>44289.32255368055</v>
@@ -13286,13 +13325,13 @@
         <v>3660</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I134" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J134" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K134">
         <v>97</v>
@@ -13316,7 +13355,7 @@
         <v>21.21666667</v>
       </c>
       <c r="V134" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W134">
         <v>-0.01</v>
@@ -13345,10 +13384,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C135" s="2">
         <v>44289.32289793981</v>
@@ -13366,13 +13405,13 @@
         <v>3690</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I135" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J135" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K135">
         <v>99</v>
@@ -13396,7 +13435,7 @@
         <v>18.83333333</v>
       </c>
       <c r="V135" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W135">
         <v>-0.079444</v>
@@ -13425,10 +13464,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C136" s="2">
         <v>44289.32313953704</v>
@@ -13446,13 +13485,13 @@
         <v>3708</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I136" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J136" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K136">
         <v>97</v>
@@ -13488,7 +13527,7 @@
         <v>18.8</v>
       </c>
       <c r="V136" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="W136">
         <v>-0.000556</v>
@@ -13527,102 +13566,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>44289.323943125</v>
@@ -13640,13 +13679,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K2">
         <v>88</v>
@@ -13670,7 +13709,7 @@
         <v>-20.78888889</v>
       </c>
       <c r="V2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="X2">
         <v>-20.788889</v>
@@ -13681,10 +13720,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>44289.32420905092</v>
@@ -13702,13 +13741,13 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="K3">
         <v>108</v>
@@ -13744,7 +13783,7 @@
         <v>-58.6</v>
       </c>
       <c r="V3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W3">
         <v>-0.420123</v>
@@ -13767,10 +13806,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>44289.32428706018</v>
@@ -13788,13 +13827,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I4" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J4" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K4">
         <v>103</v>
@@ -13818,7 +13857,7 @@
         <v>-156.3</v>
       </c>
       <c r="V4" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W4">
         <v>-3.256667</v>
@@ -13847,10 +13886,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>44289.32452712963</v>
@@ -13868,13 +13907,13 @@
         <v>48</v>
       </c>
       <c r="H5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J5" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K5">
         <v>106</v>
@@ -13910,7 +13949,7 @@
         <v>-145.36666667</v>
       </c>
       <c r="V5" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W5">
         <v>0.364444</v>
@@ -13939,10 +13978,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>44289.32463643519</v>
@@ -13960,13 +13999,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I6" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K6">
         <v>67</v>
@@ -13990,7 +14029,7 @@
         <v>-139.53333333</v>
       </c>
       <c r="V6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W6">
         <v>0.194444</v>
@@ -14019,10 +14058,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>44289.32485122685</v>
@@ -14040,13 +14079,13 @@
         <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="K7">
         <v>94</v>
@@ -14082,7 +14121,7 @@
         <v>-130.16666667</v>
       </c>
       <c r="V7" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W7">
         <v>0.312222</v>
@@ -14111,10 +14150,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>44289.32522667824</v>
@@ -14132,13 +14171,13 @@
         <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I8" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="K8">
         <v>118</v>
@@ -14174,7 +14213,7 @@
         <v>-119.26666667</v>
       </c>
       <c r="V8" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W8">
         <v>0.363333</v>
@@ -14203,10 +14242,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>44289.32533144676</v>
@@ -14224,13 +14263,13 @@
         <v>120</v>
       </c>
       <c r="H9" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I9" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J9" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="K9">
         <v>110</v>
@@ -14254,7 +14293,7 @@
         <v>-121.2</v>
       </c>
       <c r="V9" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W9">
         <v>-0.032222</v>
@@ -14283,10 +14322,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>44289.32567565973</v>
@@ -14304,13 +14343,13 @@
         <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I10" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J10" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K10">
         <v>103</v>
@@ -14334,7 +14373,7 @@
         <v>-109.56666667</v>
       </c>
       <c r="V10" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W10">
         <v>0.387778</v>
@@ -14363,10 +14402,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>44289.32591612269</v>
@@ -14384,13 +14423,13 @@
         <v>168</v>
       </c>
       <c r="H11" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I11" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K11">
         <v>107</v>
@@ -14426,7 +14465,7 @@
         <v>-107.21666667</v>
       </c>
       <c r="V11" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W11">
         <v>0.039167</v>
@@ -14455,10 +14494,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>44289.32637018518</v>
@@ -14476,13 +14515,13 @@
         <v>210</v>
       </c>
       <c r="H12" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I12" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J12" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K12">
         <v>180</v>
@@ -14506,7 +14545,7 @@
         <v>-92.81666667</v>
       </c>
       <c r="V12" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W12">
         <v>0.24</v>
@@ -14535,10 +14574,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>44289.32664009259</v>
@@ -14556,13 +14595,13 @@
         <v>228</v>
       </c>
       <c r="H13" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I13" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J13" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K13">
         <v>118</v>
@@ -14598,7 +14637,7 @@
         <v>-89.40000000000001</v>
       </c>
       <c r="V13" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W13">
         <v>0.056944</v>
@@ -14627,10 +14666,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>44289.32672039352</v>
@@ -14648,13 +14687,13 @@
         <v>240</v>
       </c>
       <c r="H14" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J14" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K14">
         <v>61</v>
@@ -14678,7 +14717,7 @@
         <v>-88.26666667000001</v>
       </c>
       <c r="V14" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W14">
         <v>0.037778</v>
@@ -14707,10 +14746,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>44289.32699259259</v>
@@ -14728,13 +14767,13 @@
         <v>258</v>
       </c>
       <c r="H15" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I15" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J15" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -14770,7 +14809,7 @@
         <v>-85.66666667</v>
       </c>
       <c r="V15" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W15">
         <v>0.08666699999999999</v>
@@ -14799,10 +14838,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>44289.32706525463</v>
@@ -14820,13 +14859,13 @@
         <v>270</v>
       </c>
       <c r="H16" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I16" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J16" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -14850,7 +14889,7 @@
         <v>-83.56666667</v>
       </c>
       <c r="V16" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W16">
         <v>0.07000000000000001</v>
@@ -14879,10 +14918,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>44289.32730726852</v>
@@ -14900,13 +14939,13 @@
         <v>288</v>
       </c>
       <c r="H17" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I17" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J17" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K17">
         <v>67</v>
@@ -14942,7 +14981,7 @@
         <v>-81.06666667</v>
       </c>
       <c r="V17" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W17">
         <v>0.083333</v>
@@ -14971,10 +15010,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>44289.3274146412</v>
@@ -14992,13 +15031,13 @@
         <v>300</v>
       </c>
       <c r="H18" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I18" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J18" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K18">
         <v>117</v>
@@ -15022,7 +15061,7 @@
         <v>-79.5</v>
       </c>
       <c r="V18" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W18">
         <v>0.052222</v>
@@ -15051,10 +15090,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>44289.32800023148</v>
@@ -15072,13 +15111,13 @@
         <v>348</v>
       </c>
       <c r="H19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I19" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J19" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K19">
         <v>132</v>
@@ -15114,7 +15153,7 @@
         <v>-73.84999999999999</v>
       </c>
       <c r="V19" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W19">
         <v>0.094167</v>
@@ -15143,10 +15182,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>44289.32810972222</v>
@@ -15164,13 +15203,13 @@
         <v>360</v>
       </c>
       <c r="H20" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I20" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J20" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K20">
         <v>125</v>
@@ -15194,7 +15233,7 @@
         <v>-71.96666667</v>
       </c>
       <c r="V20" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W20">
         <v>0.031389</v>
@@ -15223,10 +15262,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>44289.32845418982</v>
@@ -15244,13 +15283,13 @@
         <v>390</v>
       </c>
       <c r="H21" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I21" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J21" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K21">
         <v>102</v>
@@ -15274,7 +15313,7 @@
         <v>-65.73333332999999</v>
       </c>
       <c r="V21" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W21">
         <v>0.207778</v>
@@ -15303,10 +15342,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>44289.32869456019</v>
@@ -15324,13 +15363,13 @@
         <v>408</v>
       </c>
       <c r="H22" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I22" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J22" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K22">
         <v>107</v>
@@ -15366,7 +15405,7 @@
         <v>-64.41666667</v>
       </c>
       <c r="V22" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W22">
         <v>0.021944</v>
@@ -15395,10 +15434,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>44289.32938958333</v>
@@ -15416,13 +15455,13 @@
         <v>468</v>
       </c>
       <c r="H23" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I23" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J23" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K23">
         <v>114</v>
@@ -15458,7 +15497,7 @@
         <v>-57.56666667</v>
       </c>
       <c r="V23" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W23">
         <v>0.114167</v>
@@ -15487,10 +15526,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>44289.32949666667</v>
@@ -15508,13 +15547,13 @@
         <v>480</v>
       </c>
       <c r="H24" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I24" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J24" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K24">
         <v>102</v>
@@ -15538,7 +15577,7 @@
         <v>-58.12222222</v>
       </c>
       <c r="V24" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W24">
         <v>-0.006173</v>
@@ -15567,10 +15606,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>44289.32984449074</v>
@@ -15588,13 +15627,13 @@
         <v>510</v>
       </c>
       <c r="H25" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I25" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J25" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K25">
         <v>114</v>
@@ -15618,7 +15657,7 @@
         <v>-54.23333333</v>
       </c>
       <c r="V25" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W25">
         <v>0.12963</v>
@@ -15647,10 +15686,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>44289.33008274306</v>
@@ -15668,13 +15707,13 @@
         <v>528</v>
       </c>
       <c r="H26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I26" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J26" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K26">
         <v>98</v>
@@ -15710,7 +15749,7 @@
         <v>-54.06666667</v>
       </c>
       <c r="V26" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W26">
         <v>0.002778</v>
@@ -15739,10 +15778,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>44289.33053688658</v>
@@ -15760,13 +15799,13 @@
         <v>570</v>
       </c>
       <c r="H27" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I27" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J27" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K27">
         <v>95</v>
@@ -15790,7 +15829,7 @@
         <v>-51.4</v>
       </c>
       <c r="V27" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W27">
         <v>0.044444</v>
@@ -15819,10 +15858,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>44289.33077887732</v>
@@ -15840,13 +15879,13 @@
         <v>588</v>
       </c>
       <c r="H28" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I28" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J28" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K28">
         <v>99</v>
@@ -15882,7 +15921,7 @@
         <v>-49.51666667</v>
       </c>
       <c r="V28" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W28">
         <v>0.031389</v>
@@ -15911,10 +15950,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>44289.33088658565</v>
@@ -15932,13 +15971,13 @@
         <v>600</v>
       </c>
       <c r="H29" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I29" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J29" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K29">
         <v>83</v>
@@ -15962,7 +16001,7 @@
         <v>-49</v>
       </c>
       <c r="V29" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W29">
         <v>0.017222</v>
@@ -15991,10 +16030,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>44289.33147219908</v>
@@ -16012,13 +16051,13 @@
         <v>648</v>
       </c>
       <c r="H30" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I30" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J30" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -16054,7 +16093,7 @@
         <v>-45.78333333</v>
       </c>
       <c r="V30" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W30">
         <v>0.053611</v>
@@ -16083,10 +16122,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>44289.3321668287</v>
@@ -16104,13 +16143,13 @@
         <v>708</v>
       </c>
       <c r="H31" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I31" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J31" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K31">
         <v>130</v>
@@ -16146,7 +16185,7 @@
         <v>-44.16666667</v>
       </c>
       <c r="V31" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W31">
         <v>0.026944</v>
@@ -16175,10 +16214,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>44289.33286096065</v>
@@ -16196,13 +16235,13 @@
         <v>768</v>
       </c>
       <c r="H32" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I32" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J32" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K32">
         <v>147</v>
@@ -16238,7 +16277,7 @@
         <v>-40.38333333</v>
       </c>
       <c r="V32" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W32">
         <v>0.063056</v>
@@ -16267,10 +16306,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>44289.33300252315</v>
@@ -16288,13 +16327,13 @@
         <v>780</v>
       </c>
       <c r="H33" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I33" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J33" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K33">
         <v>112</v>
@@ -16318,7 +16357,7 @@
         <v>-42.63888889</v>
       </c>
       <c r="V33" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W33">
         <v>-0.012531</v>
@@ -16347,10 +16386,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>44289.33355666666</v>
@@ -16368,13 +16407,13 @@
         <v>828</v>
       </c>
       <c r="H34" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I34" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J34" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K34">
         <v>124</v>
@@ -16410,7 +16449,7 @@
         <v>-38.73333333</v>
       </c>
       <c r="V34" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W34">
         <v>0.065093</v>
@@ -16439,10 +16478,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
         <v>44289.33366600695</v>
@@ -16460,13 +16499,13 @@
         <v>840</v>
       </c>
       <c r="H35" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J35" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K35">
         <v>143</v>
@@ -16490,7 +16529,7 @@
         <v>-38.71666667</v>
       </c>
       <c r="V35" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W35">
         <v>0.000278</v>
@@ -16519,10 +16558,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>44289.334250625</v>
@@ -16540,13 +16579,13 @@
         <v>888</v>
       </c>
       <c r="H36" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I36" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J36" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K36">
         <v>146</v>
@@ -16582,7 +16621,7 @@
         <v>-37.5</v>
       </c>
       <c r="V36" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W36">
         <v>0.020278</v>
@@ -16611,10 +16650,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>44289.33438798611</v>
@@ -16632,13 +16671,13 @@
         <v>900</v>
       </c>
       <c r="H37" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I37" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J37" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K37">
         <v>119</v>
@@ -16662,7 +16701,7 @@
         <v>-36.98333333</v>
       </c>
       <c r="V37" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W37">
         <v>0.008611000000000001</v>
@@ -16691,10 +16730,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>44289.33494449074</v>
@@ -16712,13 +16751,13 @@
         <v>948</v>
       </c>
       <c r="H38" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I38" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J38" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K38">
         <v>134</v>
@@ -16754,7 +16793,7 @@
         <v>-36.06666667</v>
       </c>
       <c r="V38" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W38">
         <v>0.015278</v>
@@ -16783,10 +16822,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>44289.33563971065</v>
@@ -16804,13 +16843,13 @@
         <v>1008</v>
       </c>
       <c r="H39" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J39" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -16846,7 +16885,7 @@
         <v>-35.01666667</v>
       </c>
       <c r="V39" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W39">
         <v>0.0175</v>
@@ -16875,10 +16914,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>44289.33574947916</v>
@@ -16896,13 +16935,13 @@
         <v>1020</v>
       </c>
       <c r="H40" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I40" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J40" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K40">
         <v>63</v>
@@ -16926,7 +16965,7 @@
         <v>-35.35</v>
       </c>
       <c r="V40" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W40">
         <v>-0.002778</v>
@@ -16955,10 +16994,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>44289.33609668982</v>
@@ -16976,13 +17015,13 @@
         <v>1050</v>
       </c>
       <c r="H41" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I41" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J41" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K41">
         <v>93</v>
@@ -17006,7 +17045,7 @@
         <v>-32.83333333</v>
       </c>
       <c r="V41" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W41">
         <v>0.08388900000000001</v>
@@ -17035,10 +17074,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>44289.33633015047</v>
@@ -17056,13 +17095,13 @@
         <v>1068</v>
       </c>
       <c r="H42" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I42" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J42" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K42">
         <v>116</v>
@@ -17098,7 +17137,7 @@
         <v>-32.96666667</v>
       </c>
       <c r="V42" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W42">
         <v>-0.002222</v>
@@ -17127,10 +17166,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>44289.33643967593</v>
@@ -17148,13 +17187,13 @@
         <v>1080</v>
       </c>
       <c r="H43" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I43" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J43" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K43">
         <v>75</v>
@@ -17178,7 +17217,7 @@
         <v>-32.36666667</v>
       </c>
       <c r="V43" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W43">
         <v>0.02</v>
@@ -17207,10 +17246,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>44289.33702545139</v>
@@ -17228,13 +17267,13 @@
         <v>1128</v>
       </c>
       <c r="H44" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I44" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J44" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K44">
         <v>135</v>
@@ -17270,7 +17309,7 @@
         <v>-31.73333333</v>
       </c>
       <c r="V44" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W44">
         <v>0.010556</v>
@@ -17299,10 +17338,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>44289.33748606482</v>
@@ -17320,13 +17359,13 @@
         <v>1170</v>
       </c>
       <c r="H45" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I45" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J45" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K45">
         <v>71</v>
@@ -17350,7 +17389,7 @@
         <v>-30.87777778</v>
       </c>
       <c r="V45" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W45">
         <v>0.009506000000000001</v>
@@ -17379,10 +17418,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>44289.33771907407</v>
@@ -17400,13 +17439,13 @@
         <v>1188</v>
       </c>
       <c r="H46" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I46" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J46" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K46">
         <v>133</v>
@@ -17442,7 +17481,7 @@
         <v>-29.98333333</v>
       </c>
       <c r="V46" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W46">
         <v>0.014907</v>
@@ -17471,10 +17510,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>44289.33817644676</v>
@@ -17492,13 +17531,13 @@
         <v>1230</v>
       </c>
       <c r="H47" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I47" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J47" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K47">
         <v>145</v>
@@ -17522,7 +17561,7 @@
         <v>-28.93333333</v>
       </c>
       <c r="V47" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W47">
         <v>0.0175</v>
@@ -17551,10 +17590,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>44289.33841356482</v>
@@ -17572,13 +17611,13 @@
         <v>1248</v>
       </c>
       <c r="H48" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I48" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J48" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K48">
         <v>131</v>
@@ -17614,7 +17653,7 @@
         <v>-28.7</v>
       </c>
       <c r="V48" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W48">
         <v>0.003889</v>
@@ -17643,10 +17682,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>44289.33887225694</v>
@@ -17664,13 +17703,13 @@
         <v>1290</v>
       </c>
       <c r="H49" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I49" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J49" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K49">
         <v>73</v>
@@ -17694,7 +17733,7 @@
         <v>-29.75</v>
       </c>
       <c r="V49" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W49">
         <v>-0.0175</v>
@@ -17723,10 +17762,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <v>44289.33911373842</v>
@@ -17744,13 +17783,13 @@
         <v>1308</v>
       </c>
       <c r="H50" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I50" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J50" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K50">
         <v>134</v>
@@ -17786,7 +17825,7 @@
         <v>-29.83333333</v>
       </c>
       <c r="V50" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W50">
         <v>-0.001389</v>
@@ -17815,10 +17854,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>44289.33921880787</v>
@@ -17836,13 +17875,13 @@
         <v>1320</v>
       </c>
       <c r="H51" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I51" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J51" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K51">
         <v>190</v>
@@ -17866,7 +17905,7 @@
         <v>-29.53333333</v>
       </c>
       <c r="V51" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W51">
         <v>0.01</v>
@@ -17895,10 +17934,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>44289.33956538195</v>
@@ -17916,13 +17955,13 @@
         <v>1350</v>
       </c>
       <c r="H52" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I52" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J52" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K52">
         <v>139</v>
@@ -17946,7 +17985,7 @@
         <v>-26.8</v>
       </c>
       <c r="V52" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W52">
         <v>0.091111</v>
@@ -17975,10 +18014,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>44289.33994267361</v>
@@ -17996,13 +18035,13 @@
         <v>1380</v>
       </c>
       <c r="H53" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I53" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J53" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K53">
         <v>74</v>
@@ -18026,7 +18065,7 @@
         <v>-26.9</v>
       </c>
       <c r="V53" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W53">
         <v>-0.003333</v>
@@ -18055,10 +18094,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>44289.34026041667</v>
@@ -18076,13 +18115,13 @@
         <v>1410</v>
       </c>
       <c r="H54" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I54" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J54" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K54">
         <v>137</v>
@@ -18106,7 +18145,7 @@
         <v>-27.33333333</v>
       </c>
       <c r="V54" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W54">
         <v>-0.014444</v>
@@ -18135,10 +18174,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>44289.3404971875</v>
@@ -18156,13 +18195,13 @@
         <v>1428</v>
       </c>
       <c r="H55" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I55" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J55" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K55">
         <v>87</v>
@@ -18198,7 +18237,7 @@
         <v>-27.31666667</v>
       </c>
       <c r="V55" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W55">
         <v>0.000139</v>
@@ -18227,10 +18266,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>44289.34095932871</v>
@@ -18248,13 +18287,13 @@
         <v>1470</v>
       </c>
       <c r="H56" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I56" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J56" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K56">
         <v>102</v>
@@ -18278,7 +18317,7 @@
         <v>-27.61666667</v>
       </c>
       <c r="V56" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W56">
         <v>-0.005</v>
@@ -18307,10 +18346,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>44289.34119378472</v>
@@ -18328,13 +18367,13 @@
         <v>1488</v>
       </c>
       <c r="H57" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I57" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J57" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K57">
         <v>109</v>
@@ -18370,7 +18409,7 @@
         <v>-27.26666667</v>
       </c>
       <c r="V57" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W57">
         <v>0.005833</v>
@@ -18399,10 +18438,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>44289.34165127315</v>
@@ -18420,13 +18459,13 @@
         <v>1530</v>
       </c>
       <c r="H58" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I58" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J58" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K58">
         <v>91</v>
@@ -18450,7 +18489,7 @@
         <v>-26.46666667</v>
       </c>
       <c r="V58" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W58">
         <v>0.013333</v>
@@ -18479,10 +18518,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>44289.34188908565</v>
@@ -18500,13 +18539,13 @@
         <v>1548</v>
       </c>
       <c r="H59" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I59" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J59" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K59">
         <v>122</v>
@@ -18542,7 +18581,7 @@
         <v>-26.45</v>
       </c>
       <c r="V59" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W59">
         <v>0.000278</v>
@@ -18571,10 +18610,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>44289.34199621528</v>
@@ -18592,13 +18631,13 @@
         <v>1560</v>
       </c>
       <c r="H60" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I60" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J60" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K60">
         <v>148</v>
@@ -18622,7 +18661,7 @@
         <v>-26.36666667</v>
       </c>
       <c r="V60" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W60">
         <v>0.002778</v>
@@ -18651,10 +18690,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>44289.34234319445</v>
@@ -18672,13 +18711,13 @@
         <v>1590</v>
       </c>
       <c r="H61" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I61" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J61" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K61">
         <v>81</v>
@@ -18702,7 +18741,7 @@
         <v>-24.5</v>
       </c>
       <c r="V61" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W61">
         <v>0.062222</v>
@@ -18731,10 +18770,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>44289.34258387732</v>
@@ -18752,13 +18791,13 @@
         <v>1608</v>
       </c>
       <c r="H62" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I62" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J62" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K62">
         <v>90</v>
@@ -18794,7 +18833,7 @@
         <v>-24.96666667</v>
       </c>
       <c r="V62" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W62">
         <v>-0.007778</v>
@@ -18823,10 +18862,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>44289.34304075231</v>
@@ -18844,13 +18883,13 @@
         <v>1650</v>
       </c>
       <c r="H63" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I63" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J63" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K63">
         <v>164</v>
@@ -18874,7 +18913,7 @@
         <v>-24.4</v>
       </c>
       <c r="V63" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W63">
         <v>0.009443999999999999</v>
@@ -18903,10 +18942,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>44289.34327881945</v>
@@ -18924,13 +18963,13 @@
         <v>1668</v>
       </c>
       <c r="H64" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I64" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J64" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K64">
         <v>125</v>
@@ -18966,7 +19005,7 @@
         <v>-24.05</v>
       </c>
       <c r="V64" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W64">
         <v>0.005833</v>
@@ -18995,10 +19034,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>44289.34397466435</v>
@@ -19016,13 +19055,13 @@
         <v>1728</v>
       </c>
       <c r="H65" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I65" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J65" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K65">
         <v>126</v>
@@ -19058,7 +19097,7 @@
         <v>-23.01666667</v>
       </c>
       <c r="V65" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W65">
         <v>0.017222</v>
@@ -19087,10 +19126,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>44289.34411050926</v>
@@ -19108,13 +19147,13 @@
         <v>1740</v>
       </c>
       <c r="H66" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I66" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J66" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="K66">
         <v>112</v>
@@ -19138,7 +19177,7 @@
         <v>-23.22222222</v>
       </c>
       <c r="V66" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W66">
         <v>-0.002284</v>
@@ -19167,10 +19206,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>44289.34466366898</v>
@@ -19188,13 +19227,13 @@
         <v>1788</v>
       </c>
       <c r="H67" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I67" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J67" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K67">
         <v>16</v>
@@ -19230,7 +19269,7 @@
         <v>-23.85</v>
       </c>
       <c r="V67" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W67">
         <v>-0.010463</v>
@@ -19259,10 +19298,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>44289.34477461805</v>
@@ -19280,13 +19319,13 @@
         <v>1800</v>
       </c>
       <c r="H68" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I68" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J68" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K68">
         <v>79</v>
@@ -19310,7 +19349,7 @@
         <v>-24.05</v>
       </c>
       <c r="V68" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W68">
         <v>-0.003333</v>
@@ -19339,10 +19378,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>44289.34512208333</v>
@@ -19360,13 +19399,13 @@
         <v>1830</v>
       </c>
       <c r="H69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I69" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J69" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K69">
         <v>24</v>
@@ -19390,7 +19429,7 @@
         <v>-23.86666667</v>
       </c>
       <c r="V69" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W69">
         <v>0.006111</v>
@@ -19419,10 +19458,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>44289.34535753472</v>
@@ -19440,13 +19479,13 @@
         <v>1848</v>
       </c>
       <c r="H70" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I70" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J70" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K70">
         <v>21</v>
@@ -19482,7 +19521,7 @@
         <v>-23.65</v>
       </c>
       <c r="V70" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W70">
         <v>0.003611</v>
@@ -19511,10 +19550,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>44289.34547163195</v>
@@ -19532,13 +19571,13 @@
         <v>1860</v>
       </c>
       <c r="H71" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I71" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J71" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K71">
         <v>43</v>
@@ -19562,7 +19601,7 @@
         <v>-23.16666667</v>
       </c>
       <c r="V71" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W71">
         <v>0.016111</v>
@@ -19591,10 +19630,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C72" s="2">
         <v>44289.34581603009</v>
@@ -19612,13 +19651,13 @@
         <v>1890</v>
       </c>
       <c r="H72" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I72" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J72" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="K72">
         <v>333</v>
@@ -19642,7 +19681,7 @@
         <v>-23.43333333</v>
       </c>
       <c r="V72" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W72">
         <v>-0.008888999999999999</v>
@@ -19671,10 +19710,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2">
         <v>44289.3460546875</v>
@@ -19692,13 +19731,13 @@
         <v>1908</v>
       </c>
       <c r="H73" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I73" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J73" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K73">
         <v>352</v>
@@ -19734,7 +19773,7 @@
         <v>-23.48333333</v>
       </c>
       <c r="V73" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W73">
         <v>-0.000833</v>
@@ -19763,10 +19802,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>44289.34640887732</v>
@@ -19784,13 +19823,13 @@
         <v>1938</v>
       </c>
       <c r="H74" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I74" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J74" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K74">
         <v>59</v>
@@ -19826,7 +19865,7 @@
         <v>-11.2</v>
       </c>
       <c r="V74" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W74">
         <v>0.409444</v>
@@ -19855,10 +19894,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>44289.34720649305</v>
@@ -19876,13 +19915,13 @@
         <v>2010</v>
       </c>
       <c r="H75" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I75" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J75" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -19906,7 +19945,7 @@
         <v>-5.44166667</v>
       </c>
       <c r="V75" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="W75">
         <v>0.047986</v>

--- a/www/flightdata/xlsx/eoss-308.xlsx
+++ b/www/flightdata/xlsx/eoss-308.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="498">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>AE0SS-12</t>
   </si>
   <si>
@@ -1051,6 +1054,12 @@
   </si>
   <si>
     <t>high Re</t>
+  </si>
+  <si>
+    <t>low_to_high</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -2026,10 +2035,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE136"/>
+  <dimension ref="A1:AF136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2123,13 +2132,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>44289.28019246528</v>
@@ -2147,13 +2159,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2180,7 +2192,7 @@
         <v>1.1</v>
       </c>
       <c r="W2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y2">
         <v>1.1</v>
@@ -2189,12 +2201,12 @@
         <v>2.36044</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>44289.28077677084</v>
@@ -2212,13 +2224,13 @@
         <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K3">
         <v>152</v>
@@ -2257,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X3">
         <v>-0.003333</v>
@@ -2278,12 +2290,12 @@
         <v>2.625597</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>44289.2812353125</v>
@@ -2301,13 +2313,13 @@
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -2334,7 +2346,7 @@
         <v>9.733333330000001</v>
       </c>
       <c r="W4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X4">
         <v>0.145556</v>
@@ -2361,12 +2373,12 @@
         <v>9.849247</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>44289.28146958334</v>
@@ -2384,13 +2396,13 @@
         <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K5">
         <v>27</v>
@@ -2429,7 +2441,7 @@
         <v>18.98333333</v>
       </c>
       <c r="W5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X5">
         <v>0.154167</v>
@@ -2456,12 +2468,12 @@
         <v>15.264438</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>44289.28192900463</v>
@@ -2479,13 +2491,13 @@
         <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K6">
         <v>66</v>
@@ -2512,7 +2524,7 @@
         <v>23.41666667</v>
       </c>
       <c r="W6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X6">
         <v>0.073889</v>
@@ -2539,12 +2551,12 @@
         <v>20.523884</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>44289.28216378472</v>
@@ -2562,13 +2574,13 @@
         <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K7">
         <v>53</v>
@@ -2607,7 +2619,7 @@
         <v>23.5</v>
       </c>
       <c r="W7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X7">
         <v>0.001389</v>
@@ -2634,12 +2646,12 @@
         <v>22.82048</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>44289.28227481482</v>
@@ -2657,13 +2669,13 @@
         <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -2690,7 +2702,7 @@
         <v>23.26666667</v>
       </c>
       <c r="W8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X8">
         <v>-0.007778</v>
@@ -2717,12 +2729,12 @@
         <v>23.188329</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>44289.28262090278</v>
@@ -2740,13 +2752,13 @@
         <v>210</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K9">
         <v>51</v>
@@ -2773,7 +2785,7 @@
         <v>23.63333333</v>
       </c>
       <c r="W9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X9">
         <v>0.012222</v>
@@ -2800,12 +2812,12 @@
         <v>24.759667</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>44289.28285877315</v>
@@ -2823,13 +2835,13 @@
         <v>228</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K10">
         <v>89</v>
@@ -2868,7 +2880,7 @@
         <v>24.1</v>
       </c>
       <c r="W10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X10">
         <v>0.007778</v>
@@ -2895,12 +2907,12 @@
         <v>25.482938</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>44289.28331505787</v>
@@ -2918,13 +2930,13 @@
         <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K11">
         <v>121</v>
@@ -2951,7 +2963,7 @@
         <v>23.8</v>
       </c>
       <c r="W11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X11">
         <v>-0.005</v>
@@ -2978,12 +2990,12 @@
         <v>25.849688</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>44289.28355309028</v>
@@ -3001,13 +3013,13 @@
         <v>288</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K12">
         <v>108</v>
@@ -3046,7 +3058,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X12">
         <v>0.006111</v>
@@ -3073,12 +3085,12 @@
         <v>25.862169</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>44289.28366530093</v>
@@ -3096,13 +3108,13 @@
         <v>300</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K13">
         <v>131</v>
@@ -3129,7 +3141,7 @@
         <v>24.8</v>
       </c>
       <c r="W13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X13">
         <v>0.021111</v>
@@ -3155,13 +3167,16 @@
       <c r="AE13">
         <v>25.850357</v>
       </c>
-    </row>
-    <row r="14" spans="1:31">
+      <c r="AF13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>44289.28424723379</v>
@@ -3179,13 +3194,13 @@
         <v>348</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K14">
         <v>139</v>
@@ -3224,7 +3239,7 @@
         <v>25.16666667</v>
       </c>
       <c r="W14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X14">
         <v>0.006111</v>
@@ -3251,12 +3266,12 @@
         <v>25.561442</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>44289.28494046296</v>
@@ -3274,13 +3289,13 @@
         <v>408</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K15">
         <v>123</v>
@@ -3319,7 +3334,7 @@
         <v>25.71666667</v>
       </c>
       <c r="W15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X15">
         <v>0.009167</v>
@@ -3346,12 +3361,12 @@
         <v>25.402386</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>44289.28505245371</v>
@@ -3369,13 +3384,13 @@
         <v>420</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K16">
         <v>106</v>
@@ -3402,7 +3417,7 @@
         <v>25.625</v>
       </c>
       <c r="W16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X16">
         <v>-0.000764</v>
@@ -3434,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>44289.28539890047</v>
@@ -3452,13 +3467,13 @@
         <v>450</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K17">
         <v>127</v>
@@ -3485,7 +3500,7 @@
         <v>26.36666667</v>
       </c>
       <c r="W17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X17">
         <v>0.024722</v>
@@ -3517,7 +3532,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>44289.28563660879</v>
@@ -3535,13 +3550,13 @@
         <v>468</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K18">
         <v>121</v>
@@ -3580,7 +3595,7 @@
         <v>26.48333333</v>
       </c>
       <c r="W18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X18">
         <v>0.001944</v>
@@ -3612,7 +3627,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>44289.28609410879</v>
@@ -3630,13 +3645,13 @@
         <v>510</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K19">
         <v>119</v>
@@ -3663,7 +3678,7 @@
         <v>27.4</v>
       </c>
       <c r="W19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X19">
         <v>0.015278</v>
@@ -3695,7 +3710,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>44289.28633056713</v>
@@ -3713,13 +3728,13 @@
         <v>528</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K20">
         <v>87</v>
@@ -3758,7 +3773,7 @@
         <v>27.73333333</v>
       </c>
       <c r="W20" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X20">
         <v>0.005556</v>
@@ -3790,7 +3805,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>44289.28644520833</v>
@@ -3808,13 +3823,13 @@
         <v>540</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K21">
         <v>25</v>
@@ -3841,7 +3856,7 @@
         <v>28</v>
       </c>
       <c r="W21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X21">
         <v>0.008888999999999999</v>
@@ -3873,7 +3888,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2">
         <v>44289.2867875463</v>
@@ -3891,13 +3906,13 @@
         <v>570</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K22">
         <v>70</v>
@@ -3924,7 +3939,7 @@
         <v>27</v>
       </c>
       <c r="W22" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X22">
         <v>-0.033333</v>
@@ -3956,7 +3971,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>44289.28702484954</v>
@@ -3974,13 +3989,13 @@
         <v>588</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K23">
         <v>141</v>
@@ -4019,7 +4034,7 @@
         <v>27.56666667</v>
       </c>
       <c r="W23" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X23">
         <v>0.009443999999999999</v>
@@ -4051,7 +4066,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>44289.28772012731</v>
@@ -4069,13 +4084,13 @@
         <v>648</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K24">
         <v>88</v>
@@ -4114,7 +4129,7 @@
         <v>27.93333333</v>
       </c>
       <c r="W24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X24">
         <v>0.006111</v>
@@ -4146,7 +4161,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>44289.28783434028</v>
@@ -4164,13 +4179,13 @@
         <v>660</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K25">
         <v>165</v>
@@ -4197,7 +4212,7 @@
         <v>27.96666667</v>
       </c>
       <c r="W25" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X25">
         <v>0.00037</v>
@@ -4229,7 +4244,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>44289.28817766203</v>
@@ -4247,13 +4262,13 @@
         <v>690</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K26">
         <v>145</v>
@@ -4280,7 +4295,7 @@
         <v>27.43333333</v>
       </c>
       <c r="W26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X26">
         <v>-0.017778</v>
@@ -4312,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>44289.28910834491</v>
@@ -4330,13 +4345,13 @@
         <v>768</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K27">
         <v>136</v>
@@ -4375,7 +4390,7 @@
         <v>27.76666667</v>
       </c>
       <c r="W27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X27">
         <v>0.002778</v>
@@ -4407,7 +4422,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>44289.28922019676</v>
@@ -4425,13 +4440,13 @@
         <v>780</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K28">
         <v>136</v>
@@ -4458,7 +4473,7 @@
         <v>27.9</v>
       </c>
       <c r="W28" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X28">
         <v>0.001481</v>
@@ -4490,7 +4505,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>44289.28956606481</v>
@@ -4508,13 +4523,13 @@
         <v>810</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K29">
         <v>129</v>
@@ -4541,7 +4556,7 @@
         <v>28.3</v>
       </c>
       <c r="W29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X29">
         <v>0.013333</v>
@@ -4573,7 +4588,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>44289.28980344907</v>
@@ -4591,13 +4606,13 @@
         <v>828</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K30">
         <v>129</v>
@@ -4636,7 +4651,7 @@
         <v>28.38333333</v>
       </c>
       <c r="W30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X30">
         <v>0.001389</v>
@@ -4668,7 +4683,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>44289.29049829861</v>
@@ -4686,13 +4701,13 @@
         <v>888</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K31">
         <v>106</v>
@@ -4731,7 +4746,7 @@
         <v>28.9</v>
       </c>
       <c r="W31" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X31">
         <v>0.008611000000000001</v>
@@ -4763,7 +4778,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>44289.29060908565</v>
@@ -4781,13 +4796,13 @@
         <v>900</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K32">
         <v>77</v>
@@ -4814,7 +4829,7 @@
         <v>28.65555556</v>
       </c>
       <c r="W32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X32">
         <v>-0.002716</v>
@@ -4846,7 +4861,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>44289.29095655093</v>
@@ -4864,13 +4879,13 @@
         <v>930</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K33">
         <v>118</v>
@@ -4897,7 +4912,7 @@
         <v>27.8</v>
       </c>
       <c r="W33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X33">
         <v>-0.028519</v>
@@ -4929,7 +4944,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>44289.29119109954</v>
@@ -4947,13 +4962,13 @@
         <v>948</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K34">
         <v>114</v>
@@ -4992,7 +5007,7 @@
         <v>28.01666667</v>
       </c>
       <c r="W34" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X34">
         <v>0.003611</v>
@@ -5024,7 +5039,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>44289.2918871875</v>
@@ -5042,13 +5057,13 @@
         <v>1008</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K35">
         <v>108</v>
@@ -5087,7 +5102,7 @@
         <v>28.26666667</v>
       </c>
       <c r="W35" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X35">
         <v>0.004167</v>
@@ -5119,7 +5134,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>44289.29200021991</v>
@@ -5137,13 +5152,13 @@
         <v>1020</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K36">
         <v>168</v>
@@ -5170,7 +5185,7 @@
         <v>28.36666667</v>
       </c>
       <c r="W36" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X36">
         <v>0.001111</v>
@@ -5202,7 +5217,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>44289.29234341435</v>
@@ -5220,13 +5235,13 @@
         <v>1050</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K37">
         <v>110</v>
@@ -5253,7 +5268,7 @@
         <v>28.53333333</v>
       </c>
       <c r="W37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X37">
         <v>0.005556</v>
@@ -5285,7 +5300,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>44289.29258180556</v>
@@ -5303,13 +5318,13 @@
         <v>1068</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K38">
         <v>152</v>
@@ -5348,7 +5363,7 @@
         <v>28.98333333</v>
       </c>
       <c r="W38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X38">
         <v>0.0075</v>
@@ -5380,7 +5395,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>44289.29327503472</v>
@@ -5398,13 +5413,13 @@
         <v>1128</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K39">
         <v>117</v>
@@ -5443,7 +5458,7 @@
         <v>29.56666667</v>
       </c>
       <c r="W39" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X39">
         <v>0.009722</v>
@@ -5475,7 +5490,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>44289.29338480324</v>
@@ -5493,13 +5508,13 @@
         <v>1140</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K40">
         <v>70</v>
@@ -5526,7 +5541,7 @@
         <v>29.78888889</v>
       </c>
       <c r="W40" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X40">
         <v>0.002469</v>
@@ -5558,7 +5573,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>44289.29373170139</v>
@@ -5576,13 +5591,13 @@
         <v>1170</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K41">
         <v>144</v>
@@ -5609,7 +5624,7 @@
         <v>28.53333333</v>
       </c>
       <c r="W41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X41">
         <v>-0.041852</v>
@@ -5641,7 +5656,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>44289.29397111111</v>
@@ -5659,13 +5674,13 @@
         <v>1188</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K42">
         <v>120</v>
@@ -5704,7 +5719,7 @@
         <v>28.48333333</v>
       </c>
       <c r="W42" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X42">
         <v>-0.000833</v>
@@ -5736,7 +5751,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>44289.29410799769</v>
@@ -5754,13 +5769,13 @@
         <v>1200</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K43">
         <v>92</v>
@@ -5787,7 +5802,7 @@
         <v>28.9</v>
       </c>
       <c r="W43" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X43">
         <v>0.013889</v>
@@ -5819,7 +5834,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>44289.29443003472</v>
@@ -5837,13 +5852,13 @@
         <v>1230</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K44">
         <v>76</v>
@@ -5870,7 +5885,7 @@
         <v>30.4</v>
       </c>
       <c r="W44" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X44">
         <v>0.05</v>
@@ -5902,7 +5917,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>44289.29466424768</v>
@@ -5920,13 +5935,13 @@
         <v>1248</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K45">
         <v>136</v>
@@ -5965,7 +5980,7 @@
         <v>31.2</v>
       </c>
       <c r="W45" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X45">
         <v>0.013333</v>
@@ -5997,7 +6012,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>44289.29477479167</v>
@@ -6015,13 +6030,13 @@
         <v>1260</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K46">
         <v>136</v>
@@ -6048,7 +6063,7 @@
         <v>28.1</v>
       </c>
       <c r="W46" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X46">
         <v>-0.103333</v>
@@ -6080,7 +6095,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>44289.29512045139</v>
@@ -6098,13 +6113,13 @@
         <v>1290</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K47">
         <v>163</v>
@@ -6131,7 +6146,7 @@
         <v>29.43333333</v>
       </c>
       <c r="W47" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X47">
         <v>0.044444</v>
@@ -6163,7 +6178,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>44289.29535901621</v>
@@ -6181,13 +6196,13 @@
         <v>1308</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K48">
         <v>123</v>
@@ -6226,7 +6241,7 @@
         <v>28.4</v>
       </c>
       <c r="W48" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X48">
         <v>-0.017222</v>
@@ -6258,7 +6273,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>44289.29605268518</v>
@@ -6276,13 +6291,13 @@
         <v>1368</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K49">
         <v>112</v>
@@ -6321,7 +6336,7 @@
         <v>29.23333333</v>
       </c>
       <c r="W49" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X49">
         <v>0.013889</v>
@@ -6353,7 +6368,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>44289.29616422454</v>
@@ -6371,13 +6386,13 @@
         <v>1380</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K50">
         <v>102</v>
@@ -6404,7 +6419,7 @@
         <v>29.6</v>
       </c>
       <c r="W50" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X50">
         <v>0.004074</v>
@@ -6436,7 +6451,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>44289.29674895833</v>
@@ -6454,13 +6469,13 @@
         <v>1428</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K51">
         <v>118</v>
@@ -6499,7 +6514,7 @@
         <v>28.75</v>
       </c>
       <c r="W51" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X51">
         <v>-0.014167</v>
@@ -6531,7 +6546,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>44289.29688769676</v>
@@ -6549,13 +6564,13 @@
         <v>1440</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K52">
         <v>133</v>
@@ -6582,7 +6597,7 @@
         <v>29.1</v>
       </c>
       <c r="W52" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X52">
         <v>0.005833</v>
@@ -6614,7 +6629,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>44289.29744302083</v>
@@ -6632,13 +6647,13 @@
         <v>1488</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K53">
         <v>112</v>
@@ -6677,7 +6692,7 @@
         <v>31.65</v>
       </c>
       <c r="W53" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X53">
         <v>0.0425</v>
@@ -6709,7 +6724,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>44289.29790137731</v>
@@ -6727,13 +6742,13 @@
         <v>1530</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K54">
         <v>104</v>
@@ -6760,7 +6775,7 @@
         <v>33.93333333</v>
       </c>
       <c r="W54" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X54">
         <v>0.02537</v>
@@ -6792,7 +6807,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>44289.2981371412</v>
@@ -6810,13 +6825,13 @@
         <v>1548</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K55">
         <v>110</v>
@@ -6855,7 +6870,7 @@
         <v>35.66666667</v>
       </c>
       <c r="W55" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X55">
         <v>0.028889</v>
@@ -6887,7 +6902,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>44289.29859505787</v>
@@ -6905,13 +6920,13 @@
         <v>1590</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K56">
         <v>93</v>
@@ -6938,7 +6953,7 @@
         <v>32.65</v>
       </c>
       <c r="W56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X56">
         <v>-0.050278</v>
@@ -6970,7 +6985,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>44289.29883195602</v>
@@ -6988,13 +7003,13 @@
         <v>1608</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K57">
         <v>94</v>
@@ -7033,7 +7048,7 @@
         <v>33.08333333</v>
       </c>
       <c r="W57" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X57">
         <v>0.007222</v>
@@ -7065,7 +7080,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>44289.29894071759</v>
@@ -7083,13 +7098,13 @@
         <v>1620</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K58">
         <v>71</v>
@@ -7116,7 +7131,7 @@
         <v>34.23333333</v>
       </c>
       <c r="W58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X58">
         <v>0.038333</v>
@@ -7148,7 +7163,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>44289.29928905093</v>
@@ -7166,13 +7181,13 @@
         <v>1650</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K59">
         <v>93</v>
@@ -7199,7 +7214,7 @@
         <v>32.26666667</v>
       </c>
       <c r="W59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X59">
         <v>-0.065556</v>
@@ -7231,7 +7246,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>44289.29952543981</v>
@@ -7249,13 +7264,13 @@
         <v>1668</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K60">
         <v>95</v>
@@ -7294,7 +7309,7 @@
         <v>33.25</v>
       </c>
       <c r="W60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X60">
         <v>0.016389</v>
@@ -7326,7 +7341,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>44289.29998225695</v>
@@ -7344,13 +7359,13 @@
         <v>1710</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K61">
         <v>94</v>
@@ -7377,7 +7392,7 @@
         <v>33.31666667</v>
       </c>
       <c r="W61" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X61">
         <v>0.001111</v>
@@ -7409,7 +7424,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>44289.30022049769</v>
@@ -7427,13 +7442,13 @@
         <v>1728</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K62">
         <v>103</v>
@@ -7472,7 +7487,7 @@
         <v>32.2</v>
       </c>
       <c r="W62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X62">
         <v>-0.018611</v>
@@ -7504,7 +7519,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>44289.30032944444</v>
@@ -7522,13 +7537,13 @@
         <v>1740</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K63">
         <v>107</v>
@@ -7555,7 +7570,7 @@
         <v>32.56666667</v>
       </c>
       <c r="W63" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X63">
         <v>0.012222</v>
@@ -7587,7 +7602,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>44289.3006796412</v>
@@ -7605,13 +7620,13 @@
         <v>1770</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K64">
         <v>119</v>
@@ -7638,7 +7653,7 @@
         <v>32.06666667</v>
       </c>
       <c r="W64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X64">
         <v>-0.016667</v>
@@ -7665,12 +7680,12 @@
         <v>30.444084</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>44289.30091864584</v>
@@ -7688,13 +7703,13 @@
         <v>1788</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K65">
         <v>88</v>
@@ -7733,7 +7748,7 @@
         <v>33.85</v>
       </c>
       <c r="W65" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X65">
         <v>0.029722</v>
@@ -7760,12 +7775,12 @@
         <v>29.813605</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>44289.30160892361</v>
@@ -7783,13 +7798,13 @@
         <v>1848</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K66">
         <v>138</v>
@@ -7828,7 +7843,7 @@
         <v>31.85</v>
       </c>
       <c r="W66" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X66">
         <v>-0.033333</v>
@@ -7854,13 +7869,16 @@
       <c r="AE66">
         <v>28.303233</v>
       </c>
-    </row>
-    <row r="67" spans="1:31">
+      <c r="AF66" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>44289.30172013889</v>
@@ -7878,13 +7896,13 @@
         <v>1860</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K67">
         <v>125</v>
@@ -7911,7 +7929,7 @@
         <v>31.97777778</v>
       </c>
       <c r="W67" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X67">
         <v>0.00142</v>
@@ -7938,12 +7956,12 @@
         <v>28.213432</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>44289.30230331019</v>
@@ -7961,13 +7979,13 @@
         <v>1908</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K68">
         <v>97</v>
@@ -8006,7 +8024,7 @@
         <v>23.66666667</v>
       </c>
       <c r="W68" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X68">
         <v>-0.138519</v>
@@ -8033,12 +8051,12 @@
         <v>27.159131</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>44289.3024141088</v>
@@ -8056,13 +8074,13 @@
         <v>1920</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K69">
         <v>101</v>
@@ -8089,7 +8107,7 @@
         <v>22.51666667</v>
       </c>
       <c r="W69" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X69">
         <v>-0.019167</v>
@@ -8116,12 +8134,12 @@
         <v>27.125729</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>44289.30299829861</v>
@@ -8139,13 +8157,13 @@
         <v>1968</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -8184,7 +8202,7 @@
         <v>18.35</v>
       </c>
       <c r="W70" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X70">
         <v>-0.06944400000000001</v>
@@ -8211,12 +8229,12 @@
         <v>26.301387</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>44289.30310839121</v>
@@ -8234,13 +8252,13 @@
         <v>1980</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K71">
         <v>109</v>
@@ -8267,7 +8285,7 @@
         <v>18.05</v>
       </c>
       <c r="W71" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X71">
         <v>-0.005</v>
@@ -8294,12 +8312,12 @@
         <v>26.283192</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>44289.30369325232</v>
@@ -8317,13 +8335,13 @@
         <v>2028</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K72">
         <v>103</v>
@@ -8362,7 +8380,7 @@
         <v>19.6</v>
       </c>
       <c r="W72" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X72">
         <v>0.025833</v>
@@ -8389,12 +8407,12 @@
         <v>25.44378</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2">
         <v>44289.30383386574</v>
@@ -8412,13 +8430,13 @@
         <v>2040</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K73">
         <v>148</v>
@@ -8445,7 +8463,7 @@
         <v>23.68333333</v>
       </c>
       <c r="W73" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X73">
         <v>0.06805600000000001</v>
@@ -8472,12 +8490,12 @@
         <v>25.258742</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>44289.30438799768</v>
@@ -8495,13 +8513,13 @@
         <v>2088</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K74">
         <v>108</v>
@@ -8540,7 +8558,7 @@
         <v>28.9</v>
       </c>
       <c r="W74" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X74">
         <v>0.08694399999999999</v>
@@ -8567,12 +8585,12 @@
         <v>24.339676</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>44289.30449833333</v>
@@ -8590,13 +8608,13 @@
         <v>2100</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K75">
         <v>65</v>
@@ -8623,7 +8641,7 @@
         <v>27.18333333</v>
       </c>
       <c r="W75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X75">
         <v>-0.028611</v>
@@ -8650,12 +8668,12 @@
         <v>24.245868</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:32">
       <c r="A76" t="s">
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>44289.30508075232</v>
@@ -8673,13 +8691,13 @@
         <v>2148</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K76">
         <v>63</v>
@@ -8718,7 +8736,7 @@
         <v>27.41666667</v>
       </c>
       <c r="W76" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X76">
         <v>0.003889</v>
@@ -8745,12 +8763,12 @@
         <v>23.511982</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>44289.30577674769</v>
@@ -8768,13 +8786,13 @@
         <v>2208</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K77">
         <v>95</v>
@@ -8813,7 +8831,7 @@
         <v>22.65</v>
       </c>
       <c r="W77" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X77">
         <v>-0.079444</v>
@@ -8840,12 +8858,12 @@
         <v>23.004829</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>44289.30588592593</v>
@@ -8863,13 +8881,13 @@
         <v>2220</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K78">
         <v>130</v>
@@ -8896,7 +8914,7 @@
         <v>24.225</v>
       </c>
       <c r="W78" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X78">
         <v>0.013125</v>
@@ -8923,12 +8941,12 @@
         <v>22.983351</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:32">
       <c r="A79" t="s">
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>44289.30647016204</v>
@@ -8946,13 +8964,13 @@
         <v>2268</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K79">
         <v>122</v>
@@ -8991,7 +9009,7 @@
         <v>24.11666667</v>
       </c>
       <c r="W79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X79">
         <v>-0.001806</v>
@@ -9018,12 +9036,12 @@
         <v>22.637188</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>44289.30716491898</v>
@@ -9041,13 +9059,13 @@
         <v>2328</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K80">
         <v>63</v>
@@ -9086,7 +9104,7 @@
         <v>23.23333333</v>
       </c>
       <c r="W80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X80">
         <v>-0.014722</v>
@@ -9118,7 +9136,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2">
         <v>44289.30727484954</v>
@@ -9136,13 +9154,13 @@
         <v>2340</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K81">
         <v>97</v>
@@ -9169,7 +9187,7 @@
         <v>24.5</v>
       </c>
       <c r="W81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X81">
         <v>0.010556</v>
@@ -9201,7 +9219,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>44289.30786054398</v>
@@ -9219,13 +9237,13 @@
         <v>2388</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K82">
         <v>96</v>
@@ -9264,7 +9282,7 @@
         <v>23.96666667</v>
       </c>
       <c r="W82" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X82">
         <v>-0.008888999999999999</v>
@@ -9296,7 +9314,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C83" s="2">
         <v>44289.30797071759</v>
@@ -9314,13 +9332,13 @@
         <v>2400</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K83">
         <v>168</v>
@@ -9347,7 +9365,7 @@
         <v>26.3</v>
       </c>
       <c r="W83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X83">
         <v>0.038889</v>
@@ -9379,7 +9397,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>44289.30855472222</v>
@@ -9397,13 +9415,13 @@
         <v>2448</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K84">
         <v>115</v>
@@ -9442,7 +9460,7 @@
         <v>27.68333333</v>
       </c>
       <c r="W84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X84">
         <v>0.023056</v>
@@ -9474,7 +9492,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2">
         <v>44289.30866436342</v>
@@ -9492,13 +9510,13 @@
         <v>2460</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K85">
         <v>190</v>
@@ -9525,7 +9543,7 @@
         <v>23.95</v>
       </c>
       <c r="W85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X85">
         <v>-0.062222</v>
@@ -9557,7 +9575,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>44289.30900952547</v>
@@ -9575,13 +9593,13 @@
         <v>2490</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K86">
         <v>205</v>
@@ -9608,7 +9626,7 @@
         <v>19.16666667</v>
       </c>
       <c r="W86" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X86">
         <v>-0.159444</v>
@@ -9640,7 +9658,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>44289.30924861111</v>
@@ -9658,13 +9676,13 @@
         <v>2508</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K87">
         <v>117</v>
@@ -9703,7 +9721,7 @@
         <v>19.56666667</v>
       </c>
       <c r="W87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X87">
         <v>0.006667</v>
@@ -9735,7 +9753,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>44289.30970675926</v>
@@ -9753,13 +9771,13 @@
         <v>2550</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K88">
         <v>187</v>
@@ -9786,7 +9804,7 @@
         <v>21.31666667</v>
       </c>
       <c r="W88" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X88">
         <v>0.029167</v>
@@ -9818,7 +9836,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>44289.30994333333</v>
@@ -9836,13 +9854,13 @@
         <v>2568</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K89">
         <v>118</v>
@@ -9881,7 +9899,7 @@
         <v>21.13333333</v>
       </c>
       <c r="W89" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X89">
         <v>-0.003056</v>
@@ -9913,7 +9931,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>44289.31005087963</v>
@@ -9931,13 +9949,13 @@
         <v>2580</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K90">
         <v>153</v>
@@ -9964,7 +9982,7 @@
         <v>20.46666667</v>
       </c>
       <c r="W90" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X90">
         <v>-0.022222</v>
@@ -9996,7 +10014,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2">
         <v>44289.31039877314</v>
@@ -10014,13 +10032,13 @@
         <v>2610</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K91">
         <v>171</v>
@@ -10047,7 +10065,7 @@
         <v>22.2</v>
       </c>
       <c r="W91" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X91">
         <v>0.057778</v>
@@ -10079,7 +10097,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2">
         <v>44289.31063765047</v>
@@ -10097,13 +10115,13 @@
         <v>2628</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K92">
         <v>150</v>
@@ -10142,7 +10160,7 @@
         <v>21.7</v>
       </c>
       <c r="W92" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X92">
         <v>-0.008333</v>
@@ -10174,7 +10192,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>44289.31133126158</v>
@@ -10192,13 +10210,13 @@
         <v>2688</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K93">
         <v>134</v>
@@ -10237,7 +10255,7 @@
         <v>21.31666667</v>
       </c>
       <c r="W93" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X93">
         <v>-0.006389</v>
@@ -10269,7 +10287,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>44289.31144152777</v>
@@ -10287,13 +10305,13 @@
         <v>2700</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K94">
         <v>182</v>
@@ -10320,7 +10338,7 @@
         <v>20.96666667</v>
       </c>
       <c r="W94" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X94">
         <v>-0.003889</v>
@@ -10352,7 +10370,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2">
         <v>44289.3117890162</v>
@@ -10370,13 +10388,13 @@
         <v>2730</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K95">
         <v>170</v>
@@ -10403,7 +10421,7 @@
         <v>19.8</v>
       </c>
       <c r="W95" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X95">
         <v>-0.038889</v>
@@ -10435,7 +10453,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="2">
         <v>44289.31202645833</v>
@@ -10453,13 +10471,13 @@
         <v>2748</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K96">
         <v>112</v>
@@ -10498,7 +10516,7 @@
         <v>18.98333333</v>
       </c>
       <c r="W96" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X96">
         <v>-0.013611</v>
@@ -10530,7 +10548,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2">
         <v>44289.31248106482</v>
@@ -10548,13 +10566,13 @@
         <v>2790</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K97">
         <v>143</v>
@@ -10581,7 +10599,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W97" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X97">
         <v>-0.015833</v>
@@ -10613,7 +10631,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2">
         <v>44289.31272116898</v>
@@ -10631,13 +10649,13 @@
         <v>2808</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K98">
         <v>98</v>
@@ -10676,7 +10694,7 @@
         <v>19.3</v>
       </c>
       <c r="W98" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X98">
         <v>0.021111</v>
@@ -10708,7 +10726,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C99" s="2">
         <v>44289.31283771991</v>
@@ -10726,13 +10744,13 @@
         <v>2820</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K99">
         <v>121</v>
@@ -10759,7 +10777,7 @@
         <v>21.33333333</v>
       </c>
       <c r="W99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X99">
         <v>0.067778</v>
@@ -10791,7 +10809,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>44289.3131762037</v>
@@ -10809,13 +10827,13 @@
         <v>2850</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K100">
         <v>136</v>
@@ -10842,7 +10860,7 @@
         <v>29.86666667</v>
       </c>
       <c r="W100" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X100">
         <v>0.284444</v>
@@ -10874,7 +10892,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="2">
         <v>44289.31341512731</v>
@@ -10892,13 +10910,13 @@
         <v>2868</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K101">
         <v>120</v>
@@ -10937,7 +10955,7 @@
         <v>27.78333333</v>
       </c>
       <c r="W101" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X101">
         <v>-0.034722</v>
@@ -10969,7 +10987,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C102" s="2">
         <v>44289.31352519676</v>
@@ -10987,13 +11005,13 @@
         <v>2880</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K102">
         <v>134</v>
@@ -11020,7 +11038,7 @@
         <v>27.03333333</v>
       </c>
       <c r="W102" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X102">
         <v>-0.025</v>
@@ -11052,7 +11070,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C103" s="2">
         <v>44289.31387267361</v>
@@ -11070,13 +11088,13 @@
         <v>2910</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K103">
         <v>114</v>
@@ -11103,7 +11121,7 @@
         <v>26.33333333</v>
       </c>
       <c r="W103" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X103">
         <v>-0.023333</v>
@@ -11135,7 +11153,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>44289.31411021991</v>
@@ -11153,13 +11171,13 @@
         <v>2928</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K104">
         <v>108</v>
@@ -11198,7 +11216,7 @@
         <v>25.11666667</v>
       </c>
       <c r="W104" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X104">
         <v>-0.020278</v>
@@ -11230,7 +11248,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C105" s="2">
         <v>44289.31422042824</v>
@@ -11248,13 +11266,13 @@
         <v>2940</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K105">
         <v>111</v>
@@ -11281,7 +11299,7 @@
         <v>23.3</v>
       </c>
       <c r="W105" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X105">
         <v>-0.060556</v>
@@ -11313,7 +11331,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C106" s="2">
         <v>44289.31456719907</v>
@@ -11331,13 +11349,13 @@
         <v>2970</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K106">
         <v>96</v>
@@ -11364,7 +11382,7 @@
         <v>20.8</v>
       </c>
       <c r="W106" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X106">
         <v>-0.083333</v>
@@ -11396,7 +11414,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C107" s="2">
         <v>44289.31480430556</v>
@@ -11414,13 +11432,13 @@
         <v>2988</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K107">
         <v>110</v>
@@ -11459,7 +11477,7 @@
         <v>20.71666667</v>
       </c>
       <c r="W107" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X107">
         <v>-0.001389</v>
@@ -11491,7 +11509,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C108" s="2">
         <v>44289.31549835648</v>
@@ -11509,13 +11527,13 @@
         <v>3048</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K108">
         <v>116</v>
@@ -11554,7 +11572,7 @@
         <v>16.75</v>
       </c>
       <c r="W108" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X108">
         <v>-0.066111</v>
@@ -11586,7 +11604,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2">
         <v>44289.31561175926</v>
@@ -11604,13 +11622,13 @@
         <v>3060</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K109">
         <v>92</v>
@@ -11637,7 +11655,7 @@
         <v>17.56666667</v>
       </c>
       <c r="W109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X109">
         <v>0.009074</v>
@@ -11669,7 +11687,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" s="2">
         <v>44289.31595774306</v>
@@ -11687,13 +11705,13 @@
         <v>3090</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K110">
         <v>83</v>
@@ -11720,7 +11738,7 @@
         <v>18.6</v>
       </c>
       <c r="W110" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X110">
         <v>0.034444</v>
@@ -11752,7 +11770,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2">
         <v>44289.31619278935</v>
@@ -11770,13 +11788,13 @@
         <v>3108</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K111">
         <v>90</v>
@@ -11815,7 +11833,7 @@
         <v>19.41666667</v>
       </c>
       <c r="W111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X111">
         <v>0.013611</v>
@@ -11847,7 +11865,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2">
         <v>44289.31630166667</v>
@@ -11865,13 +11883,13 @@
         <v>3120</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K112">
         <v>70</v>
@@ -11898,7 +11916,7 @@
         <v>21.23333333</v>
       </c>
       <c r="W112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X112">
         <v>0.060556</v>
@@ -11930,7 +11948,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2">
         <v>44289.3168882176</v>
@@ -11948,13 +11966,13 @@
         <v>3168</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K113">
         <v>98</v>
@@ -11993,7 +12011,7 @@
         <v>23.76666667</v>
       </c>
       <c r="W113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X113">
         <v>0.042222</v>
@@ -12025,7 +12043,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
         <v>44289.31699675926</v>
@@ -12043,13 +12061,13 @@
         <v>3180</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K114">
         <v>88</v>
@@ -12076,7 +12094,7 @@
         <v>24.65</v>
       </c>
       <c r="W114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X114">
         <v>0.014722</v>
@@ -12108,7 +12126,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C115" s="2">
         <v>44289.31734570602</v>
@@ -12126,13 +12144,13 @@
         <v>3210</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K115">
         <v>103</v>
@@ -12159,7 +12177,7 @@
         <v>26.16666667</v>
       </c>
       <c r="W115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X115">
         <v>0.050556</v>
@@ -12191,7 +12209,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C116" s="2">
         <v>44289.3175825463</v>
@@ -12209,13 +12227,13 @@
         <v>3228</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K116">
         <v>97</v>
@@ -12254,7 +12272,7 @@
         <v>26.41666667</v>
       </c>
       <c r="W116" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X116">
         <v>0.004167</v>
@@ -12286,7 +12304,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C117" s="2">
         <v>44289.31803774305</v>
@@ -12304,13 +12322,13 @@
         <v>3270</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K117">
         <v>86</v>
@@ -12337,7 +12355,7 @@
         <v>24.71666667</v>
       </c>
       <c r="W117" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X117">
         <v>-0.028333</v>
@@ -12369,7 +12387,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C118" s="2">
         <v>44289.31827712963</v>
@@ -12387,13 +12405,13 @@
         <v>3288</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K118">
         <v>94</v>
@@ -12432,7 +12450,7 @@
         <v>23.85</v>
       </c>
       <c r="W118" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X118">
         <v>-0.014444</v>
@@ -12464,7 +12482,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C119" s="2">
         <v>44289.31838730324</v>
@@ -12482,13 +12500,13 @@
         <v>3300</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K119">
         <v>99</v>
@@ -12515,7 +12533,7 @@
         <v>23.5</v>
       </c>
       <c r="W119" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X119">
         <v>-0.011667</v>
@@ -12547,7 +12565,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2">
         <v>44289.31873393519</v>
@@ -12565,13 +12583,13 @@
         <v>3330</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K120">
         <v>114</v>
@@ -12598,7 +12616,7 @@
         <v>22.43333333</v>
       </c>
       <c r="W120" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X120">
         <v>-0.035556</v>
@@ -12630,7 +12648,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C121" s="2">
         <v>44289.31897037037</v>
@@ -12648,13 +12666,13 @@
         <v>3348</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K121">
         <v>103</v>
@@ -12693,7 +12711,7 @@
         <v>22.75</v>
       </c>
       <c r="W121" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X121">
         <v>0.005278</v>
@@ -12725,7 +12743,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" s="2">
         <v>44289.31942747685</v>
@@ -12743,13 +12761,13 @@
         <v>3390</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K122">
         <v>110</v>
@@ -12776,7 +12794,7 @@
         <v>21.65</v>
       </c>
       <c r="W122" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X122">
         <v>-0.018333</v>
@@ -12808,7 +12826,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C123" s="2">
         <v>44289.31966621528</v>
@@ -12826,13 +12844,13 @@
         <v>3408</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K123">
         <v>99</v>
@@ -12871,7 +12889,7 @@
         <v>21.28333333</v>
       </c>
       <c r="W123" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X123">
         <v>-0.006111</v>
@@ -12903,7 +12921,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C124" s="2">
         <v>44289.31977466435</v>
@@ -12921,13 +12939,13 @@
         <v>3420</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K124">
         <v>99</v>
@@ -12954,7 +12972,7 @@
         <v>20.56666667</v>
       </c>
       <c r="W124" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X124">
         <v>-0.023889</v>
@@ -12986,7 +13004,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2">
         <v>44289.32012114584</v>
@@ -13004,13 +13022,13 @@
         <v>3450</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K125">
         <v>113</v>
@@ -13037,7 +13055,7 @@
         <v>19.03333333</v>
       </c>
       <c r="W125" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X125">
         <v>-0.051111</v>
@@ -13069,7 +13087,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C126" s="2">
         <v>44289.32035984954</v>
@@ -13087,13 +13105,13 @@
         <v>3468</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K126">
         <v>101</v>
@@ -13132,7 +13150,7 @@
         <v>19.18333333</v>
       </c>
       <c r="W126" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X126">
         <v>0.0025</v>
@@ -13164,7 +13182,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2">
         <v>44289.32081715278</v>
@@ -13182,13 +13200,13 @@
         <v>3510</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K127">
         <v>97</v>
@@ -13215,7 +13233,7 @@
         <v>20.28333333</v>
       </c>
       <c r="W127" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X127">
         <v>0.018333</v>
@@ -13247,7 +13265,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2">
         <v>44289.32105385417</v>
@@ -13265,13 +13283,13 @@
         <v>3528</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K128">
         <v>101</v>
@@ -13310,7 +13328,7 @@
         <v>21.45</v>
       </c>
       <c r="W128" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X128">
         <v>0.019444</v>
@@ -13342,7 +13360,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C129" s="2">
         <v>44289.32116510416</v>
@@ -13360,13 +13378,13 @@
         <v>3540</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K129">
         <v>83</v>
@@ -13393,7 +13411,7 @@
         <v>22.76666667</v>
       </c>
       <c r="W129" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X129">
         <v>0.043889</v>
@@ -13425,7 +13443,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C130" s="2">
         <v>44289.32151105324</v>
@@ -13443,13 +13461,13 @@
         <v>3570</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K130">
         <v>114</v>
@@ -13476,7 +13494,7 @@
         <v>24.5</v>
       </c>
       <c r="W130" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X130">
         <v>0.057778</v>
@@ -13508,7 +13526,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C131" s="2">
         <v>44289.32174909722</v>
@@ -13526,13 +13544,13 @@
         <v>3588</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K131">
         <v>101</v>
@@ -13571,7 +13589,7 @@
         <v>23.85</v>
       </c>
       <c r="W131" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X131">
         <v>-0.010833</v>
@@ -13603,7 +13621,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C132" s="2">
         <v>44289.32185712963</v>
@@ -13621,13 +13639,13 @@
         <v>3600</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K132">
         <v>108</v>
@@ -13654,7 +13672,7 @@
         <v>23.4</v>
       </c>
       <c r="W132" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X132">
         <v>-0.015</v>
@@ -13686,7 +13704,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C133" s="2">
         <v>44289.32244366898</v>
@@ -13704,13 +13722,13 @@
         <v>3648</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K133">
         <v>94</v>
@@ -13749,7 +13767,7 @@
         <v>21.81666667</v>
       </c>
       <c r="W133" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X133">
         <v>-0.026389</v>
@@ -13781,7 +13799,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C134" s="2">
         <v>44289.32255368055</v>
@@ -13799,13 +13817,13 @@
         <v>3660</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K134">
         <v>97</v>
@@ -13832,7 +13850,7 @@
         <v>21.21666667</v>
       </c>
       <c r="W134" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X134">
         <v>-0.01</v>
@@ -13864,7 +13882,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" s="2">
         <v>44289.32289793981</v>
@@ -13882,13 +13900,13 @@
         <v>3690</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K135">
         <v>99</v>
@@ -13915,7 +13933,7 @@
         <v>18.83333333</v>
       </c>
       <c r="W135" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X135">
         <v>-0.079444</v>
@@ -13947,7 +13965,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C136" s="2">
         <v>44289.32313953704</v>
@@ -13965,13 +13983,13 @@
         <v>3708</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K136">
         <v>97</v>
@@ -14010,7 +14028,7 @@
         <v>18.8</v>
       </c>
       <c r="W136" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X136">
         <v>-0.000556</v>
@@ -14044,10 +14062,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE75"/>
+  <dimension ref="A1:AF75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -14141,13 +14159,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>44289.323943125</v>
@@ -14165,13 +14186,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K2">
         <v>88</v>
@@ -14198,7 +14219,7 @@
         <v>-20.78888889</v>
       </c>
       <c r="W2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Y2">
         <v>-20.788889</v>
@@ -14207,12 +14228,12 @@
         <v>-18.605264</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>44289.32420905092</v>
@@ -14230,13 +14251,13 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K3">
         <v>108</v>
@@ -14275,7 +14296,7 @@
         <v>-58.6</v>
       </c>
       <c r="W3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X3">
         <v>-0.420123</v>
@@ -14296,12 +14317,12 @@
         <v>-77.675119</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>44289.32428706018</v>
@@ -14319,13 +14340,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K4">
         <v>103</v>
@@ -14352,7 +14373,7 @@
         <v>-156.3</v>
       </c>
       <c r="W4" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X4">
         <v>-3.256667</v>
@@ -14379,12 +14400,12 @@
         <v>-126.429148</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>44289.32452712963</v>
@@ -14402,13 +14423,13 @@
         <v>48</v>
       </c>
       <c r="H5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K5">
         <v>106</v>
@@ -14447,7 +14468,7 @@
         <v>-145.36666667</v>
       </c>
       <c r="W5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X5">
         <v>0.364444</v>
@@ -14474,12 +14495,12 @@
         <v>-152.767649</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>44289.32463643519</v>
@@ -14497,13 +14518,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K6">
         <v>67</v>
@@ -14530,7 +14551,7 @@
         <v>-139.53333333</v>
       </c>
       <c r="W6" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X6">
         <v>0.194444</v>
@@ -14557,12 +14578,12 @@
         <v>-148.951924</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>44289.32485122685</v>
@@ -14580,13 +14601,13 @@
         <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I7" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K7">
         <v>94</v>
@@ -14625,7 +14646,7 @@
         <v>-130.16666667</v>
       </c>
       <c r="W7" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X7">
         <v>0.312222</v>
@@ -14652,12 +14673,12 @@
         <v>-133.716809</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>44289.32522667824</v>
@@ -14675,13 +14696,13 @@
         <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K8">
         <v>118</v>
@@ -14720,7 +14741,7 @@
         <v>-119.26666667</v>
       </c>
       <c r="W8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X8">
         <v>0.363333</v>
@@ -14747,12 +14768,12 @@
         <v>-115.293418</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>44289.32533144676</v>
@@ -14770,13 +14791,13 @@
         <v>120</v>
       </c>
       <c r="H9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K9">
         <v>110</v>
@@ -14803,7 +14824,7 @@
         <v>-121.2</v>
       </c>
       <c r="W9" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X9">
         <v>-0.032222</v>
@@ -14830,12 +14851,12 @@
         <v>-112.309322</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>44289.32567565973</v>
@@ -14853,13 +14874,13 @@
         <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K10">
         <v>103</v>
@@ -14886,7 +14907,7 @@
         <v>-109.56666667</v>
       </c>
       <c r="W10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X10">
         <v>0.387778</v>
@@ -14913,12 +14934,12 @@
         <v>-109.804856</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>44289.32591612269</v>
@@ -14936,13 +14957,13 @@
         <v>168</v>
       </c>
       <c r="H11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J11" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K11">
         <v>107</v>
@@ -14981,7 +15002,7 @@
         <v>-107.21666667</v>
       </c>
       <c r="W11" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X11">
         <v>0.039167</v>
@@ -15008,12 +15029,12 @@
         <v>-108.171591</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>44289.32637018518</v>
@@ -15031,13 +15052,13 @@
         <v>210</v>
       </c>
       <c r="H12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J12" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K12">
         <v>180</v>
@@ -15064,7 +15085,7 @@
         <v>-92.81666667</v>
       </c>
       <c r="W12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X12">
         <v>0.24</v>
@@ -15091,12 +15112,12 @@
         <v>-99.314358</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>44289.32664009259</v>
@@ -15114,13 +15135,13 @@
         <v>228</v>
       </c>
       <c r="H13" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K13">
         <v>118</v>
@@ -15159,7 +15180,7 @@
         <v>-89.40000000000001</v>
       </c>
       <c r="W13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X13">
         <v>0.056944</v>
@@ -15186,12 +15207,12 @@
         <v>-94.031071</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>44289.32672039352</v>
@@ -15209,13 +15230,13 @@
         <v>240</v>
       </c>
       <c r="H14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K14">
         <v>61</v>
@@ -15242,7 +15263,7 @@
         <v>-88.26666667000001</v>
       </c>
       <c r="W14" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X14">
         <v>0.037778</v>
@@ -15269,12 +15290,12 @@
         <v>-90.08716800000001</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>44289.32699259259</v>
@@ -15292,13 +15313,13 @@
         <v>258</v>
       </c>
       <c r="H15" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I15" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -15337,7 +15358,7 @@
         <v>-85.66666667</v>
       </c>
       <c r="W15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X15">
         <v>0.08666699999999999</v>
@@ -15364,12 +15385,12 @@
         <v>-84.95657199999999</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>44289.32706525463</v>
@@ -15387,13 +15408,13 @@
         <v>270</v>
       </c>
       <c r="H16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I16" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J16" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -15420,7 +15441,7 @@
         <v>-83.56666667</v>
       </c>
       <c r="W16" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X16">
         <v>0.07000000000000001</v>
@@ -15452,7 +15473,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>44289.32730726852</v>
@@ -15470,13 +15491,13 @@
         <v>288</v>
       </c>
       <c r="H17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K17">
         <v>67</v>
@@ -15515,7 +15536,7 @@
         <v>-81.06666667</v>
       </c>
       <c r="W17" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X17">
         <v>0.083333</v>
@@ -15547,7 +15568,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>44289.3274146412</v>
@@ -15565,13 +15586,13 @@
         <v>300</v>
       </c>
       <c r="H18" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I18" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J18" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K18">
         <v>117</v>
@@ -15598,7 +15619,7 @@
         <v>-79.5</v>
       </c>
       <c r="W18" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X18">
         <v>0.052222</v>
@@ -15630,7 +15651,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>44289.32800023148</v>
@@ -15648,13 +15669,13 @@
         <v>348</v>
       </c>
       <c r="H19" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I19" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J19" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K19">
         <v>132</v>
@@ -15693,7 +15714,7 @@
         <v>-73.84999999999999</v>
       </c>
       <c r="W19" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X19">
         <v>0.094167</v>
@@ -15725,7 +15746,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>44289.32810972222</v>
@@ -15743,13 +15764,13 @@
         <v>360</v>
       </c>
       <c r="H20" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I20" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J20" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K20">
         <v>125</v>
@@ -15776,7 +15797,7 @@
         <v>-71.96666667</v>
       </c>
       <c r="W20" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X20">
         <v>0.031389</v>
@@ -15808,7 +15829,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>44289.32845418982</v>
@@ -15826,13 +15847,13 @@
         <v>390</v>
       </c>
       <c r="H21" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J21" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K21">
         <v>102</v>
@@ -15859,7 +15880,7 @@
         <v>-65.73333332999999</v>
       </c>
       <c r="W21" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X21">
         <v>0.207778</v>
@@ -15891,7 +15912,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>44289.32869456019</v>
@@ -15909,13 +15930,13 @@
         <v>408</v>
       </c>
       <c r="H22" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I22" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J22" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K22">
         <v>107</v>
@@ -15954,7 +15975,7 @@
         <v>-64.41666667</v>
       </c>
       <c r="W22" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X22">
         <v>0.021944</v>
@@ -15986,7 +16007,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>44289.32938958333</v>
@@ -16004,13 +16025,13 @@
         <v>468</v>
       </c>
       <c r="H23" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I23" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J23" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K23">
         <v>114</v>
@@ -16049,7 +16070,7 @@
         <v>-57.56666667</v>
       </c>
       <c r="W23" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X23">
         <v>0.114167</v>
@@ -16081,7 +16102,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>44289.32949666667</v>
@@ -16099,13 +16120,13 @@
         <v>480</v>
       </c>
       <c r="H24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="J24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K24">
         <v>102</v>
@@ -16132,7 +16153,7 @@
         <v>-58.12222222</v>
       </c>
       <c r="W24" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X24">
         <v>-0.006173</v>
@@ -16164,7 +16185,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>44289.32984449074</v>
@@ -16182,13 +16203,13 @@
         <v>510</v>
       </c>
       <c r="H25" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I25" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J25" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K25">
         <v>114</v>
@@ -16215,7 +16236,7 @@
         <v>-54.23333333</v>
       </c>
       <c r="W25" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X25">
         <v>0.12963</v>
@@ -16247,7 +16268,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>44289.33008274306</v>
@@ -16265,13 +16286,13 @@
         <v>528</v>
       </c>
       <c r="H26" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I26" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J26" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K26">
         <v>98</v>
@@ -16310,7 +16331,7 @@
         <v>-54.06666667</v>
       </c>
       <c r="W26" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X26">
         <v>0.002778</v>
@@ -16342,7 +16363,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>44289.33053688658</v>
@@ -16360,13 +16381,13 @@
         <v>570</v>
       </c>
       <c r="H27" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I27" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J27" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K27">
         <v>95</v>
@@ -16393,7 +16414,7 @@
         <v>-51.4</v>
       </c>
       <c r="W27" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X27">
         <v>0.044444</v>
@@ -16425,7 +16446,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>44289.33077887732</v>
@@ -16443,13 +16464,13 @@
         <v>588</v>
       </c>
       <c r="H28" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I28" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J28" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K28">
         <v>99</v>
@@ -16488,7 +16509,7 @@
         <v>-49.51666667</v>
       </c>
       <c r="W28" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X28">
         <v>0.031389</v>
@@ -16520,7 +16541,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>44289.33088658565</v>
@@ -16538,13 +16559,13 @@
         <v>600</v>
       </c>
       <c r="H29" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I29" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J29" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K29">
         <v>83</v>
@@ -16571,7 +16592,7 @@
         <v>-49</v>
       </c>
       <c r="W29" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X29">
         <v>0.017222</v>
@@ -16603,7 +16624,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>44289.33147219908</v>
@@ -16621,13 +16642,13 @@
         <v>648</v>
       </c>
       <c r="H30" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I30" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J30" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -16666,7 +16687,7 @@
         <v>-45.78333333</v>
       </c>
       <c r="W30" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X30">
         <v>0.053611</v>
@@ -16698,7 +16719,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>44289.3321668287</v>
@@ -16716,13 +16737,13 @@
         <v>708</v>
       </c>
       <c r="H31" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I31" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J31" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K31">
         <v>130</v>
@@ -16761,7 +16782,7 @@
         <v>-44.16666667</v>
       </c>
       <c r="W31" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X31">
         <v>0.026944</v>
@@ -16793,7 +16814,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>44289.33286096065</v>
@@ -16811,13 +16832,13 @@
         <v>768</v>
       </c>
       <c r="H32" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I32" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J32" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K32">
         <v>147</v>
@@ -16856,7 +16877,7 @@
         <v>-40.38333333</v>
       </c>
       <c r="W32" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X32">
         <v>0.063056</v>
@@ -16888,7 +16909,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>44289.33300252315</v>
@@ -16906,13 +16927,13 @@
         <v>780</v>
       </c>
       <c r="H33" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I33" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J33" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K33">
         <v>112</v>
@@ -16939,7 +16960,7 @@
         <v>-42.63888889</v>
       </c>
       <c r="W33" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X33">
         <v>-0.012531</v>
@@ -16971,7 +16992,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>44289.33355666666</v>
@@ -16989,13 +17010,13 @@
         <v>828</v>
       </c>
       <c r="H34" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I34" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J34" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K34">
         <v>124</v>
@@ -17034,7 +17055,7 @@
         <v>-38.73333333</v>
       </c>
       <c r="W34" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X34">
         <v>0.065093</v>
@@ -17066,7 +17087,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>44289.33366600695</v>
@@ -17084,13 +17105,13 @@
         <v>840</v>
       </c>
       <c r="H35" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I35" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J35" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K35">
         <v>143</v>
@@ -17117,7 +17138,7 @@
         <v>-38.71666667</v>
       </c>
       <c r="W35" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X35">
         <v>0.000278</v>
@@ -17149,7 +17170,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>44289.334250625</v>
@@ -17167,13 +17188,13 @@
         <v>888</v>
       </c>
       <c r="H36" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I36" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J36" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K36">
         <v>146</v>
@@ -17212,7 +17233,7 @@
         <v>-37.5</v>
       </c>
       <c r="W36" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X36">
         <v>0.020278</v>
@@ -17244,7 +17265,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>44289.33438798611</v>
@@ -17262,13 +17283,13 @@
         <v>900</v>
       </c>
       <c r="H37" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I37" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J37" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K37">
         <v>119</v>
@@ -17295,7 +17316,7 @@
         <v>-36.98333333</v>
       </c>
       <c r="W37" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X37">
         <v>0.008611000000000001</v>
@@ -17327,7 +17348,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>44289.33494449074</v>
@@ -17345,13 +17366,13 @@
         <v>948</v>
       </c>
       <c r="H38" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I38" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J38" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K38">
         <v>134</v>
@@ -17390,7 +17411,7 @@
         <v>-36.06666667</v>
       </c>
       <c r="W38" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X38">
         <v>0.015278</v>
@@ -17422,7 +17443,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>44289.33563971065</v>
@@ -17440,13 +17461,13 @@
         <v>1008</v>
       </c>
       <c r="H39" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I39" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J39" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -17485,7 +17506,7 @@
         <v>-35.01666667</v>
       </c>
       <c r="W39" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X39">
         <v>0.0175</v>
@@ -17517,7 +17538,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>44289.33574947916</v>
@@ -17535,13 +17556,13 @@
         <v>1020</v>
       </c>
       <c r="H40" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I40" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J40" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K40">
         <v>63</v>
@@ -17568,7 +17589,7 @@
         <v>-35.35</v>
       </c>
       <c r="W40" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X40">
         <v>-0.002778</v>
@@ -17600,7 +17621,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>44289.33609668982</v>
@@ -17618,13 +17639,13 @@
         <v>1050</v>
       </c>
       <c r="H41" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I41" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J41" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K41">
         <v>93</v>
@@ -17651,7 +17672,7 @@
         <v>-32.83333333</v>
       </c>
       <c r="W41" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X41">
         <v>0.08388900000000001</v>
@@ -17683,7 +17704,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>44289.33633015047</v>
@@ -17701,13 +17722,13 @@
         <v>1068</v>
       </c>
       <c r="H42" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I42" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J42" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K42">
         <v>116</v>
@@ -17746,7 +17767,7 @@
         <v>-32.96666667</v>
       </c>
       <c r="W42" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X42">
         <v>-0.002222</v>
@@ -17778,7 +17799,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>44289.33643967593</v>
@@ -17796,13 +17817,13 @@
         <v>1080</v>
       </c>
       <c r="H43" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I43" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J43" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="K43">
         <v>75</v>
@@ -17829,7 +17850,7 @@
         <v>-32.36666667</v>
       </c>
       <c r="W43" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X43">
         <v>0.02</v>
@@ -17861,7 +17882,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>44289.33702545139</v>
@@ -17879,13 +17900,13 @@
         <v>1128</v>
       </c>
       <c r="H44" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I44" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J44" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="K44">
         <v>135</v>
@@ -17924,7 +17945,7 @@
         <v>-31.73333333</v>
       </c>
       <c r="W44" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X44">
         <v>0.010556</v>
@@ -17956,7 +17977,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>44289.33748606482</v>
@@ -17974,13 +17995,13 @@
         <v>1170</v>
       </c>
       <c r="H45" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I45" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J45" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K45">
         <v>71</v>
@@ -18007,7 +18028,7 @@
         <v>-30.87777778</v>
       </c>
       <c r="W45" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X45">
         <v>0.009506000000000001</v>
@@ -18039,7 +18060,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>44289.33771907407</v>
@@ -18057,13 +18078,13 @@
         <v>1188</v>
       </c>
       <c r="H46" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I46" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J46" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K46">
         <v>133</v>
@@ -18102,7 +18123,7 @@
         <v>-29.98333333</v>
       </c>
       <c r="W46" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X46">
         <v>0.014907</v>
@@ -18134,7 +18155,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>44289.33817644676</v>
@@ -18152,13 +18173,13 @@
         <v>1230</v>
       </c>
       <c r="H47" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I47" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J47" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K47">
         <v>145</v>
@@ -18185,7 +18206,7 @@
         <v>-28.93333333</v>
       </c>
       <c r="W47" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X47">
         <v>0.0175</v>
@@ -18217,7 +18238,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>44289.33841356482</v>
@@ -18235,13 +18256,13 @@
         <v>1248</v>
       </c>
       <c r="H48" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I48" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J48" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K48">
         <v>131</v>
@@ -18280,7 +18301,7 @@
         <v>-28.7</v>
       </c>
       <c r="W48" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X48">
         <v>0.003889</v>
@@ -18312,7 +18333,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>44289.33887225694</v>
@@ -18330,13 +18351,13 @@
         <v>1290</v>
       </c>
       <c r="H49" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I49" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J49" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K49">
         <v>73</v>
@@ -18363,7 +18384,7 @@
         <v>-29.75</v>
       </c>
       <c r="W49" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X49">
         <v>-0.0175</v>
@@ -18395,7 +18416,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>44289.33911373842</v>
@@ -18413,13 +18434,13 @@
         <v>1308</v>
       </c>
       <c r="H50" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I50" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="J50" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K50">
         <v>134</v>
@@ -18458,7 +18479,7 @@
         <v>-29.83333333</v>
       </c>
       <c r="W50" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X50">
         <v>-0.001389</v>
@@ -18490,7 +18511,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>44289.33921880787</v>
@@ -18508,13 +18529,13 @@
         <v>1320</v>
       </c>
       <c r="H51" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I51" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J51" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K51">
         <v>190</v>
@@ -18541,7 +18562,7 @@
         <v>-29.53333333</v>
       </c>
       <c r="W51" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X51">
         <v>0.01</v>
@@ -18573,7 +18594,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>44289.33956538195</v>
@@ -18591,13 +18612,13 @@
         <v>1350</v>
       </c>
       <c r="H52" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I52" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J52" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K52">
         <v>139</v>
@@ -18624,7 +18645,7 @@
         <v>-26.8</v>
       </c>
       <c r="W52" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X52">
         <v>0.091111</v>
@@ -18656,7 +18677,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>44289.33994267361</v>
@@ -18674,13 +18695,13 @@
         <v>1380</v>
       </c>
       <c r="H53" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I53" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J53" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K53">
         <v>74</v>
@@ -18707,7 +18728,7 @@
         <v>-26.9</v>
       </c>
       <c r="W53" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X53">
         <v>-0.003333</v>
@@ -18739,7 +18760,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>44289.34026041667</v>
@@ -18757,13 +18778,13 @@
         <v>1410</v>
       </c>
       <c r="H54" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I54" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J54" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K54">
         <v>137</v>
@@ -18790,7 +18811,7 @@
         <v>-27.33333333</v>
       </c>
       <c r="W54" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X54">
         <v>-0.014444</v>
@@ -18822,7 +18843,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>44289.3404971875</v>
@@ -18840,13 +18861,13 @@
         <v>1428</v>
       </c>
       <c r="H55" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I55" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J55" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K55">
         <v>87</v>
@@ -18885,7 +18906,7 @@
         <v>-27.31666667</v>
       </c>
       <c r="W55" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X55">
         <v>0.000139</v>
@@ -18917,7 +18938,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>44289.34095932871</v>
@@ -18935,13 +18956,13 @@
         <v>1470</v>
       </c>
       <c r="H56" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I56" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J56" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K56">
         <v>102</v>
@@ -18968,7 +18989,7 @@
         <v>-27.61666667</v>
       </c>
       <c r="W56" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X56">
         <v>-0.005</v>
@@ -19000,7 +19021,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>44289.34119378472</v>
@@ -19018,13 +19039,13 @@
         <v>1488</v>
       </c>
       <c r="H57" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I57" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="J57" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K57">
         <v>109</v>
@@ -19063,7 +19084,7 @@
         <v>-27.26666667</v>
       </c>
       <c r="W57" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X57">
         <v>0.005833</v>
@@ -19095,7 +19116,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>44289.34165127315</v>
@@ -19113,13 +19134,13 @@
         <v>1530</v>
       </c>
       <c r="H58" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I58" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J58" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K58">
         <v>91</v>
@@ -19146,7 +19167,7 @@
         <v>-26.46666667</v>
       </c>
       <c r="W58" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X58">
         <v>0.013333</v>
@@ -19178,7 +19199,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>44289.34188908565</v>
@@ -19196,13 +19217,13 @@
         <v>1548</v>
       </c>
       <c r="H59" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I59" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J59" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K59">
         <v>122</v>
@@ -19241,7 +19262,7 @@
         <v>-26.45</v>
       </c>
       <c r="W59" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X59">
         <v>0.000278</v>
@@ -19273,7 +19294,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>44289.34199621528</v>
@@ -19291,13 +19312,13 @@
         <v>1560</v>
       </c>
       <c r="H60" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I60" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J60" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K60">
         <v>148</v>
@@ -19324,7 +19345,7 @@
         <v>-26.36666667</v>
       </c>
       <c r="W60" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X60">
         <v>0.002778</v>
@@ -19356,7 +19377,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>44289.34234319445</v>
@@ -19374,13 +19395,13 @@
         <v>1590</v>
       </c>
       <c r="H61" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I61" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J61" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K61">
         <v>81</v>
@@ -19407,7 +19428,7 @@
         <v>-24.5</v>
       </c>
       <c r="W61" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X61">
         <v>0.062222</v>
@@ -19439,7 +19460,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>44289.34258387732</v>
@@ -19457,13 +19478,13 @@
         <v>1608</v>
       </c>
       <c r="H62" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I62" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J62" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K62">
         <v>90</v>
@@ -19502,7 +19523,7 @@
         <v>-24.96666667</v>
       </c>
       <c r="W62" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X62">
         <v>-0.007778</v>
@@ -19534,7 +19555,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>44289.34304075231</v>
@@ -19552,13 +19573,13 @@
         <v>1650</v>
       </c>
       <c r="H63" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I63" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J63" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K63">
         <v>164</v>
@@ -19585,7 +19606,7 @@
         <v>-24.4</v>
       </c>
       <c r="W63" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X63">
         <v>0.009443999999999999</v>
@@ -19617,7 +19638,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>44289.34327881945</v>
@@ -19635,13 +19656,13 @@
         <v>1668</v>
       </c>
       <c r="H64" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I64" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J64" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K64">
         <v>125</v>
@@ -19680,7 +19701,7 @@
         <v>-24.05</v>
       </c>
       <c r="W64" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X64">
         <v>0.005833</v>
@@ -19712,7 +19733,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>44289.34397466435</v>
@@ -19730,13 +19751,13 @@
         <v>1728</v>
       </c>
       <c r="H65" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I65" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J65" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K65">
         <v>126</v>
@@ -19775,7 +19796,7 @@
         <v>-23.01666667</v>
       </c>
       <c r="W65" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X65">
         <v>0.017222</v>
@@ -19807,7 +19828,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>44289.34411050926</v>
@@ -19825,13 +19846,13 @@
         <v>1740</v>
       </c>
       <c r="H66" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I66" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J66" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K66">
         <v>112</v>
@@ -19858,7 +19879,7 @@
         <v>-23.22222222</v>
       </c>
       <c r="W66" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X66">
         <v>-0.002284</v>
@@ -19890,7 +19911,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>44289.34466366898</v>
@@ -19908,13 +19929,13 @@
         <v>1788</v>
       </c>
       <c r="H67" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I67" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J67" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K67">
         <v>16</v>
@@ -19953,7 +19974,7 @@
         <v>-23.85</v>
       </c>
       <c r="W67" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X67">
         <v>-0.010463</v>
@@ -19985,7 +20006,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>44289.34477461805</v>
@@ -20003,13 +20024,13 @@
         <v>1800</v>
       </c>
       <c r="H68" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I68" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J68" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="K68">
         <v>79</v>
@@ -20036,7 +20057,7 @@
         <v>-24.05</v>
       </c>
       <c r="W68" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X68">
         <v>-0.003333</v>
@@ -20068,7 +20089,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>44289.34512208333</v>
@@ -20086,13 +20107,13 @@
         <v>1830</v>
       </c>
       <c r="H69" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I69" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J69" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="K69">
         <v>24</v>
@@ -20119,7 +20140,7 @@
         <v>-23.86666667</v>
       </c>
       <c r="W69" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X69">
         <v>0.006111</v>
@@ -20151,7 +20172,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>44289.34535753472</v>
@@ -20169,13 +20190,13 @@
         <v>1848</v>
       </c>
       <c r="H70" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I70" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J70" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K70">
         <v>21</v>
@@ -20214,7 +20235,7 @@
         <v>-23.65</v>
       </c>
       <c r="W70" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X70">
         <v>0.003611</v>
@@ -20246,7 +20267,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>44289.34547163195</v>
@@ -20264,13 +20285,13 @@
         <v>1860</v>
       </c>
       <c r="H71" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I71" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J71" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K71">
         <v>43</v>
@@ -20297,7 +20318,7 @@
         <v>-23.16666667</v>
       </c>
       <c r="W71" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X71">
         <v>0.016111</v>
@@ -20329,7 +20350,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>44289.34581603009</v>
@@ -20347,13 +20368,13 @@
         <v>1890</v>
       </c>
       <c r="H72" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I72" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J72" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K72">
         <v>333</v>
@@ -20380,7 +20401,7 @@
         <v>-23.43333333</v>
       </c>
       <c r="W72" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X72">
         <v>-0.008888999999999999</v>
@@ -20412,7 +20433,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>44289.3460546875</v>
@@ -20430,13 +20451,13 @@
         <v>1908</v>
       </c>
       <c r="H73" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I73" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J73" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K73">
         <v>352</v>
@@ -20475,7 +20496,7 @@
         <v>-23.48333333</v>
       </c>
       <c r="W73" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X73">
         <v>-0.000833</v>
@@ -20507,7 +20528,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>44289.34640887732</v>
@@ -20525,13 +20546,13 @@
         <v>1938</v>
       </c>
       <c r="H74" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I74" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J74" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K74">
         <v>59</v>
@@ -20570,7 +20591,7 @@
         <v>-11.2</v>
       </c>
       <c r="W74" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X74">
         <v>0.409444</v>
@@ -20602,7 +20623,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>44289.34720649305</v>
@@ -20620,13 +20641,13 @@
         <v>2010</v>
       </c>
       <c r="H75" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I75" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J75" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -20653,7 +20674,7 @@
         <v>-5.44166667</v>
       </c>
       <c r="W75" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="X75">
         <v>0.047986</v>

--- a/www/flightdata/xlsx/eoss-308.xlsx
+++ b/www/flightdata/xlsx/eoss-308.xlsx
@@ -2076,7 +2076,7 @@
         <v>29959.1</v>
       </c>
       <c r="I2">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-308.xlsx
+++ b/www/flightdata/xlsx/eoss-308.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="529">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>1hrs 35mins 18secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1934,10 +1964,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2049,25 +2079,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>98291</v>
@@ -2079,7 +2133,7 @@
         <v>209</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>5718</v>
@@ -2090,76 +2144,100 @@
       <c r="M2">
         <v>67.42</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.15</v>
+      </c>
+      <c r="R2">
+        <v>0.52</v>
+      </c>
+      <c r="S2">
         <v>18.68</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>8.470000000000001</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>4.63</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>2.1</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>1.15</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>0.52</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>24.45</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>11.09</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>6.61</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>3</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>31.07</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>14.09</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>30.67</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>13.91</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>99203</v>
+      </c>
+      <c r="AI2">
+        <v>30237.07</v>
+      </c>
+      <c r="AJ2">
         <v>39.6076333333</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-104.04125</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>5204</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>1586.18</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>39.422</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-103.2925</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>41.89</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>67.42</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>5151</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>1570.02</v>
       </c>
     </row>
@@ -2175,156 +2253,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>44289.28054075231</v>
@@ -2345,16 +2423,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2390,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2407,10 +2485,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>44289.28077677084</v>
@@ -2431,16 +2509,16 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="M3">
         <v>152</v>
@@ -2497,7 +2575,7 @@
         <v>0.305</v>
       </c>
       <c r="AE3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF3">
         <v>0.033333</v>
@@ -2538,10 +2616,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>44289.2812353125</v>
@@ -2562,16 +2640,16 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -2607,7 +2685,7 @@
         <v>2.96666667</v>
       </c>
       <c r="AE4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF4">
         <v>0.145556</v>
@@ -2660,10 +2738,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>44289.28146958334</v>
@@ -2684,16 +2762,16 @@
         <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M5">
         <v>27</v>
@@ -2750,7 +2828,7 @@
         <v>5.786</v>
       </c>
       <c r="AE5" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF5">
         <v>0.154167</v>
@@ -2803,10 +2881,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>44289.28192900463</v>
@@ -2827,16 +2905,16 @@
         <v>120</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M6">
         <v>66</v>
@@ -2872,7 +2950,7 @@
         <v>7.1375</v>
       </c>
       <c r="AE6" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF6">
         <v>0.073889</v>
@@ -2925,10 +3003,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>44289.28216378472</v>
@@ -2949,16 +3027,16 @@
         <v>138</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="M7">
         <v>53</v>
@@ -3015,7 +3093,7 @@
         <v>7.16283333</v>
       </c>
       <c r="AE7" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF7">
         <v>0.001389</v>
@@ -3068,10 +3146,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>44289.28227481482</v>
@@ -3092,16 +3170,16 @@
         <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -3137,7 +3215,7 @@
         <v>7.09166667</v>
       </c>
       <c r="AE8" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF8">
         <v>-0.007778</v>
@@ -3190,10 +3268,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>44289.28262090278</v>
@@ -3214,16 +3292,16 @@
         <v>180</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M9">
         <v>51</v>
@@ -3259,7 +3337,7 @@
         <v>7.20333333</v>
       </c>
       <c r="AE9" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF9">
         <v>0.012222</v>
@@ -3312,10 +3390,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>44289.28285877315</v>
@@ -3336,16 +3414,16 @@
         <v>198</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M10">
         <v>89</v>
@@ -3402,7 +3480,7 @@
         <v>7.34566667</v>
       </c>
       <c r="AE10" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF10">
         <v>0.007778</v>
@@ -3455,10 +3533,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>44289.28331505787</v>
@@ -3479,16 +3557,16 @@
         <v>240</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M11">
         <v>121</v>
@@ -3524,7 +3602,7 @@
         <v>7.25416667</v>
       </c>
       <c r="AE11" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF11">
         <v>-0.005</v>
@@ -3577,10 +3655,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>44289.28355309028</v>
@@ -3601,16 +3679,16 @@
         <v>258</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L12" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M12">
         <v>108</v>
@@ -3667,7 +3745,7 @@
         <v>7.366</v>
       </c>
       <c r="AE12" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF12">
         <v>0.006111</v>
@@ -3720,10 +3798,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>44289.28366530093</v>
@@ -3744,16 +3822,16 @@
         <v>270</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M13">
         <v>131</v>
@@ -3789,7 +3867,7 @@
         <v>7.55933333</v>
       </c>
       <c r="AE13" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF13">
         <v>0.021111</v>
@@ -3840,15 +3918,15 @@
         <v>7.819838</v>
       </c>
       <c r="AV13" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
         <v>44289.28424723379</v>
@@ -3869,16 +3947,16 @@
         <v>318</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M14">
         <v>139</v>
@@ -3935,7 +4013,7 @@
         <v>7.67083333</v>
       </c>
       <c r="AE14" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF14">
         <v>0.006111</v>
@@ -3988,10 +4066,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>44289.28494046296</v>
@@ -4012,16 +4090,16 @@
         <v>378</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M15">
         <v>123</v>
@@ -4078,7 +4156,7 @@
         <v>7.8385</v>
       </c>
       <c r="AE15" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF15">
         <v>0.009167</v>
@@ -4131,10 +4209,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>44289.28505245371</v>
@@ -4155,16 +4233,16 @@
         <v>390</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M16">
         <v>106</v>
@@ -4200,7 +4278,7 @@
         <v>7.8105</v>
       </c>
       <c r="AE16" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF16">
         <v>-0.000764</v>
@@ -4253,10 +4331,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>44289.28539890047</v>
@@ -4277,16 +4355,16 @@
         <v>420</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M17">
         <v>127</v>
@@ -4322,7 +4400,7 @@
         <v>8.03633333</v>
       </c>
       <c r="AE17" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF17">
         <v>0.024722</v>
@@ -4375,10 +4453,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>44289.28563660879</v>
@@ -4399,16 +4477,16 @@
         <v>438</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M18">
         <v>121</v>
@@ -4465,7 +4543,7 @@
         <v>8.071999999999999</v>
       </c>
       <c r="AE18" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF18">
         <v>0.001944</v>
@@ -4518,10 +4596,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>44289.28609410879</v>
@@ -4542,16 +4620,16 @@
         <v>480</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M19">
         <v>119</v>
@@ -4587,7 +4665,7 @@
         <v>8.3515</v>
       </c>
       <c r="AE19" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF19">
         <v>0.015278</v>
@@ -4640,10 +4718,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>44289.28633056713</v>
@@ -4664,16 +4742,16 @@
         <v>498</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M20">
         <v>87</v>
@@ -4730,7 +4808,7 @@
         <v>8.45316667</v>
       </c>
       <c r="AE20" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF20">
         <v>0.005556</v>
@@ -4783,10 +4861,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>44289.28644520833</v>
@@ -4807,16 +4885,16 @@
         <v>510</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M21">
         <v>25</v>
@@ -4852,7 +4930,7 @@
         <v>8.53466667</v>
       </c>
       <c r="AE21" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF21">
         <v>0.008888999999999999</v>
@@ -4905,10 +4983,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>44289.2867875463</v>
@@ -4929,16 +5007,16 @@
         <v>540</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M22">
         <v>70</v>
@@ -4974,7 +5052,7 @@
         <v>8.229333329999999</v>
       </c>
       <c r="AE22" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF22">
         <v>-0.033333</v>
@@ -5027,10 +5105,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>44289.28702484954</v>
@@ -5051,16 +5129,16 @@
         <v>558</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M23">
         <v>141</v>
@@ -5117,7 +5195,7 @@
         <v>8.402333329999999</v>
       </c>
       <c r="AE23" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF23">
         <v>0.009443999999999999</v>
@@ -5170,10 +5248,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>44289.28772012731</v>
@@ -5194,16 +5272,16 @@
         <v>618</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M24">
         <v>88</v>
@@ -5260,7 +5338,7 @@
         <v>8.513999999999999</v>
       </c>
       <c r="AE24" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF24">
         <v>0.006111</v>
@@ -5313,10 +5391,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>44289.28783434028</v>
@@ -5337,16 +5415,16 @@
         <v>630</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M25">
         <v>165</v>
@@ -5382,7 +5460,7 @@
         <v>8.524333329999999</v>
       </c>
       <c r="AE25" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF25">
         <v>0.00037</v>
@@ -5435,10 +5513,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>44289.28817766203</v>
@@ -5459,16 +5537,16 @@
         <v>660</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M26">
         <v>145</v>
@@ -5504,7 +5582,7 @@
         <v>8.36166667</v>
       </c>
       <c r="AE26" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF26">
         <v>-0.017778</v>
@@ -5557,10 +5635,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>44289.28910834491</v>
@@ -5581,16 +5659,16 @@
         <v>738</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M27">
         <v>136</v>
@@ -5647,7 +5725,7 @@
         <v>8.463333329999999</v>
       </c>
       <c r="AE27" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF27">
         <v>0.002778</v>
@@ -5700,10 +5778,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>44289.28922019676</v>
@@ -5724,16 +5802,16 @@
         <v>750</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M28">
         <v>136</v>
@@ -5769,7 +5847,7 @@
         <v>8.503888890000001</v>
       </c>
       <c r="AE28" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF28">
         <v>0.001481</v>
@@ -5822,10 +5900,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>44289.28956606481</v>
@@ -5846,16 +5924,16 @@
         <v>780</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M29">
         <v>129</v>
@@ -5891,7 +5969,7 @@
         <v>8.625666669999999</v>
       </c>
       <c r="AE29" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF29">
         <v>0.013333</v>
@@ -5944,10 +6022,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>44289.28980344907</v>
@@ -5968,16 +6046,16 @@
         <v>798</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M30">
         <v>129</v>
@@ -6034,7 +6112,7 @@
         <v>8.65116667</v>
       </c>
       <c r="AE30" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF30">
         <v>0.001389</v>
@@ -6087,10 +6165,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>44289.29049829861</v>
@@ -6111,16 +6189,16 @@
         <v>858</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M31">
         <v>106</v>
@@ -6177,7 +6255,7 @@
         <v>8.808833330000001</v>
       </c>
       <c r="AE31" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF31">
         <v>0.008611000000000001</v>
@@ -6230,10 +6308,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>44289.29060908565</v>
@@ -6254,16 +6332,16 @@
         <v>870</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M32">
         <v>77</v>
@@ -6299,7 +6377,7 @@
         <v>8.734222219999999</v>
       </c>
       <c r="AE32" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF32">
         <v>-0.002716</v>
@@ -6352,10 +6430,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>44289.29095655093</v>
@@ -6376,16 +6454,16 @@
         <v>900</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M33">
         <v>118</v>
@@ -6421,7 +6499,7 @@
         <v>8.47366667</v>
       </c>
       <c r="AE33" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF33">
         <v>-0.028519</v>
@@ -6474,10 +6552,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>44289.29119109954</v>
@@ -6498,16 +6576,16 @@
         <v>918</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M34">
         <v>114</v>
@@ -6564,7 +6642,7 @@
         <v>8.53933333</v>
       </c>
       <c r="AE34" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF34">
         <v>0.003611</v>
@@ -6617,10 +6695,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2">
         <v>44289.2918871875</v>
@@ -6641,16 +6719,16 @@
         <v>978</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M35">
         <v>108</v>
@@ -6707,7 +6785,7 @@
         <v>8.615833329999999</v>
       </c>
       <c r="AE35" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF35">
         <v>0.004167</v>
@@ -6760,10 +6838,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2">
         <v>44289.29200021991</v>
@@ -6784,16 +6862,16 @@
         <v>990</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M36">
         <v>168</v>
@@ -6829,7 +6907,7 @@
         <v>8.64611111</v>
       </c>
       <c r="AE36" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF36">
         <v>0.001111</v>
@@ -6882,10 +6960,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>44289.29234341435</v>
@@ -6906,16 +6984,16 @@
         <v>1020</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M37">
         <v>110</v>
@@ -6951,7 +7029,7 @@
         <v>8.696999999999999</v>
       </c>
       <c r="AE37" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF37">
         <v>0.005556</v>
@@ -7004,10 +7082,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>44289.29258180556</v>
@@ -7028,16 +7106,16 @@
         <v>1038</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M38">
         <v>152</v>
@@ -7094,7 +7172,7 @@
         <v>8.834</v>
       </c>
       <c r="AE38" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF38">
         <v>0.0075</v>
@@ -7147,10 +7225,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>44289.29327503472</v>
@@ -7171,16 +7249,16 @@
         <v>1098</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M39">
         <v>117</v>
@@ -7237,7 +7315,7 @@
         <v>9.012</v>
       </c>
       <c r="AE39" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF39">
         <v>0.009722</v>
@@ -7290,10 +7368,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>44289.29338480324</v>
@@ -7314,16 +7392,16 @@
         <v>1110</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M40">
         <v>70</v>
@@ -7359,7 +7437,7 @@
         <v>9.07966667</v>
       </c>
       <c r="AE40" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF40">
         <v>0.002469</v>
@@ -7412,10 +7490,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>44289.29373170139</v>
@@ -7436,16 +7514,16 @@
         <v>1140</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M41">
         <v>144</v>
@@ -7481,7 +7559,7 @@
         <v>8.696999999999999</v>
       </c>
       <c r="AE41" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF41">
         <v>-0.041852</v>
@@ -7534,10 +7612,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>44289.29397111111</v>
@@ -7558,16 +7636,16 @@
         <v>1158</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M42">
         <v>120</v>
@@ -7624,7 +7702,7 @@
         <v>8.68166667</v>
       </c>
       <c r="AE42" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF42">
         <v>-0.000833</v>
@@ -7677,10 +7755,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>44289.29410799769</v>
@@ -7701,16 +7779,16 @@
         <v>1170</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M43">
         <v>92</v>
@@ -7746,7 +7824,7 @@
         <v>8.808666669999999</v>
       </c>
       <c r="AE43" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF43">
         <v>0.013889</v>
@@ -7799,10 +7877,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>44289.29443003472</v>
@@ -7823,16 +7901,16 @@
         <v>1200</v>
       </c>
       <c r="I44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M44">
         <v>76</v>
@@ -7868,7 +7946,7 @@
         <v>9.266</v>
       </c>
       <c r="AE44" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF44">
         <v>0.05</v>
@@ -7921,10 +7999,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>44289.29466424768</v>
@@ -7945,16 +8023,16 @@
         <v>1218</v>
       </c>
       <c r="I45" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M45">
         <v>136</v>
@@ -8011,7 +8089,7 @@
         <v>9.509833329999999</v>
       </c>
       <c r="AE45" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF45">
         <v>0.013333</v>
@@ -8064,10 +8142,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>44289.29477479167</v>
@@ -8088,16 +8166,16 @@
         <v>1230</v>
       </c>
       <c r="I46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M46">
         <v>136</v>
@@ -8133,7 +8211,7 @@
         <v>8.564666669999999</v>
       </c>
       <c r="AE46" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF46">
         <v>-0.103333</v>
@@ -8186,10 +8264,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>44289.29512045139</v>
@@ -8210,16 +8288,16 @@
         <v>1260</v>
       </c>
       <c r="I47" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M47">
         <v>163</v>
@@ -8255,7 +8333,7 @@
         <v>8.97133333</v>
       </c>
       <c r="AE47" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF47">
         <v>0.044444</v>
@@ -8308,10 +8386,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>44289.29535901621</v>
@@ -8332,16 +8410,16 @@
         <v>1278</v>
       </c>
       <c r="I48" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M48">
         <v>123</v>
@@ -8398,7 +8476,7 @@
         <v>8.656333330000001</v>
       </c>
       <c r="AE48" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF48">
         <v>-0.017222</v>
@@ -8451,10 +8529,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2">
         <v>44289.29605268518</v>
@@ -8475,16 +8553,16 @@
         <v>1338</v>
       </c>
       <c r="I49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M49">
         <v>112</v>
@@ -8541,7 +8619,7 @@
         <v>8.910166670000001</v>
       </c>
       <c r="AE49" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF49">
         <v>0.013889</v>
@@ -8594,10 +8672,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>44289.29616422454</v>
@@ -8618,16 +8696,16 @@
         <v>1350</v>
       </c>
       <c r="I50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M50">
         <v>102</v>
@@ -8663,7 +8741,7 @@
         <v>9.022111110000001</v>
       </c>
       <c r="AE50" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF50">
         <v>0.004074</v>
@@ -8716,10 +8794,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>44289.29674895833</v>
@@ -8740,16 +8818,16 @@
         <v>1398</v>
       </c>
       <c r="I51" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L51" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M51">
         <v>118</v>
@@ -8806,7 +8884,7 @@
         <v>8.763</v>
       </c>
       <c r="AE51" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF51">
         <v>-0.014167</v>
@@ -8859,10 +8937,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>44289.29688769676</v>
@@ -8883,16 +8961,16 @@
         <v>1410</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M52">
         <v>133</v>
@@ -8928,7 +9006,7 @@
         <v>8.869666670000001</v>
       </c>
       <c r="AE52" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF52">
         <v>0.005833</v>
@@ -8981,10 +9059,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2">
         <v>44289.29744302083</v>
@@ -9005,16 +9083,16 @@
         <v>1458</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M53">
         <v>112</v>
@@ -9071,7 +9149,7 @@
         <v>9.647</v>
       </c>
       <c r="AE53" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF53">
         <v>0.0425</v>
@@ -9124,10 +9202,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>44289.29790137731</v>
@@ -9148,16 +9226,16 @@
         <v>1500</v>
       </c>
       <c r="I54" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M54">
         <v>104</v>
@@ -9193,7 +9271,7 @@
         <v>10.34288889</v>
       </c>
       <c r="AE54" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF54">
         <v>0.02537</v>
@@ -9246,10 +9324,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
         <v>44289.2981371412</v>
@@ -9270,16 +9348,16 @@
         <v>1518</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M55">
         <v>110</v>
@@ -9336,7 +9414,7 @@
         <v>10.87116667</v>
       </c>
       <c r="AE55" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF55">
         <v>0.028889</v>
@@ -9389,10 +9467,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>44289.29859505787</v>
@@ -9413,16 +9491,16 @@
         <v>1560</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M56">
         <v>93</v>
@@ -9458,7 +9536,7 @@
         <v>9.95166667</v>
       </c>
       <c r="AE56" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF56">
         <v>-0.050278</v>
@@ -9511,10 +9589,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2">
         <v>44289.29883195602</v>
@@ -9535,16 +9613,16 @@
         <v>1578</v>
       </c>
       <c r="I57" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L57" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M57">
         <v>94</v>
@@ -9601,7 +9679,7 @@
         <v>10.08383333</v>
       </c>
       <c r="AE57" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF57">
         <v>0.007222</v>
@@ -9654,10 +9732,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>44289.29894071759</v>
@@ -9678,16 +9756,16 @@
         <v>1590</v>
       </c>
       <c r="I58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M58">
         <v>71</v>
@@ -9723,7 +9801,7 @@
         <v>10.43433333</v>
       </c>
       <c r="AE58" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF58">
         <v>0.038333</v>
@@ -9776,10 +9854,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>44289.29928905093</v>
@@ -9800,16 +9878,16 @@
         <v>1620</v>
       </c>
       <c r="I59" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L59" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M59">
         <v>93</v>
@@ -9845,7 +9923,7 @@
         <v>9.835000000000001</v>
       </c>
       <c r="AE59" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF59">
         <v>-0.065556</v>
@@ -9898,10 +9976,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>44289.29952543981</v>
@@ -9922,16 +10000,16 @@
         <v>1638</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M60">
         <v>95</v>
@@ -9988,7 +10066,7 @@
         <v>10.13466667</v>
       </c>
       <c r="AE60" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF60">
         <v>0.016389</v>
@@ -10041,10 +10119,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>44289.29998225695</v>
@@ -10065,16 +10143,16 @@
         <v>1680</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M61">
         <v>94</v>
@@ -10110,7 +10188,7 @@
         <v>10.15483333</v>
       </c>
       <c r="AE61" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF61">
         <v>0.001111</v>
@@ -10163,10 +10241,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>44289.30022049769</v>
@@ -10187,16 +10265,16 @@
         <v>1698</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M62">
         <v>103</v>
@@ -10253,7 +10331,7 @@
         <v>9.814500000000001</v>
       </c>
       <c r="AE62" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF62">
         <v>-0.018611</v>
@@ -10306,10 +10384,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>44289.30032944444</v>
@@ -10330,16 +10408,16 @@
         <v>1710</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M63">
         <v>107</v>
@@ -10375,7 +10453,7 @@
         <v>9.92633333</v>
       </c>
       <c r="AE63" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF63">
         <v>0.012222</v>
@@ -10428,10 +10506,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>44289.3006796412</v>
@@ -10452,16 +10530,16 @@
         <v>1740</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M64">
         <v>119</v>
@@ -10497,7 +10575,7 @@
         <v>9.773999999999999</v>
       </c>
       <c r="AE64" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF64">
         <v>-0.016667</v>
@@ -10550,10 +10628,10 @@
     </row>
     <row r="65" spans="1:48">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C65" s="2">
         <v>44289.30091864584</v>
@@ -10574,16 +10652,16 @@
         <v>1758</v>
       </c>
       <c r="I65" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M65">
         <v>88</v>
@@ -10640,7 +10718,7 @@
         <v>10.3175</v>
       </c>
       <c r="AE65" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AF65">
         <v>0.029722</v>
@@ -10693,10 +10771,10 @@
     </row>
     <row r="66" spans="1:48">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>44289.30160892361</v>
@@ -10717,16 +10795,16 @@
         <v>1818</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M66">
         <v>138</v>
@@ -10783,7 +10861,7 @@
         <v>9.70783333</v>
       </c>
       <c r="AE66" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF66">
         <v>-0.033333</v>
@@ -10834,15 +10912,15 @@
         <v>8.533886000000001</v>
       </c>
       <c r="AV66" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67" spans="1:48">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>44289.30172013889</v>
@@ -10863,16 +10941,16 @@
         <v>1830</v>
       </c>
       <c r="I67" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L67" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M67">
         <v>125</v>
@@ -10908,7 +10986,7 @@
         <v>9.74677778</v>
       </c>
       <c r="AE67" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF67">
         <v>0.00142</v>
@@ -10961,10 +11039,10 @@
     </row>
     <row r="68" spans="1:48">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>44289.30230331019</v>
@@ -10985,16 +11063,16 @@
         <v>1878</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M68">
         <v>97</v>
@@ -11051,7 +11129,7 @@
         <v>7.21366667</v>
       </c>
       <c r="AE68" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF68">
         <v>-0.138519</v>
@@ -11104,10 +11182,10 @@
     </row>
     <row r="69" spans="1:48">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>44289.3024141088</v>
@@ -11128,16 +11206,16 @@
         <v>1890</v>
       </c>
       <c r="I69" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M69">
         <v>101</v>
@@ -11173,7 +11251,7 @@
         <v>6.86316667</v>
       </c>
       <c r="AE69" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF69">
         <v>-0.019167</v>
@@ -11226,10 +11304,10 @@
     </row>
     <row r="70" spans="1:48">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>44289.30299829861</v>
@@ -11250,16 +11328,16 @@
         <v>1938</v>
       </c>
       <c r="I70" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M70">
         <v>100</v>
@@ -11316,7 +11394,7 @@
         <v>5.593</v>
       </c>
       <c r="AE70" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF70">
         <v>-0.06944400000000001</v>
@@ -11369,10 +11447,10 @@
     </row>
     <row r="71" spans="1:48">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>44289.30310839121</v>
@@ -11393,16 +11471,16 @@
         <v>1950</v>
       </c>
       <c r="I71" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L71" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M71">
         <v>109</v>
@@ -11438,7 +11516,7 @@
         <v>5.50166667</v>
       </c>
       <c r="AE71" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF71">
         <v>-0.005</v>
@@ -11491,10 +11569,10 @@
     </row>
     <row r="72" spans="1:48">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>44289.30369325232</v>
@@ -11515,16 +11593,16 @@
         <v>1998</v>
       </c>
       <c r="I72" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M72">
         <v>103</v>
@@ -11581,7 +11659,7 @@
         <v>5.97416667</v>
       </c>
       <c r="AE72" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF72">
         <v>0.025833</v>
@@ -11634,10 +11712,10 @@
     </row>
     <row r="73" spans="1:48">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>44289.30383386574</v>
@@ -11658,16 +11736,16 @@
         <v>2010</v>
       </c>
       <c r="I73" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M73">
         <v>148</v>
@@ -11703,7 +11781,7 @@
         <v>7.21866667</v>
       </c>
       <c r="AE73" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF73">
         <v>0.06805600000000001</v>
@@ -11756,10 +11834,10 @@
     </row>
     <row r="74" spans="1:48">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>44289.30438799768</v>
@@ -11780,16 +11858,16 @@
         <v>2058</v>
       </c>
       <c r="I74" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M74">
         <v>108</v>
@@ -11846,7 +11924,7 @@
         <v>8.808666669999999</v>
       </c>
       <c r="AE74" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF74">
         <v>0.08694399999999999</v>
@@ -11899,10 +11977,10 @@
     </row>
     <row r="75" spans="1:48">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2">
         <v>44289.30449833333</v>
@@ -11923,16 +12001,16 @@
         <v>2070</v>
       </c>
       <c r="I75" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M75">
         <v>65</v>
@@ -11968,7 +12046,7 @@
         <v>8.285500000000001</v>
       </c>
       <c r="AE75" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF75">
         <v>-0.028611</v>
@@ -12021,10 +12099,10 @@
     </row>
     <row r="76" spans="1:48">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2">
         <v>44289.30508075232</v>
@@ -12045,16 +12123,16 @@
         <v>2118</v>
       </c>
       <c r="I76" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L76" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M76">
         <v>63</v>
@@ -12111,7 +12189,7 @@
         <v>8.356666669999999</v>
       </c>
       <c r="AE76" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF76">
         <v>0.003889</v>
@@ -12164,10 +12242,10 @@
     </row>
     <row r="77" spans="1:48">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2">
         <v>44289.30577674769</v>
@@ -12188,16 +12266,16 @@
         <v>2178</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L77" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M77">
         <v>95</v>
@@ -12254,7 +12332,7 @@
         <v>6.90366667</v>
       </c>
       <c r="AE77" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF77">
         <v>-0.079444</v>
@@ -12307,10 +12385,10 @@
     </row>
     <row r="78" spans="1:48">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C78" s="2">
         <v>44289.30588592593</v>
@@ -12331,16 +12409,16 @@
         <v>2190</v>
       </c>
       <c r="I78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L78" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M78">
         <v>130</v>
@@ -12376,7 +12454,7 @@
         <v>7.38375</v>
       </c>
       <c r="AE78" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF78">
         <v>0.013125</v>
@@ -12429,10 +12507,10 @@
     </row>
     <row r="79" spans="1:48">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C79" s="2">
         <v>44289.30647016204</v>
@@ -12453,16 +12531,16 @@
         <v>2238</v>
       </c>
       <c r="I79" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L79" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M79">
         <v>122</v>
@@ -12519,7 +12597,7 @@
         <v>7.35066667</v>
       </c>
       <c r="AE79" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF79">
         <v>-0.001806</v>
@@ -12572,10 +12650,10 @@
     </row>
     <row r="80" spans="1:48">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>44289.30716491898</v>
@@ -12596,16 +12674,16 @@
         <v>2298</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M80">
         <v>63</v>
@@ -12662,7 +12740,7 @@
         <v>7.08166667</v>
       </c>
       <c r="AE80" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF80">
         <v>-0.014722</v>
@@ -12715,10 +12793,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C81" s="2">
         <v>44289.30727484954</v>
@@ -12739,16 +12817,16 @@
         <v>2310</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M81">
         <v>97</v>
@@ -12784,7 +12862,7 @@
         <v>7.46758333</v>
       </c>
       <c r="AE81" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF81">
         <v>0.010556</v>
@@ -12837,10 +12915,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C82" s="2">
         <v>44289.30786054398</v>
@@ -12861,16 +12939,16 @@
         <v>2358</v>
       </c>
       <c r="I82" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="M82">
         <v>96</v>
@@ -12927,7 +13005,7 @@
         <v>7.305</v>
       </c>
       <c r="AE82" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF82">
         <v>-0.008888999999999999</v>
@@ -12980,10 +13058,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>44289.30797071759</v>
@@ -13004,16 +13082,16 @@
         <v>2370</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M83">
         <v>168</v>
@@ -13049,7 +13127,7 @@
         <v>8.01633333</v>
       </c>
       <c r="AE83" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF83">
         <v>0.038889</v>
@@ -13102,10 +13180,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>44289.30855472222</v>
@@ -13126,16 +13204,16 @@
         <v>2418</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M84">
         <v>115</v>
@@ -13192,7 +13270,7 @@
         <v>8.43783333</v>
       </c>
       <c r="AE84" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF84">
         <v>0.023056</v>
@@ -13245,10 +13323,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>44289.30866436342</v>
@@ -13269,16 +13347,16 @@
         <v>2430</v>
       </c>
       <c r="I85" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M85">
         <v>190</v>
@@ -13314,7 +13392,7 @@
         <v>7.29983333</v>
       </c>
       <c r="AE85" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF85">
         <v>-0.062222</v>
@@ -13367,10 +13445,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>44289.30900952547</v>
@@ -13391,16 +13469,16 @@
         <v>2460</v>
       </c>
       <c r="I86" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M86">
         <v>205</v>
@@ -13436,7 +13514,7 @@
         <v>5.842</v>
       </c>
       <c r="AE86" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF86">
         <v>-0.159444</v>
@@ -13489,10 +13567,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2">
         <v>44289.30924861111</v>
@@ -13513,16 +13591,16 @@
         <v>2478</v>
       </c>
       <c r="I87" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L87" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M87">
         <v>117</v>
@@ -13579,7 +13657,7 @@
         <v>5.964</v>
       </c>
       <c r="AE87" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF87">
         <v>0.006667</v>
@@ -13632,10 +13710,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C88" s="2">
         <v>44289.30970675926</v>
@@ -13656,16 +13734,16 @@
         <v>2520</v>
       </c>
       <c r="I88" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M88">
         <v>187</v>
@@ -13701,7 +13779,7 @@
         <v>6.49733333</v>
       </c>
       <c r="AE88" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF88">
         <v>0.029167</v>
@@ -13754,10 +13832,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C89" s="2">
         <v>44289.30994333333</v>
@@ -13778,16 +13856,16 @@
         <v>2538</v>
       </c>
       <c r="I89" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M89">
         <v>118</v>
@@ -13844,7 +13922,7 @@
         <v>6.44133333</v>
       </c>
       <c r="AE89" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF89">
         <v>-0.003056</v>
@@ -13897,10 +13975,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>44289.31005087963</v>
@@ -13921,16 +13999,16 @@
         <v>2550</v>
       </c>
       <c r="I90" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M90">
         <v>153</v>
@@ -13966,7 +14044,7 @@
         <v>6.23833333</v>
       </c>
       <c r="AE90" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF90">
         <v>-0.022222</v>
@@ -14019,10 +14097,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>44289.31039877314</v>
@@ -14043,16 +14121,16 @@
         <v>2580</v>
       </c>
       <c r="I91" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="M91">
         <v>171</v>
@@ -14088,7 +14166,7 @@
         <v>6.76666667</v>
       </c>
       <c r="AE91" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF91">
         <v>0.057778</v>
@@ -14141,10 +14219,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2">
         <v>44289.31063765047</v>
@@ -14165,16 +14243,16 @@
         <v>2598</v>
       </c>
       <c r="I92" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="M92">
         <v>150</v>
@@ -14231,7 +14309,7 @@
         <v>6.61416667</v>
       </c>
       <c r="AE92" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF92">
         <v>-0.008333</v>
@@ -14284,10 +14362,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>44289.31133126158</v>
@@ -14308,16 +14386,16 @@
         <v>2658</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L93" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M93">
         <v>134</v>
@@ -14374,7 +14452,7 @@
         <v>6.49733333</v>
       </c>
       <c r="AE93" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF93">
         <v>-0.006389</v>
@@ -14427,10 +14505,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>44289.31144152777</v>
@@ -14451,16 +14529,16 @@
         <v>2670</v>
       </c>
       <c r="I94" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L94" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M94">
         <v>182</v>
@@ -14496,7 +14574,7 @@
         <v>6.39066667</v>
       </c>
       <c r="AE94" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF94">
         <v>-0.003889</v>
@@ -14549,10 +14627,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>44289.3117890162</v>
@@ -14573,16 +14651,16 @@
         <v>2700</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L95" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="M95">
         <v>170</v>
@@ -14618,7 +14696,7 @@
         <v>6.035</v>
       </c>
       <c r="AE95" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF95">
         <v>-0.038889</v>
@@ -14671,10 +14749,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C96" s="2">
         <v>44289.31202645833</v>
@@ -14695,16 +14773,16 @@
         <v>2718</v>
       </c>
       <c r="I96" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M96">
         <v>112</v>
@@ -14761,7 +14839,7 @@
         <v>5.78616667</v>
       </c>
       <c r="AE96" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF96">
         <v>-0.013611</v>
@@ -14814,10 +14892,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>44289.31248106482</v>
@@ -14838,16 +14916,16 @@
         <v>2760</v>
       </c>
       <c r="I97" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L97" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M97">
         <v>143</v>
@@ -14883,7 +14961,7 @@
         <v>5.4965</v>
       </c>
       <c r="AE97" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF97">
         <v>-0.015833</v>
@@ -14936,10 +15014,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C98" s="2">
         <v>44289.31272116898</v>
@@ -14960,16 +15038,16 @@
         <v>2778</v>
       </c>
       <c r="I98" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L98" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M98">
         <v>98</v>
@@ -15026,7 +15104,7 @@
         <v>5.88266667</v>
       </c>
       <c r="AE98" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF98">
         <v>0.021111</v>
@@ -15079,10 +15157,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>44289.31283771991</v>
@@ -15103,16 +15181,16 @@
         <v>2790</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L99" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M99">
         <v>121</v>
@@ -15148,7 +15226,7 @@
         <v>6.50233333</v>
       </c>
       <c r="AE99" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF99">
         <v>0.067778</v>
@@ -15201,10 +15279,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C100" s="2">
         <v>44289.3131762037</v>
@@ -15225,16 +15303,16 @@
         <v>2820</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="M100">
         <v>136</v>
@@ -15270,7 +15348,7 @@
         <v>9.10333333</v>
       </c>
       <c r="AE100" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF100">
         <v>0.284444</v>
@@ -15323,10 +15401,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C101" s="2">
         <v>44289.31341512731</v>
@@ -15347,16 +15425,16 @@
         <v>2838</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M101">
         <v>120</v>
@@ -15413,7 +15491,7 @@
         <v>8.46833333</v>
       </c>
       <c r="AE101" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF101">
         <v>-0.034722</v>
@@ -15466,10 +15544,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C102" s="2">
         <v>44289.31352519676</v>
@@ -15490,16 +15568,16 @@
         <v>2850</v>
       </c>
       <c r="I102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L102" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M102">
         <v>134</v>
@@ -15535,7 +15613,7 @@
         <v>8.24</v>
       </c>
       <c r="AE102" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF102">
         <v>-0.025</v>
@@ -15588,10 +15666,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2">
         <v>44289.31387267361</v>
@@ -15612,16 +15690,16 @@
         <v>2880</v>
       </c>
       <c r="I103" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M103">
         <v>114</v>
@@ -15657,7 +15735,7 @@
         <v>8.02633333</v>
       </c>
       <c r="AE103" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF103">
         <v>-0.023333</v>
@@ -15710,10 +15788,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C104" s="2">
         <v>44289.31411021991</v>
@@ -15734,16 +15812,16 @@
         <v>2898</v>
       </c>
       <c r="I104" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M104">
         <v>108</v>
@@ -15800,7 +15878,7 @@
         <v>7.6555</v>
       </c>
       <c r="AE104" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF104">
         <v>-0.020278</v>
@@ -15853,10 +15931,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C105" s="2">
         <v>44289.31422042824</v>
@@ -15877,16 +15955,16 @@
         <v>2910</v>
       </c>
       <c r="I105" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M105">
         <v>111</v>
@@ -15922,7 +16000,7 @@
         <v>7.10166667</v>
       </c>
       <c r="AE105" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF105">
         <v>-0.060556</v>
@@ -15975,10 +16053,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C106" s="2">
         <v>44289.31456719907</v>
@@ -15999,16 +16077,16 @@
         <v>2940</v>
       </c>
       <c r="I106" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M106">
         <v>96</v>
@@ -16044,7 +16122,7 @@
         <v>6.34</v>
       </c>
       <c r="AE106" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF106">
         <v>-0.083333</v>
@@ -16097,10 +16175,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C107" s="2">
         <v>44289.31480430556</v>
@@ -16121,16 +16199,16 @@
         <v>2958</v>
       </c>
       <c r="I107" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="M107">
         <v>110</v>
@@ -16187,7 +16265,7 @@
         <v>6.3145</v>
       </c>
       <c r="AE107" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF107">
         <v>-0.001389</v>
@@ -16240,10 +16318,10 @@
     </row>
     <row r="108" spans="1:47">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C108" s="2">
         <v>44289.31549835648</v>
@@ -16264,16 +16342,16 @@
         <v>3018</v>
       </c>
       <c r="I108" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L108" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M108">
         <v>116</v>
@@ -16330,7 +16408,7 @@
         <v>5.10533333</v>
       </c>
       <c r="AE108" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF108">
         <v>-0.066111</v>
@@ -16383,10 +16461,10 @@
     </row>
     <row r="109" spans="1:47">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C109" s="2">
         <v>44289.31561175926</v>
@@ -16407,16 +16485,16 @@
         <v>3030</v>
       </c>
       <c r="I109" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L109" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M109">
         <v>92</v>
@@ -16452,7 +16530,7 @@
         <v>5.35433333</v>
       </c>
       <c r="AE109" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF109">
         <v>0.009074</v>
@@ -16505,10 +16583,10 @@
     </row>
     <row r="110" spans="1:47">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2">
         <v>44289.31595774306</v>
@@ -16529,16 +16607,16 @@
         <v>3060</v>
       </c>
       <c r="I110" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L110" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="M110">
         <v>83</v>
@@ -16574,7 +16652,7 @@
         <v>5.66933333</v>
       </c>
       <c r="AE110" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF110">
         <v>0.034444</v>
@@ -16627,10 +16705,10 @@
     </row>
     <row r="111" spans="1:47">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C111" s="2">
         <v>44289.31619278935</v>
@@ -16651,16 +16729,16 @@
         <v>3078</v>
       </c>
       <c r="I111" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L111" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M111">
         <v>90</v>
@@ -16717,7 +16795,7 @@
         <v>5.91816667</v>
       </c>
       <c r="AE111" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF111">
         <v>0.013611</v>
@@ -16770,10 +16848,10 @@
     </row>
     <row r="112" spans="1:47">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2">
         <v>44289.31630166667</v>
@@ -16794,16 +16872,16 @@
         <v>3090</v>
       </c>
       <c r="I112" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M112">
         <v>70</v>
@@ -16839,7 +16917,7 @@
         <v>6.47166667</v>
       </c>
       <c r="AE112" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF112">
         <v>0.060556</v>
@@ -16892,10 +16970,10 @@
     </row>
     <row r="113" spans="1:47">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C113" s="2">
         <v>44289.3168882176</v>
@@ -16916,16 +16994,16 @@
         <v>3138</v>
       </c>
       <c r="I113" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L113" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="M113">
         <v>98</v>
@@ -16982,7 +17060,7 @@
         <v>7.24416667</v>
       </c>
       <c r="AE113" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF113">
         <v>0.042222</v>
@@ -17035,10 +17113,10 @@
     </row>
     <row r="114" spans="1:47">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C114" s="2">
         <v>44289.31699675926</v>
@@ -17059,16 +17137,16 @@
         <v>3150</v>
       </c>
       <c r="I114" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L114" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M114">
         <v>88</v>
@@ -17104,7 +17182,7 @@
         <v>7.51333333</v>
       </c>
       <c r="AE114" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF114">
         <v>0.014722</v>
@@ -17157,10 +17235,10 @@
     </row>
     <row r="115" spans="1:47">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2">
         <v>44289.31734570602</v>
@@ -17181,16 +17259,16 @@
         <v>3180</v>
       </c>
       <c r="I115" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="L115" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="M115">
         <v>103</v>
@@ -17226,7 +17304,7 @@
         <v>7.97566667</v>
       </c>
       <c r="AE115" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF115">
         <v>0.050556</v>
@@ -17279,10 +17357,10 @@
     </row>
     <row r="116" spans="1:47">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C116" s="2">
         <v>44289.3175825463</v>
@@ -17303,16 +17381,16 @@
         <v>3198</v>
       </c>
       <c r="I116" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L116" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M116">
         <v>97</v>
@@ -17369,7 +17447,7 @@
         <v>8.051833329999999</v>
       </c>
       <c r="AE116" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF116">
         <v>0.004167</v>
@@ -17422,10 +17500,10 @@
     </row>
     <row r="117" spans="1:47">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C117" s="2">
         <v>44289.31803774305</v>
@@ -17446,16 +17524,16 @@
         <v>3240</v>
       </c>
       <c r="I117" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L117" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M117">
         <v>86</v>
@@ -17491,7 +17569,7 @@
         <v>7.53366667</v>
       </c>
       <c r="AE117" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF117">
         <v>-0.028333</v>
@@ -17544,10 +17622,10 @@
     </row>
     <row r="118" spans="1:47">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C118" s="2">
         <v>44289.31827712963</v>
@@ -17568,16 +17646,16 @@
         <v>3258</v>
       </c>
       <c r="I118" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L118" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="M118">
         <v>94</v>
@@ -17634,7 +17712,7 @@
         <v>7.2695</v>
       </c>
       <c r="AE118" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF118">
         <v>-0.014444</v>
@@ -17687,10 +17765,10 @@
     </row>
     <row r="119" spans="1:47">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C119" s="2">
         <v>44289.31838730324</v>
@@ -17711,16 +17789,16 @@
         <v>3270</v>
       </c>
       <c r="I119" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="M119">
         <v>99</v>
@@ -17756,7 +17834,7 @@
         <v>7.16266667</v>
       </c>
       <c r="AE119" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF119">
         <v>-0.011667</v>
@@ -17809,10 +17887,10 @@
     </row>
     <row r="120" spans="1:47">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C120" s="2">
         <v>44289.31873393519</v>
@@ -17833,16 +17911,16 @@
         <v>3300</v>
       </c>
       <c r="I120" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J120" t="b">
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L120" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="M120">
         <v>114</v>
@@ -17878,7 +17956,7 @@
         <v>6.83766667</v>
       </c>
       <c r="AE120" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF120">
         <v>-0.035556</v>
@@ -17931,10 +18009,10 @@
     </row>
     <row r="121" spans="1:47">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C121" s="2">
         <v>44289.31897037037</v>
@@ -17955,16 +18033,16 @@
         <v>3318</v>
       </c>
       <c r="I121" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J121" t="b">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L121" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M121">
         <v>103</v>
@@ -18021,7 +18099,7 @@
         <v>6.93416667</v>
       </c>
       <c r="AE121" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF121">
         <v>0.005278</v>
@@ -18074,10 +18152,10 @@
     </row>
     <row r="122" spans="1:47">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C122" s="2">
         <v>44289.31942747685</v>
@@ -18098,16 +18176,16 @@
         <v>3360</v>
       </c>
       <c r="I122" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="L122" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M122">
         <v>110</v>
@@ -18143,7 +18221,7 @@
         <v>6.599</v>
       </c>
       <c r="AE122" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF122">
         <v>-0.018333</v>
@@ -18196,10 +18274,10 @@
     </row>
     <row r="123" spans="1:47">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C123" s="2">
         <v>44289.31966621528</v>
@@ -18220,16 +18298,16 @@
         <v>3378</v>
       </c>
       <c r="I123" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="M123">
         <v>99</v>
@@ -18286,7 +18364,7 @@
         <v>6.48716667</v>
       </c>
       <c r="AE123" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF123">
         <v>-0.006111</v>
@@ -18339,10 +18417,10 @@
     </row>
     <row r="124" spans="1:47">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C124" s="2">
         <v>44289.31977466435</v>
@@ -18363,16 +18441,16 @@
         <v>3390</v>
       </c>
       <c r="I124" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L124" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M124">
         <v>99</v>
@@ -18408,7 +18486,7 @@
         <v>6.26866667</v>
       </c>
       <c r="AE124" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF124">
         <v>-0.023889</v>
@@ -18461,10 +18539,10 @@
     </row>
     <row r="125" spans="1:47">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C125" s="2">
         <v>44289.32012114584</v>
@@ -18485,16 +18563,16 @@
         <v>3420</v>
       </c>
       <c r="I125" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L125" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="M125">
         <v>113</v>
@@ -18530,7 +18608,7 @@
         <v>5.80133333</v>
       </c>
       <c r="AE125" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF125">
         <v>-0.051111</v>
@@ -18583,10 +18661,10 @@
     </row>
     <row r="126" spans="1:47">
       <c r="A126" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C126" s="2">
         <v>44289.32035984954</v>
@@ -18607,16 +18685,16 @@
         <v>3438</v>
       </c>
       <c r="I126" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L126" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="M126">
         <v>101</v>
@@ -18673,7 +18751,7 @@
         <v>5.847</v>
       </c>
       <c r="AE126" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF126">
         <v>0.0025</v>
@@ -18726,10 +18804,10 @@
     </row>
     <row r="127" spans="1:47">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C127" s="2">
         <v>44289.32081715278</v>
@@ -18750,16 +18828,16 @@
         <v>3480</v>
       </c>
       <c r="I127" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L127" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M127">
         <v>97</v>
@@ -18795,7 +18873,7 @@
         <v>6.18233333</v>
       </c>
       <c r="AE127" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF127">
         <v>0.018333</v>
@@ -18848,10 +18926,10 @@
     </row>
     <row r="128" spans="1:47">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B128" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C128" s="2">
         <v>44289.32105385417</v>
@@ -18872,16 +18950,16 @@
         <v>3498</v>
       </c>
       <c r="I128" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="L128" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="M128">
         <v>101</v>
@@ -18938,7 +19016,7 @@
         <v>6.538</v>
       </c>
       <c r="AE128" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF128">
         <v>0.019444</v>
@@ -18991,10 +19069,10 @@
     </row>
     <row r="129" spans="1:47">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C129" s="2">
         <v>44289.32116510416</v>
@@ -19015,16 +19093,16 @@
         <v>3510</v>
       </c>
       <c r="I129" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L129" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="M129">
         <v>83</v>
@@ -19060,7 +19138,7 @@
         <v>6.93933333</v>
       </c>
       <c r="AE129" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF129">
         <v>0.043889</v>
@@ -19113,10 +19191,10 @@
     </row>
     <row r="130" spans="1:47">
       <c r="A130" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C130" s="2">
         <v>44289.32151105324</v>
@@ -19137,16 +19215,16 @@
         <v>3540</v>
       </c>
       <c r="I130" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="L130" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M130">
         <v>114</v>
@@ -19182,7 +19260,7 @@
         <v>7.46766667</v>
       </c>
       <c r="AE130" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF130">
         <v>0.057778</v>
@@ -19235,10 +19313,10 @@
     </row>
     <row r="131" spans="1:47">
       <c r="A131" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B131" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C131" s="2">
         <v>44289.32174909722</v>
@@ -19259,16 +19337,16 @@
         <v>3558</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="L131" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M131">
         <v>101</v>
@@ -19325,7 +19403,7 @@
         <v>7.2695</v>
       </c>
       <c r="AE131" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF131">
         <v>-0.010833</v>
@@ -19378,10 +19456,10 @@
     </row>
     <row r="132" spans="1:47">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C132" s="2">
         <v>44289.32185712963</v>
@@ -19402,16 +19480,16 @@
         <v>3570</v>
       </c>
       <c r="I132" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="L132" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="M132">
         <v>108</v>
@@ -19447,7 +19525,7 @@
         <v>7.13233333</v>
       </c>
       <c r="AE132" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF132">
         <v>-0.015</v>
@@ -19500,10 +19578,10 @@
     </row>
     <row r="133" spans="1:47">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B133" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C133" s="2">
         <v>44289.32244366898</v>
@@ -19524,16 +19602,16 @@
         <v>3618</v>
       </c>
       <c r="I133" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L133" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M133">
         <v>94</v>
@@ -19590,7 +19668,7 @@
         <v>6.64966667</v>
       </c>
       <c r="AE133" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF133">
         <v>-0.026389</v>
@@ -19643,10 +19721,10 @@
     </row>
     <row r="134" spans="1:47">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C134" s="2">
         <v>44289.32255368055</v>
@@ -19667,16 +19745,16 @@
         <v>3630</v>
       </c>
       <c r="I134" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L134" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M134">
         <v>97</v>
@@ -19712,7 +19790,7 @@
         <v>6.46683333</v>
       </c>
       <c r="AE134" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF134">
         <v>-0.01</v>
@@ -19765,10 +19843,10 @@
     </row>
     <row r="135" spans="1:47">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B135" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C135" s="2">
         <v>44289.32289793981</v>
@@ -19789,16 +19867,16 @@
         <v>3660</v>
       </c>
       <c r="I135" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="L135" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M135">
         <v>99</v>
@@ -19834,7 +19912,7 @@
         <v>5.74033333</v>
       </c>
       <c r="AE135" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF135">
         <v>-0.079444</v>
@@ -19887,10 +19965,10 @@
     </row>
     <row r="136" spans="1:47">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B136" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C136" s="2">
         <v>44289.32313953704</v>
@@ -19911,16 +19989,16 @@
         <v>3678</v>
       </c>
       <c r="I136" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L136" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="M136">
         <v>97</v>
@@ -19977,7 +20055,7 @@
         <v>5.73033333</v>
       </c>
       <c r="AE136" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AF136">
         <v>-0.000556</v>
@@ -20040,156 +20118,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>44289.323943125</v>
@@ -20210,16 +20288,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="M2">
         <v>88</v>
@@ -20255,7 +20333,7 @@
         <v>-6.33644444</v>
       </c>
       <c r="AE2" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AG2">
         <v>-20.788889</v>
@@ -20272,10 +20350,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>44289.32420905092</v>
@@ -20296,16 +20374,16 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="M3">
         <v>108</v>
@@ -20362,7 +20440,7 @@
         <v>-17.86133333</v>
       </c>
       <c r="AE3" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF3">
         <v>-0.420123</v>
@@ -20403,10 +20481,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>44289.32428706018</v>
@@ -20427,16 +20505,16 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="L4" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="M4">
         <v>103</v>
@@ -20472,7 +20550,7 @@
         <v>-47.64033333</v>
       </c>
       <c r="AE4" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF4">
         <v>-3.256667</v>
@@ -20525,10 +20603,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>44289.32452712963</v>
@@ -20549,16 +20627,16 @@
         <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="L5" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="M5">
         <v>106</v>
@@ -20615,7 +20693,7 @@
         <v>-44.30766667</v>
       </c>
       <c r="AE5" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF5">
         <v>0.364444</v>
@@ -20668,10 +20746,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>44289.32463643519</v>
@@ -20692,16 +20770,16 @@
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="L6" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="M6">
         <v>67</v>
@@ -20737,7 +20815,7 @@
         <v>-42.52966667</v>
       </c>
       <c r="AE6" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF6">
         <v>0.194444</v>
@@ -20790,10 +20868,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>44289.32485122685</v>
@@ -20814,16 +20892,16 @@
         <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="L7" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="M7">
         <v>94</v>
@@ -20880,7 +20958,7 @@
         <v>-39.675</v>
       </c>
       <c r="AE7" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF7">
         <v>0.312222</v>
@@ -20933,10 +21011,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>44289.32522667824</v>
@@ -20957,16 +21035,16 @@
         <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L8" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="M8">
         <v>118</v>
@@ -21023,7 +21101,7 @@
         <v>-36.35233333</v>
       </c>
       <c r="AE8" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF8">
         <v>0.363333</v>
@@ -21076,10 +21154,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>44289.32533144676</v>
@@ -21100,16 +21178,16 @@
         <v>120</v>
       </c>
       <c r="I9" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L9" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="M9">
         <v>110</v>
@@ -21145,7 +21223,7 @@
         <v>-36.94183333</v>
       </c>
       <c r="AE9" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF9">
         <v>-0.032222</v>
@@ -21198,10 +21276,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>44289.32567565973</v>
@@ -21222,16 +21300,16 @@
         <v>150</v>
       </c>
       <c r="I10" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="L10" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="M10">
         <v>103</v>
@@ -21267,7 +21345,7 @@
         <v>-33.39566667</v>
       </c>
       <c r="AE10" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF10">
         <v>0.387778</v>
@@ -21320,10 +21398,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>44289.32591612269</v>
@@ -21344,16 +21422,16 @@
         <v>168</v>
       </c>
       <c r="I11" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L11" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="M11">
         <v>107</v>
@@ -21410,7 +21488,7 @@
         <v>-32.67966667</v>
       </c>
       <c r="AE11" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF11">
         <v>0.039167</v>
@@ -21463,10 +21541,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>44289.32637018518</v>
@@ -21487,16 +21565,16 @@
         <v>210</v>
       </c>
       <c r="I12" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="L12" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M12">
         <v>180</v>
@@ -21532,7 +21610,7 @@
         <v>-28.2905</v>
       </c>
       <c r="AE12" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF12">
         <v>0.24</v>
@@ -21585,10 +21663,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>44289.32664009259</v>
@@ -21609,16 +21687,16 @@
         <v>228</v>
       </c>
       <c r="I13" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="L13" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="M13">
         <v>118</v>
@@ -21675,7 +21753,7 @@
         <v>-27.24916667</v>
       </c>
       <c r="AE13" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF13">
         <v>0.056944</v>
@@ -21728,10 +21806,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>44289.32672039352</v>
@@ -21752,16 +21830,16 @@
         <v>240</v>
       </c>
       <c r="I14" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L14" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M14">
         <v>61</v>
@@ -21797,7 +21875,7 @@
         <v>-26.904</v>
       </c>
       <c r="AE14" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF14">
         <v>0.037778</v>
@@ -21850,10 +21928,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>44289.32699259259</v>
@@ -21874,16 +21952,16 @@
         <v>258</v>
       </c>
       <c r="I15" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="L15" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -21940,7 +22018,7 @@
         <v>-26.111</v>
       </c>
       <c r="AE15" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF15">
         <v>0.08666699999999999</v>
@@ -21993,10 +22071,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>44289.32706525463</v>
@@ -22017,16 +22095,16 @@
         <v>270</v>
       </c>
       <c r="I16" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L16" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M16">
         <v>50</v>
@@ -22062,7 +22140,7 @@
         <v>-25.471</v>
       </c>
       <c r="AE16" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF16">
         <v>0.07000000000000001</v>
@@ -22115,10 +22193,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2">
         <v>44289.32730726852</v>
@@ -22139,16 +22217,16 @@
         <v>288</v>
       </c>
       <c r="I17" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="L17" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="M17">
         <v>67</v>
@@ -22205,7 +22283,7 @@
         <v>-24.709</v>
       </c>
       <c r="AE17" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF17">
         <v>0.083333</v>
@@ -22258,10 +22336,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>44289.3274146412</v>
@@ -22282,16 +22360,16 @@
         <v>300</v>
       </c>
       <c r="I18" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L18" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M18">
         <v>117</v>
@@ -22327,7 +22405,7 @@
         <v>-24.23166667</v>
       </c>
       <c r="AE18" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF18">
         <v>0.052222</v>
@@ -22380,10 +22458,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>44289.32800023148</v>
@@ -22404,16 +22482,16 @@
         <v>348</v>
       </c>
       <c r="I19" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L19" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="M19">
         <v>132</v>
@@ -22470,7 +22548,7 @@
         <v>-22.5095</v>
       </c>
       <c r="AE19" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF19">
         <v>0.094167</v>
@@ -22523,10 +22601,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>44289.32810972222</v>
@@ -22547,16 +22625,16 @@
         <v>360</v>
       </c>
       <c r="I20" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L20" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="M20">
         <v>125</v>
@@ -22592,7 +22670,7 @@
         <v>-21.93533333</v>
       </c>
       <c r="AE20" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF20">
         <v>0.031389</v>
@@ -22645,10 +22723,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>44289.32845418982</v>
@@ -22669,16 +22747,16 @@
         <v>390</v>
       </c>
       <c r="I21" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L21" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="M21">
         <v>102</v>
@@ -22714,7 +22792,7 @@
         <v>-20.03566667</v>
       </c>
       <c r="AE21" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF21">
         <v>0.207778</v>
@@ -22767,10 +22845,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>44289.32869456019</v>
@@ -22791,16 +22869,16 @@
         <v>408</v>
       </c>
       <c r="I22" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L22" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="M22">
         <v>107</v>
@@ -22857,7 +22935,7 @@
         <v>-19.63433333</v>
       </c>
       <c r="AE22" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF22">
         <v>0.021944</v>
@@ -22910,10 +22988,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>44289.32938958333</v>
@@ -22934,16 +23012,16 @@
         <v>468</v>
       </c>
       <c r="I23" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L23" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M23">
         <v>114</v>
@@ -23000,7 +23078,7 @@
         <v>-17.54616667</v>
       </c>
       <c r="AE23" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF23">
         <v>0.114167</v>
@@ -23053,10 +23131,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>44289.32949666667</v>
@@ -23077,16 +23155,16 @@
         <v>480</v>
       </c>
       <c r="I24" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L24" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M24">
         <v>102</v>
@@ -23122,7 +23200,7 @@
         <v>-17.71566667</v>
       </c>
       <c r="AE24" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF24">
         <v>-0.006173</v>
@@ -23175,10 +23253,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>44289.32984449074</v>
@@ -23199,16 +23277,16 @@
         <v>510</v>
       </c>
       <c r="I25" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L25" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M25">
         <v>114</v>
@@ -23244,7 +23322,7 @@
         <v>-16.53033333</v>
       </c>
       <c r="AE25" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF25">
         <v>0.12963</v>
@@ -23297,10 +23375,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>44289.33008274306</v>
@@ -23321,16 +23399,16 @@
         <v>528</v>
       </c>
       <c r="I26" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L26" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M26">
         <v>98</v>
@@ -23387,7 +23465,7 @@
         <v>-16.47966667</v>
       </c>
       <c r="AE26" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF26">
         <v>0.002778</v>
@@ -23440,10 +23518,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>44289.33053688658</v>
@@ -23464,16 +23542,16 @@
         <v>570</v>
       </c>
       <c r="I27" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L27" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M27">
         <v>95</v>
@@ -23509,7 +23587,7 @@
         <v>-15.66666667</v>
       </c>
       <c r="AE27" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF27">
         <v>0.044444</v>
@@ -23562,10 +23640,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>44289.33077887732</v>
@@ -23586,16 +23664,16 @@
         <v>588</v>
       </c>
       <c r="I28" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L28" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M28">
         <v>99</v>
@@ -23652,7 +23730,7 @@
         <v>-15.09266667</v>
       </c>
       <c r="AE28" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF28">
         <v>0.031389</v>
@@ -23705,10 +23783,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>44289.33088658565</v>
@@ -23729,16 +23807,16 @@
         <v>600</v>
       </c>
       <c r="I29" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L29" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M29">
         <v>83</v>
@@ -23774,7 +23852,7 @@
         <v>-14.93533333</v>
       </c>
       <c r="AE29" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF29">
         <v>0.017222</v>
@@ -23827,10 +23905,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>44289.33147219908</v>
@@ -23851,16 +23929,16 @@
         <v>648</v>
       </c>
       <c r="I30" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L30" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -23917,7 +23995,7 @@
         <v>-13.95466667</v>
       </c>
       <c r="AE30" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF30">
         <v>0.053611</v>
@@ -23970,10 +24048,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>44289.3321668287</v>
@@ -23994,16 +24072,16 @@
         <v>708</v>
       </c>
       <c r="I31" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="L31" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M31">
         <v>130</v>
@@ -24060,7 +24138,7 @@
         <v>-13.462</v>
       </c>
       <c r="AE31" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF31">
         <v>0.026944</v>
@@ -24113,10 +24191,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>44289.33286096065</v>
@@ -24137,16 +24215,16 @@
         <v>768</v>
       </c>
       <c r="I32" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="L32" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M32">
         <v>147</v>
@@ -24203,7 +24281,7 @@
         <v>-12.30883333</v>
       </c>
       <c r="AE32" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF32">
         <v>0.063056</v>
@@ -24256,10 +24334,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>44289.33300252315</v>
@@ -24280,16 +24358,16 @@
         <v>780</v>
       </c>
       <c r="I33" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="L33" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M33">
         <v>112</v>
@@ -24325,7 +24403,7 @@
         <v>-12.99633333</v>
       </c>
       <c r="AE33" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF33">
         <v>-0.012531</v>
@@ -24378,10 +24456,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>44289.33355666666</v>
@@ -24402,16 +24480,16 @@
         <v>828</v>
       </c>
       <c r="I34" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L34" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M34">
         <v>124</v>
@@ -24468,7 +24546,7 @@
         <v>-11.806</v>
       </c>
       <c r="AE34" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF34">
         <v>0.065093</v>
@@ -24521,10 +24599,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>44289.33366600695</v>
@@ -24545,16 +24623,16 @@
         <v>840</v>
       </c>
       <c r="I35" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L35" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M35">
         <v>143</v>
@@ -24590,7 +24668,7 @@
         <v>-11.80083333</v>
       </c>
       <c r="AE35" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF35">
         <v>0.000278</v>
@@ -24643,10 +24721,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>44289.334250625</v>
@@ -24667,16 +24745,16 @@
         <v>888</v>
       </c>
       <c r="I36" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="L36" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M36">
         <v>146</v>
@@ -24733,7 +24811,7 @@
         <v>-11.43</v>
       </c>
       <c r="AE36" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF36">
         <v>0.020278</v>
@@ -24786,10 +24864,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>44289.33438798611</v>
@@ -24810,16 +24888,16 @@
         <v>900</v>
       </c>
       <c r="I37" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L37" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M37">
         <v>119</v>
@@ -24855,7 +24933,7 @@
         <v>-11.2725</v>
       </c>
       <c r="AE37" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF37">
         <v>0.008611000000000001</v>
@@ -24908,10 +24986,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>44289.33494449074</v>
@@ -24932,16 +25010,16 @@
         <v>948</v>
       </c>
       <c r="I38" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="L38" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M38">
         <v>134</v>
@@ -24998,7 +25076,7 @@
         <v>-10.99316667</v>
       </c>
       <c r="AE38" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF38">
         <v>0.015278</v>
@@ -25051,10 +25129,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>44289.33563971065</v>
@@ -25075,16 +25153,16 @@
         <v>1008</v>
       </c>
       <c r="I39" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="L39" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M39">
         <v>130</v>
@@ -25141,7 +25219,7 @@
         <v>-10.673</v>
       </c>
       <c r="AE39" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF39">
         <v>0.0175</v>
@@ -25194,10 +25272,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>44289.33574947916</v>
@@ -25218,16 +25296,16 @@
         <v>1020</v>
       </c>
       <c r="I40" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L40" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M40">
         <v>63</v>
@@ -25263,7 +25341,7 @@
         <v>-10.77466667</v>
       </c>
       <c r="AE40" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF40">
         <v>-0.002778</v>
@@ -25316,10 +25394,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>44289.33609668982</v>
@@ -25340,16 +25418,16 @@
         <v>1050</v>
       </c>
       <c r="I41" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L41" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M41">
         <v>93</v>
@@ -25385,7 +25463,7 @@
         <v>-10.00766667</v>
       </c>
       <c r="AE41" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF41">
         <v>0.08388900000000001</v>
@@ -25438,10 +25516,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>44289.33633015047</v>
@@ -25462,16 +25540,16 @@
         <v>1068</v>
       </c>
       <c r="I42" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M42">
         <v>116</v>
@@ -25528,7 +25606,7 @@
         <v>-10.04816667</v>
       </c>
       <c r="AE42" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF42">
         <v>-0.002222</v>
@@ -25581,10 +25659,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>44289.33643967593</v>
@@ -25605,16 +25683,16 @@
         <v>1080</v>
       </c>
       <c r="I43" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="L43" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M43">
         <v>75</v>
@@ -25650,7 +25728,7 @@
         <v>-9.86533333</v>
       </c>
       <c r="AE43" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF43">
         <v>0.02</v>
@@ -25703,10 +25781,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>44289.33702545139</v>
@@ -25727,16 +25805,16 @@
         <v>1128</v>
       </c>
       <c r="I44" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="L44" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M44">
         <v>135</v>
@@ -25793,7 +25871,7 @@
         <v>-9.672333330000001</v>
       </c>
       <c r="AE44" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF44">
         <v>0.010556</v>
@@ -25846,10 +25924,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>44289.33748606482</v>
@@ -25870,16 +25948,16 @@
         <v>1170</v>
       </c>
       <c r="I45" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="L45" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M45">
         <v>71</v>
@@ -25915,7 +25993,7 @@
         <v>-9.41155556</v>
       </c>
       <c r="AE45" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF45">
         <v>0.009506000000000001</v>
@@ -25968,10 +26046,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2">
         <v>44289.33771907407</v>
@@ -25992,16 +26070,16 @@
         <v>1188</v>
       </c>
       <c r="I46" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M46">
         <v>133</v>
@@ -26058,7 +26136,7 @@
         <v>-9.138999999999999</v>
       </c>
       <c r="AE46" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF46">
         <v>0.014907</v>
@@ -26111,10 +26189,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>44289.33817644676</v>
@@ -26135,16 +26213,16 @@
         <v>1230</v>
       </c>
       <c r="I47" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="L47" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M47">
         <v>145</v>
@@ -26180,7 +26258,7 @@
         <v>-8.81883333</v>
       </c>
       <c r="AE47" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF47">
         <v>0.0175</v>
@@ -26233,10 +26311,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>44289.33841356482</v>
@@ -26257,16 +26335,16 @@
         <v>1248</v>
       </c>
       <c r="I48" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M48">
         <v>131</v>
@@ -26323,7 +26401,7 @@
         <v>-8.747666669999999</v>
       </c>
       <c r="AE48" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF48">
         <v>0.003889</v>
@@ -26376,10 +26454,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>44289.33887225694</v>
@@ -26400,16 +26478,16 @@
         <v>1290</v>
       </c>
       <c r="I49" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="L49" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M49">
         <v>73</v>
@@ -26445,7 +26523,7 @@
         <v>-9.067833329999999</v>
       </c>
       <c r="AE49" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF49">
         <v>-0.0175</v>
@@ -26498,10 +26576,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>44289.33911373842</v>
@@ -26522,16 +26600,16 @@
         <v>1308</v>
       </c>
       <c r="I50" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="L50" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M50">
         <v>134</v>
@@ -26588,7 +26666,7 @@
         <v>-9.09333333</v>
       </c>
       <c r="AE50" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF50">
         <v>-0.001389</v>
@@ -26641,10 +26719,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>44289.33921880787</v>
@@ -26665,16 +26743,16 @@
         <v>1320</v>
       </c>
       <c r="I51" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="L51" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M51">
         <v>190</v>
@@ -26710,7 +26788,7 @@
         <v>-9.001666670000001</v>
       </c>
       <c r="AE51" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF51">
         <v>0.01</v>
@@ -26763,10 +26841,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>44289.33956538195</v>
@@ -26787,16 +26865,16 @@
         <v>1350</v>
       </c>
       <c r="I52" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="L52" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M52">
         <v>139</v>
@@ -26832,7 +26910,7 @@
         <v>-8.16866667</v>
       </c>
       <c r="AE52" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF52">
         <v>0.091111</v>
@@ -26885,10 +26963,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>44289.33994267361</v>
@@ -26909,16 +26987,16 @@
         <v>1380</v>
       </c>
       <c r="I53" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="L53" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M53">
         <v>74</v>
@@ -26954,7 +27032,7 @@
         <v>-8.199</v>
       </c>
       <c r="AE53" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF53">
         <v>-0.003333</v>
@@ -27007,10 +27085,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>44289.34026041667</v>
@@ -27031,16 +27109,16 @@
         <v>1410</v>
       </c>
       <c r="I54" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="L54" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M54">
         <v>137</v>
@@ -27076,7 +27154,7 @@
         <v>-8.33133333</v>
       </c>
       <c r="AE54" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF54">
         <v>-0.014444</v>
@@ -27129,10 +27207,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
         <v>44289.3404971875</v>
@@ -27153,16 +27231,16 @@
         <v>1428</v>
       </c>
       <c r="I55" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="L55" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M55">
         <v>87</v>
@@ -27219,7 +27297,7 @@
         <v>-8.326083329999999</v>
       </c>
       <c r="AE55" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF55">
         <v>0.000139</v>
@@ -27272,10 +27350,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>44289.34095932871</v>
@@ -27296,16 +27374,16 @@
         <v>1470</v>
       </c>
       <c r="I56" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="L56" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M56">
         <v>102</v>
@@ -27341,7 +27419,7 @@
         <v>-8.4175</v>
       </c>
       <c r="AE56" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF56">
         <v>-0.005</v>
@@ -27394,10 +27472,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2">
         <v>44289.34119378472</v>
@@ -27418,16 +27496,16 @@
         <v>1488</v>
       </c>
       <c r="I57" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="L57" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M57">
         <v>109</v>
@@ -27484,7 +27562,7 @@
         <v>-8.310833329999999</v>
       </c>
       <c r="AE57" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF57">
         <v>0.005833</v>
@@ -27537,10 +27615,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>44289.34165127315</v>
@@ -27561,16 +27639,16 @@
         <v>1530</v>
       </c>
       <c r="I58" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L58" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M58">
         <v>91</v>
@@ -27606,7 +27684,7 @@
         <v>-8.067166670000001</v>
       </c>
       <c r="AE58" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF58">
         <v>0.013333</v>
@@ -27659,10 +27737,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2">
         <v>44289.34188908565</v>
@@ -27683,16 +27761,16 @@
         <v>1548</v>
       </c>
       <c r="I59" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L59" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M59">
         <v>122</v>
@@ -27749,7 +27827,7 @@
         <v>-8.061999999999999</v>
       </c>
       <c r="AE59" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF59">
         <v>0.000278</v>
@@ -27802,10 +27880,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>44289.34199621528</v>
@@ -27826,16 +27904,16 @@
         <v>1560</v>
       </c>
       <c r="I60" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="M60">
         <v>148</v>
@@ -27871,7 +27949,7 @@
         <v>-8.03633333</v>
       </c>
       <c r="AE60" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF60">
         <v>0.002778</v>
@@ -27924,10 +28002,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>44289.34234319445</v>
@@ -27948,16 +28026,16 @@
         <v>1590</v>
       </c>
       <c r="I61" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="L61" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M61">
         <v>81</v>
@@ -27993,7 +28071,7 @@
         <v>-7.46766667</v>
       </c>
       <c r="AE61" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF61">
         <v>0.062222</v>
@@ -28046,10 +28124,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>44289.34258387732</v>
@@ -28070,16 +28148,16 @@
         <v>1608</v>
       </c>
       <c r="I62" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="L62" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M62">
         <v>90</v>
@@ -28136,7 +28214,7 @@
         <v>-7.60983333</v>
       </c>
       <c r="AE62" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF62">
         <v>-0.007778</v>
@@ -28189,10 +28267,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>44289.34304075231</v>
@@ -28213,16 +28291,16 @@
         <v>1650</v>
       </c>
       <c r="I63" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M63">
         <v>164</v>
@@ -28258,7 +28336,7 @@
         <v>-7.43716667</v>
       </c>
       <c r="AE63" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF63">
         <v>0.009443999999999999</v>
@@ -28311,10 +28389,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>44289.34327881945</v>
@@ -28335,16 +28413,16 @@
         <v>1668</v>
       </c>
       <c r="I64" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="L64" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M64">
         <v>125</v>
@@ -28401,7 +28479,7 @@
         <v>-7.3305</v>
       </c>
       <c r="AE64" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF64">
         <v>0.005833</v>
@@ -28454,10 +28532,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C65" s="2">
         <v>44289.34397466435</v>
@@ -28478,16 +28556,16 @@
         <v>1728</v>
       </c>
       <c r="I65" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="L65" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="M65">
         <v>126</v>
@@ -28544,7 +28622,7 @@
         <v>-7.0155</v>
       </c>
       <c r="AE65" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF65">
         <v>0.017222</v>
@@ -28597,10 +28675,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>44289.34411050926</v>
@@ -28621,16 +28699,16 @@
         <v>1740</v>
       </c>
       <c r="I66" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L66" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="M66">
         <v>112</v>
@@ -28666,7 +28744,7 @@
         <v>-7.07811111</v>
       </c>
       <c r="AE66" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF66">
         <v>-0.002284</v>
@@ -28719,10 +28797,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C67" s="2">
         <v>44289.34466366898</v>
@@ -28743,16 +28821,16 @@
         <v>1788</v>
       </c>
       <c r="I67" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="L67" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="M67">
         <v>16</v>
@@ -28809,7 +28887,7 @@
         <v>-7.2695</v>
       </c>
       <c r="AE67" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF67">
         <v>-0.010463</v>
@@ -28862,10 +28940,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>44289.34477461805</v>
@@ -28886,16 +28964,16 @@
         <v>1800</v>
       </c>
       <c r="I68" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="L68" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M68">
         <v>79</v>
@@ -28931,7 +29009,7 @@
         <v>-7.3305</v>
       </c>
       <c r="AE68" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF68">
         <v>-0.003333</v>
@@ -28984,10 +29062,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>44289.34512208333</v>
@@ -29008,16 +29086,16 @@
         <v>1830</v>
       </c>
       <c r="I69" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="L69" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M69">
         <v>24</v>
@@ -29053,7 +29131,7 @@
         <v>-7.27433333</v>
       </c>
       <c r="AE69" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF69">
         <v>0.006111</v>
@@ -29106,10 +29184,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>44289.34535753472</v>
@@ -29130,16 +29208,16 @@
         <v>1848</v>
       </c>
       <c r="I70" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="L70" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="M70">
         <v>21</v>
@@ -29196,7 +29274,7 @@
         <v>-7.2085</v>
       </c>
       <c r="AE70" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF70">
         <v>0.003611</v>
@@ -29249,10 +29327,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>44289.34547163195</v>
@@ -29273,16 +29351,16 @@
         <v>1860</v>
       </c>
       <c r="I71" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="L71" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="M71">
         <v>43</v>
@@ -29318,7 +29396,7 @@
         <v>-7.06133333</v>
       </c>
       <c r="AE71" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF71">
         <v>0.016111</v>
@@ -29371,10 +29449,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2">
         <v>44289.34581603009</v>
@@ -29395,16 +29473,16 @@
         <v>1890</v>
       </c>
       <c r="I72" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L72" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="M72">
         <v>333</v>
@@ -29440,7 +29518,7 @@
         <v>-7.14233333</v>
       </c>
       <c r="AE72" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF72">
         <v>-0.008888999999999999</v>
@@ -29493,10 +29571,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2">
         <v>44289.3460546875</v>
@@ -29517,16 +29595,16 @@
         <v>1908</v>
       </c>
       <c r="I73" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="L73" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M73">
         <v>352</v>
@@ -29583,7 +29661,7 @@
         <v>-7.15766667</v>
       </c>
       <c r="AE73" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF73">
         <v>-0.000833</v>
@@ -29636,10 +29714,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>44289.34640887732</v>
@@ -29660,16 +29738,16 @@
         <v>1938</v>
       </c>
       <c r="I74" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L74" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="M74">
         <v>59</v>
@@ -29726,7 +29804,7 @@
         <v>-3.41366667</v>
       </c>
       <c r="AE74" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF74">
         <v>0.409444</v>
@@ -29779,10 +29857,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>44289.34674935185</v>
@@ -29803,16 +29881,16 @@
         <v>1968</v>
       </c>
       <c r="I75" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="L75" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M75">
         <v>59</v>
@@ -29869,7 +29947,7 @@
         <v>0.12166667</v>
       </c>
       <c r="AE75" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AF75">
         <v>0.386667</v>
